--- a/admin_testy/reporty_google_testy/google_data/Opravný Report.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Opravný Report.xlsx
@@ -15,9 +15,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="239">
   <si>
-    <t>Prosek</t>
+    <t>Bolevec</t>
   </si>
   <si>
     <t>Datum</t>
@@ -86,37 +86,34 @@
     <t>Počet hodin</t>
   </si>
   <si>
-    <t>Makula Radek</t>
+    <t>Tůma Vladimír</t>
   </si>
   <si>
     <t>10:00</t>
   </si>
   <si>
-    <t>18:30</t>
+    <t>17:00</t>
   </si>
   <si>
     <t>Výdaje</t>
   </si>
   <si>
-    <t>Pešová Hana</t>
+    <t>Vostrý Daniel</t>
   </si>
   <si>
-    <t>17:00</t>
+    <t>11:00</t>
   </si>
   <si>
-    <t>03:30</t>
+    <t>19:00</t>
   </si>
   <si>
     <t>Benzín</t>
   </si>
   <si>
-    <t>Bušek Pavel</t>
+    <t>Roth Stanislav ml.</t>
   </si>
   <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>23:00</t>
+    <t>01:00</t>
   </si>
   <si>
     <t>Auta</t>
@@ -168,6 +165,18 @@
   </si>
   <si>
     <t>Počet pozdě přiřazeným WoltDrive 5+</t>
+  </si>
+  <si>
+    <t>Světlík František</t>
+  </si>
+  <si>
+    <t>Vopatová Šárka</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>Kaločai Rudolf</t>
   </si>
   <si>
     <t>Woltrdive zpožděný kvůli našemu pozdnímu přiřazení</t>
@@ -260,13 +269,37 @@
     <t>Položky</t>
   </si>
   <si>
-    <t>bolt</t>
+    <t>manual</t>
   </si>
   <si>
     <t>delivered</t>
   </si>
   <si>
-    <t>Abdurakhmon</t>
+    <t>delivery</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>2026-04-06T22:44:33.681+02:00</t>
+  </si>
+  <si>
+    <t>2026-04-06T22:55:57.719+02:00</t>
+  </si>
+  <si>
+    <t>2026-04-06T23:07:27.875+02:00</t>
+  </si>
+  <si>
+    <t>2026-04-06T22:55:43.568+02:00</t>
+  </si>
+  <si>
+    <t>Ručně zadané obj.</t>
+  </si>
+  <si>
+    <t>[{"id":"18c7dc2e-3f8c-4b58-9c90-6a401315d32b","count":1,"label":"Pizza Hawai 32 cm","posId":"114","price":25900,"isExtra":false,"creatorId":"zE1getDe-l4Go65xgt3j8","isPackging":0,"actualLabel":"Pizza Hawai 32 cm"}]</t>
+  </si>
+  <si>
+    <t>damejidlo</t>
   </si>
   <si>
     <t>external-delivery</t>
@@ -275,1006 +308,313 @@
     <t>online</t>
   </si>
   <si>
-    <t>2026-04-12T02:42:53.401+02:00</t>
+    <t>2026-04-06T22:37:04.268+02:00</t>
   </si>
   <si>
-    <t>2026-04-12T02:50:30.690+02:00</t>
+    <t>2026-04-06T22:47:08.084+02:00</t>
   </si>
   <si>
-    <t>Pizza Comeback Prosek</t>
+    <t>F - Pizza Comeback Bolevec</t>
   </si>
   <si>
-    <t>[{"id":"N125","note":"","count":1,"label":"Pepsi zero sugar 1l","posId":"N125","price":5900,"isExtra":false},{"id":"116","note":"","count":1,"label":"Baby Špenát &amp; kuře 32cm","posId":"116","price":24900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"X1000","note":"","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true},{"id":"B105","note":"","count":1,"label":"Žampiony","posId":"B105","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"B115","note":"","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+    <t>[{"id":"62240199","note":"","size":"Margherita 32cm","count":2,"label":"Margherita 32cm","posId":"112","price":21900,"isExtra":false},{"id":"62240274","note":"","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
   </si>
   <si>
-    <t>manual</t>
+    <t>generic</t>
   </si>
   <si>
     <t>pickup</t>
   </si>
   <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>2026-04-12T02:19:19.006+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-12T02:26:32.320+02:00</t>
-  </si>
-  <si>
-    <t>Ručně zadané obj.</t>
-  </si>
-  <si>
-    <t>[{"id":"8cf43086-2f35-4343-92aa-dcd50f5af3a1","count":1,"label":"Pečené brambory","posId":"P103","price":6900,"isExtra":false,"creatorId":"8Tz3a6YGZlTH94KWDx-ii","isPackging":0,"actualLabel":"Pečené brambory"}]</t>
-  </si>
-  <si>
-    <t>2026-04-12T02:13:49.316+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-12T02:27:18.548+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"106","note":"","count":1,"label":"BBQ Meteor 40cm","posId":"106","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>wolt</t>
-  </si>
-  <si>
-    <t>2026-04-12T02:13:07.868+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-12T02:24:50.503+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc1d","count":1,"label":"Quattro Formaggi 32cm","posId":"123","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69400db90dc626f6c3c3fc53","count":1,"label":"Spicy Wings 🌶️","posId":"P101","price":11900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69400db90dc626f6c3c3fc2b","count":1,"label":"Hawai 32cm","posId":"114","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>Adil</t>
-  </si>
-  <si>
-    <t>2026-04-12T01:53:13.231+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-12T02:02:29.347+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"109","note":"","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"C114","note":"","count":1,"label":"Kuře","posId":"C114","price":4000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-12T01:41:46.459+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-12T01:53:25.465+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc0b","count":1,"label":"BBQ Texas 40cm","posId":"107","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"674840e52b930230e954cf9f","count":1,"label":"Rajčatový základ","posId":"ZBR40","price":0,"isExtra":true},{"id":"69bfb59f31761dcca50835ec","count":1,"label":"okraj mozzarella, bbq omáčka","posId":"A124","price":6500,"isExtra":true},{"id":"695458c28103d4672f51a9e5","count":1,"label":"Cibule","posId":"C103","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"695458c28103d4672f51a9e6","count":1,"label":"Kukuřice","posId":"C115","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"695458c28103d4672f51a9e7","count":1,"label":"Špenát s česnekem","posId":"C107","price":3500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-12T01:21:30.564+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-12T01:30:57.161+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc5b","count":1,"label":"Pepperoni Rolls 🌶️","posId":"P100","price":8900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69400db90dc626f6c3c3fc23","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"6977bf4da1da98ea63c3a718","count":1,"label":"USA těsto","posId":"17","price":1000,"isExtra":true},{"id":"69bfb59f31761dcca50839dc","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true},{"id":"695458c28103d4672f51abc3","count":1,"label":"Olivy","posId":"B112","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"69400db90dc626f6c3c3fc5d","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>Dmytro</t>
-  </si>
-  <si>
-    <t>2026-04-12T00:30:42.726+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-12T00:41:56.917+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"111","note":"","count":1,"label":"Quattro Formaggi 40cm","posId":"111","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"ZSR40","note":"","count":1,"label":"Rajčatový základ","posId":"ZSR40","price":0,"isExtra":true},{"id":"X1000","note":"","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true},{"id":"C115","note":"","count":1,"label":"Kukuřice","posId":"C115","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"P103","note":"","count":1,"label":"Pečené brambory","posId":"P103","price":6900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"N125","note":"","count":1,"label":"Pepsi zero sugar 1l","posId":"N125","price":5900,"isExtra":false}]</t>
-  </si>
-  <si>
-    <t>Tomáš</t>
-  </si>
-  <si>
-    <t>2026-04-12T00:27:08.633+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-12T00:36:33.882+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"110","note":"","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"ZRS40","note":"","count":1,"label":"Smetanový základ","posId":"ZRS40","price":0,"isExtra":true},{"id":"113","note":"","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"B115","note":"","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"B114","note":"","count":1,"label":"Kuře","posId":"B114","price":3000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-12T00:19:52.656+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-12T00:27:08.883+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"101","note":"","count":1,"label":"Capricciosa 40cm","posId":"101","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"X112","note":"","count":1,"label":"Bez oliv","posId":"X112","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"N120","note":"","count":1,"label":"Aquilla černý čaj a broskev 0,5l","posId":"N120","price":4900,"isExtra":false},{"id":"N124","note":"","count":1,"label":"Pepsi 1l","posId":"N124","price":5900,"isExtra":false},{"id":"P106","note":"","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T23:59:24.578+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-12T00:08:33.198+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc21","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69bfb59f31761dcca50839dc","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>damejidlo</t>
-  </si>
-  <si>
-    <t>2026-04-11T23:53:54.906+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-12T00:03:03.106+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"59610973","note":"","size":"Capricciosa 32cm","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"57081144","note":"","count":1,"label":"Bez žampionů","posId":"X105","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"57081163","note":"","count":1,"label":"Bez oliv","posId":"X112","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"59610964","note":"","size":"Margherita 32cm","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"57081069","note":"","size":"Česnekový dip","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T23:50:46.485+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T23:57:21.773+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc01","count":1,"label":"Margherita 40cm","posId":"100","price":26900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T23:34:14.505+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T23:43:05.754+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"109","note":"","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"X1000","note":"","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>generic</t>
-  </si>
-  <si>
     <t>card</t>
   </si>
   <si>
-    <t>2026-04-11T23:01:03.635+02:00</t>
+    <t>2026-04-06T21:49:03.985+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T23:23:35.561+02:00</t>
+    <t>2026-04-06T21:57:54.309+02:00</t>
   </si>
   <si>
-    <t>Adaptee bridge</t>
+    <t>Adaptee</t>
   </si>
   <si>
-    <t>[{"id":"1fae666b-4102-4ed0-b317-2a07b21ae279","note":"","count":1,"label":"Hot &amp; Spicy 40 cm","posId":"110","price":30900,"isExtra":false}]</t>
+    <t>[{"id":"e12521cc-9391-4513-be27-f090014536cf","note":"","count":1,"label":"BBQ Texas 32 cm","posId":"143","price":25900,"isExtra":false}]</t>
   </si>
   <si>
-    <t>2026-04-11T23:00:40.807+02:00</t>
+    <t>2026-04-06T21:33:05.971+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T23:13:11.691+02:00</t>
+    <t>2026-04-06T21:47:11.278+02:00</t>
   </si>
   <si>
-    <t>[{"id":"9d39facb-927e-41df-970a-8bfedd627640","count":1,"label":"Pizza Capricciosa 18","posId":"125","price":11900,"isExtra":false,"creatorId":"29D75GiXc5-hS0QzMh5K2","isPackging":0,"actualLabel":"Pizza Capricciosa 18"},{"id":"1582d301-bf10-4138-ae7c-8790c6504985","count":1,"label":"Pizza Pepperoni 18","posId":"132","price":11900,"isExtra":false,"creatorId":"2OJmG-Q6z_LW5rStS5fnI","isPackging":0,"actualLabel":"Pizza Pepperoni 18"}]</t>
+    <t>[{"id":"5b1f2843-926a-4dd1-a5f0-4fddc7b45013","note":"","count":1,"label":"Margherita 32 cm","posId":"112","price":21900,"isExtra":false},{"id":"8b18781f-3bd0-464d-aa33-9f081ecc1a3a","note":"","count":1,"label":"mozzarella","posId":"8b18781f-3bd0-464d-aa33-9f081ecc1a3a","price":3000,"isExtra":true},{"id":"d1e9623b-89c9-4caa-a2ba-cbaafad1a883","note":"","count":1,"label":"slanina","posId":"d1e9623b-89c9-4caa-a2ba-cbaafad1a883","price":3000,"isExtra":true},{"id":"68d93a2c-5ce2-44a5-857b-6d579cd1f445","note":"","count":1,"label":"žampiony","posId":"68d93a2c-5ce2-44a5-857b-6d579cd1f445","price":2500,"isExtra":true},{"id":"9461c599-e1f4-4267-8dd8-c1eea66839a3","note":"","count":1,"label":"Choco Rolls, 6 ks","posId":"chr100","price":8900,"isExtra":false}]</t>
   </si>
   <si>
-    <t>2026-04-11T22:59:28.109+02:00</t>
+    <t>2026-04-06T21:20:27.217+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T23:18:54.068+02:00</t>
+    <t>2026-04-06T21:26:59.032+02:00</t>
   </si>
   <si>
-    <t>[{"id":"59610967","note":"","size":"Comeback 32cm 🌶️","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"57081030","note":"","size":"Baby špenát &amp; kuře 40cm","count":1,"label":"Baby špenát &amp; kuře 40cm","posId":"104","price":30900,"isExtra":false},{"id":"57081101","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
+    <t>[{"id":"18c7dc2e-3f8c-4b58-9c90-6a401315d32b","count":1,"label":"Pizza Hawai 32 cm","posId":"114","price":25900,"isExtra":false,"creatorId":"pR4PgHht5JCs2f7VfeOUc","isPackging":0,"actualLabel":"Pizza Hawai 32 cm"}]</t>
   </si>
   <si>
-    <t>2026-04-11T22:58:33.003+02:00</t>
+    <t>bolt</t>
   </si>
   <si>
-    <t>2026-04-11T23:13:22.578+02:00</t>
+    <t>Vít</t>
   </si>
   <si>
-    <t>[{"id":"9d39facb-927e-41df-970a-8bfedd627640","count":1,"label":"Pizza Capricciosa 18","posId":"125","price":11900,"isExtra":false,"creatorId":"niameBqkfzoToTqPgQPtM","isPackging":0,"actualLabel":"Pizza Capricciosa 18"},{"id":"extra_20230331101812_49","count":1,"label":"Žampiony","posId":"A105","price":1500,"isExtra":true,"mainItemId":"9d39facb-927e-41df-970a-8bfedd627640"}]</t>
+    <t>2026-04-06T21:10:17.149+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:53:13.572+02:00</t>
+    <t>2026-04-06T21:19:40.655+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T23:09:44.528+02:00</t>
+    <t>B - Pizza Comeback Bolevec</t>
   </si>
   <si>
-    <t>[{"id":"38ba12cb-7e06-4754-8714-03609598fc8f","count":1,"label":"Pizza Hot &amp; Spicy 32","posId":"122","price":24900,"isExtra":false,"creatorId":"KLYT3RrHjHLqCOxbsTjOq","isPackging":0,"actualLabel":"Pizza Hot &amp; Spicy 32"}]</t>
+    <t>[{"id":"107","note":"","count":1,"label":"BBQ Texas 40cm","posId":"107","price":32900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"ZBR40","note":"","count":1,"label":"Rajčatový základ","posId":"ZBR40","price":0,"isExtra":true}]</t>
   </si>
   <si>
-    <t>Alimardon</t>
+    <t>2026-04-06T20:39:16.746+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:50:28.418+02:00</t>
+    <t>2026-04-06T21:02:57.691+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T23:17:25.109+02:00</t>
+    <t>[{"id":"bbef59ce-896e-4add-acca-1c087f56506a","count":1,"label":"Pepsi 0,33l","posId":"N170","price":3900,"isExtra":false,"creatorId":"YT5tHrFIarVQoBlzpTxWI","isPackging":0,"actualLabel":"Pepsi 0,33l"},{"id":"cd43f6a9-7b26-4cdf-8aa9-85510522383c","count":1,"label":"Poděbradská malinovka 0,5l","posId":"N129","price":4900,"isExtra":false,"creatorId":"Ah05_HAPxtqXrJDy-msLZ","isPackging":0,"actualLabel":"Poděbradská malinovka 0,5l"}]</t>
   </si>
   <si>
-    <t>[{"id":"104","note":"","count":1,"label":"Baby špenát &amp; kuře 40cm","posId":"104","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"C112","note":"","count":1,"label":"Olivy","posId":"C112","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"C109","note":"","count":1,"label":"Pepperoni salám","posId":"C109","price":4000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"C116","note":"","count":1,"label":"Masové kuličky","posId":"C116","price":8900,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+    <t>Ionuț</t>
   </si>
   <si>
-    <t>2026-04-11T22:44:43.397+02:00</t>
+    <t>2026-04-06T20:21:42.796+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T23:03:09.861+02:00</t>
+    <t>2026-04-06T20:27:40.518+02:00</t>
   </si>
   <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc21","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"6977bf4da1da98ea63c3a718","count":1,"label":"USA těsto","posId":"17","price":1000,"isExtra":true},{"id":"69bfb5a1d2b79c5461515a4d","count":1,"label":"Opočno vanilková","posId":"D108","price":12900,"isExtra":false},{"id":"69400db90dc626f6c3c3fc5f","count":1,"label":"BBQ dip","posId":"P105","price":2000,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+    <t>[{"id":"109","note":"","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":32900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"ZRB40","note":"","count":1,"label":"BBQ základ","posId":"ZRB40","price":0,"isExtra":true},{"id":"N131","note":"","count":1,"label":"BIRGO grapefruit 0,5l","posId":"N131","price":4900,"isExtra":false}]</t>
   </si>
   <si>
-    <t>Ashok</t>
+    <t>2026-04-06T20:11:08.994+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:39:24.215+02:00</t>
+    <t>2026-04-06T21:02:58.881+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:53:44.648+02:00</t>
+    <t>[{"id":"e258c1f0-59ca-47a0-b097-7e447a442599","count":1,"label":"Mirinda 1l","posId":"N126","price":5900,"isExtra":false,"creatorId":"iWw5LjXL5mvENpAvmuMcW","isPackging":0,"actualLabel":"Mirinda 1l"}]</t>
   </si>
   <si>
-    <t>[{"id":"113","note":"","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"ZRS32","note":"","count":1,"label":"Smetanový základ","posId":"ZRS32","price":0,"isExtra":true},{"id":"A121","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true}]</t>
+    <t>Patrik</t>
   </si>
   <si>
-    <t>delivery</t>
+    <t>2026-04-06T19:52:21.014+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:33:04.110+02:00</t>
+    <t>2026-04-06T20:00:57.647+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T23:00:10.527+02:00</t>
+    <t>[{"id":"102","note":"","count":1,"label":"Hawai 40cm","posId":"102","price":32900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"ZRS40","note":"","count":1,"label":"Smetanový základ","posId":"ZRS40","price":0,"isExtra":true}]</t>
   </si>
   <si>
-    <t>2026-04-11T23:24:10.770+02:00</t>
+    <t>2026-04-06T19:23:31.794+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:38:35.875+02:00</t>
+    <t>2026-04-06T19:26:48.220+02:00</t>
   </si>
   <si>
-    <t>[{"id":"03ade9ce-5d0f-4499-a6a3-340b58ae4468","note":"","count":1,"label":"Capricciosa 32 cm","posId":"113","price":24900,"isExtra":false},{"id":"5b1f2843-926a-4dd1-a5f0-4fddc7b45013","note":"","count":1,"label":"Margherita 32 cm","posId":"112","price":20900,"isExtra":false},{"id":"21fd0686-e8d1-43f1-84c9-d96f5842a3ca","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true},{"id":"38de8e38-e51e-422d-9a89-960ebc505f1b","note":"","count":1,"label":"šunka","posId":"B106","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"c1383a56-9eef-4159-8de6-52ba98917da4","note":"","count":1,"label":"Pepperoni Rolls, 6 ks","posId":"P100","price":8900,"isExtra":false},{"id":"3a8b6a85-3b5c-4ee4-be2d-261ab8731d6e","note":"","count":1,"label":"Dip česnekový","posId":"P106","price":2000,"isExtra":false}]</t>
+    <t>[{"id":"34a0b831-1e92-45b3-8a4a-018d05baf41c","count":1,"label":"Pepsi zero 0,33l","posId":"N171","price":3900,"isExtra":false,"creatorId":"FxpDNQLB2-Dna3w4_AmNw","isPackging":0,"actualLabel":"Pepsi zero 0,33l"}]</t>
   </si>
   <si>
-    <t>2026-04-11T22:27:06.660+02:00</t>
+    <t>2026-04-06T19:23:10.358+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:36:42.631+02:00</t>
+    <t>2026-04-06T19:26:44.139+02:00</t>
   </si>
   <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc2b","count":1,"label":"Hawai 32cm","posId":"114","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"674840e52b930230e954cbf7","count":1,"label":"Smetanový základ","posId":"ZRS32","price":0,"isExtra":true},{"id":"69bfb59f31761dcca50839dc","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true}]</t>
+    <t>[{"id":"1bf8f3b6-43e9-4ddc-97f7-70f0b7f9dc97","count":1,"label":"Pizza Pepperoni 18","posId":"132","price":13900,"isExtra":false,"creatorId":"wYdsrEWHLHFyuBH2hNBsR","isPackging":0,"actualLabel":"Pizza Pepperoni 18"}]</t>
   </si>
   <si>
-    <t>2026-04-11T22:23:35.007+02:00</t>
+    <t>2026-04-06T19:11:33.410+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:31:32.582+02:00</t>
+    <t>2026-04-06T19:26:46.608+02:00</t>
   </si>
   <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc2d","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69bfb59f31761dcca50839dc","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true},{"id":"69400db90dc626f6c3c3fc65","count":2,"label":"Dip Jalapeňos","posId":"P107","price":2000,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+    <t>[{"id":"864ed54f-c99e-45ab-b65e-dc3c6ef3ae72","count":1,"label":"Pizza Quattro Formaggi 32","posId":"123","price":25900,"isExtra":false,"creatorId":"8nR-z5SG9umZgRy9Ylwop","isPackging":0,"actualLabel":"Pizza Quattro Formaggi 32"}]</t>
   </si>
   <si>
-    <t>2026-04-11T22:21:33.877+02:00</t>
+    <t>2026-04-06T19:10:27.954+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:51:37.700+02:00</t>
+    <t>2026-04-06T19:11:56.743+02:00</t>
   </si>
   <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc1f","count":2,"label":"Hot &amp; Spicy 32cm 🌶️🌶️","posId":"122","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69400db90dc626f6c3c3fc23","count":2,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69400db90dc626f6c3c3fc2f","count":1,"label":"Baby Špenát &amp; kuře 32cm","posId":"116","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69400db90dc626f6c3c3fc5b","count":1,"label":"Pepperoni Rolls 🌶️","posId":"P100","price":8900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+    <t>[{"id":"34a0b831-1e92-45b3-8a4a-018d05baf41c","count":1,"label":"Pepsi zero 0,33l","posId":"N171","price":3900,"isExtra":false,"creatorId":"Ijaimo-_r1RXObukUW2sL","isPackging":0,"actualLabel":"Pepsi zero 0,33l"}]</t>
   </si>
   <si>
-    <t>2026-04-11T22:16:16.486+02:00</t>
+    <t>2026-04-06T19:07:58.605+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:42:11.381+02:00</t>
+    <t>2026-04-06T19:19:43.064+02:00</t>
   </si>
   <si>
-    <t>[{"id":"38ba12cb-7e06-4754-8714-03609598fc8f","count":1,"label":"Pizza Hot &amp; Spicy 32","posId":"122","price":24900,"isExtra":false,"creatorId":"nceqBco8fs1NGWhFVqcyI","isPackging":0,"actualLabel":"Pizza Hot &amp; Spicy 32"}]</t>
+    <t>[{"id":"62240190","note":"","size":"Comeback 40cm 🌶️","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":32900,"isExtra":false},{"id":"62240266","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"62240337","note":"","count":1,"label":"Bez cibule","posId":"X103","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"62240234","note":"","size":"Dip Jalapeňos","count":1,"label":"Dip Jalapeňos","posId":"P107","price":2500,"isExtra":false}]</t>
   </si>
   <si>
-    <t>2026-04-11T22:14:59.600+02:00</t>
+    <t>2026-04-06T18:46:37.967+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:42:10.388+02:00</t>
+    <t>2026-04-06T18:52:15.315+02:00</t>
   </si>
   <si>
-    <t>[{"id":"38ba12cb-7e06-4754-8714-03609598fc8f","count":1,"label":"Pizza Hot &amp; Spicy 32","posId":"122","price":24900,"isExtra":false,"creatorId":"zlAx8DQ5jWRH5a0b_A93J","isPackging":0,"actualLabel":"Pizza Hot &amp; Spicy 32"}]</t>
+    <t>[{"id":"49248c77-0000-4748-b81a-507bb0a368ea","count":1,"label":"Pepsi 1l","posId":"N124","price":5900,"isExtra":false,"creatorId":"jMSvIEN0tNU-q7aHQaQDv","isPackging":0,"actualLabel":"Pepsi 1l"},{"id":"e687efb2-38f2-4448-89a9-c358d6fc33e5","count":1,"label":"Aquila černý čaj/broskev 0,33l","posId":"N175","price":3900,"isExtra":false,"creatorId":"qXLIO-RUuNzZyr63gx3hr","isPackging":0,"actualLabel":"Aquila černý čaj/broskev 0,33l"}]</t>
   </si>
   <si>
-    <t>Jan</t>
+    <t>2026-04-06T18:20:03.365+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:10:24.134+02:00</t>
+    <t>2026-04-06T18:28:51.033+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:24:33.469+02:00</t>
+    <t>2026-04-06T18:51:28.424+02:00</t>
   </si>
   <si>
-    <t>[{"id":"123","note":"","count":1,"label":"Quattro Formaggi 32cm","posId":"123","price":24900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"ZSR32","note":"","count":1,"label":"Rajčatový základ","posId":"ZSR32","price":0,"isExtra":true},{"id":"X1000","note":"","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true},{"id":"B106","note":"","count":1,"label":"Šunka","posId":"B106","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"113","note":"","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+    <t>2026-04-06T18:23:59.908+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:09:52.676+02:00</t>
+    <t>[{"id":"5b1f2843-926a-4dd1-a5f0-4fddc7b45013","note":"","count":1,"label":"Margherita 32 cm","posId":"112","price":21900,"isExtra":false},{"id":"57c816b2-3e3f-46c2-b126-b09910d79cb0","note":"","count":1,"label":"změna na Smetanový základ","posId":"57c816b2-3e3f-46c2-b126-b09910d79cb0","price":0,"isExtra":true},{"id":"9461c599-e1f4-4267-8dd8-c1eea66839a3","note":"","count":1,"label":"Choco Rolls, 6 ks","posId":"chr100","price":8900,"isExtra":false}]</t>
   </si>
   <si>
-    <t>2026-04-11T22:20:31.662+02:00</t>
+    <t>2026-04-06T17:34:25.026+02:00</t>
   </si>
   <si>
-    <t>[{"id":"57081024","note":"","size":"Quattro Formaggi 40cm","count":1,"label":"Quattro Formaggi 40cm","posId":"111","price":30900,"isExtra":false},{"id":"57081101","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"57081071","note":"","size":"Jalapenos Rolls","count":1,"label":"Jalapenos Rolls","posId":"jpr200","price":8900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59278384","note":"","size":"Spicy Wings 🌶️","count":1,"label":"Spicy Wings 🌶️","posId":"P101","price":11900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+    <t>2026-04-06T17:43:01.469+02:00</t>
   </si>
   <si>
-    <t>Miroslav</t>
+    <t>[{"id":"666f5d57-c79d-415f-bd66-38dc47ee4585","count":1,"label":"Pizza Pepperoni 32","posId":"120","price":25900,"isExtra":false,"creatorId":"MeGZdZG0iPgGr2ZrLTs0F","isPackging":0,"actualLabel":"Pizza Pepperoni 32"},{"id":"49248c77-0000-4748-b81a-507bb0a368ea","count":1,"label":"Pepsi 1l","posId":"N124","price":5900,"isExtra":false,"creatorId":"S2g6eF31nSd3b3CGDMt6O","isPackging":0,"actualLabel":"Pepsi 1l"}]</t>
   </si>
   <si>
-    <t>2026-04-11T22:03:38.111+02:00</t>
+    <t>2026-04-06T17:26:43.672+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:09:56.388+02:00</t>
+    <t>2026-04-06T17:37:05.982+02:00</t>
   </si>
   <si>
-    <t>[{"id":"101","note":"","count":1,"label":"Capricciosa 40cm","posId":"101","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
+    <t>[{"id":"62240188","note":"","size":"Quattro Formaggi 40cm","count":1,"label":"Quattro Formaggi 40cm","posId":"111","price":32900,"isExtra":false},{"id":"62240266","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"62240246","note":"","size":"Pepsi 1l","count":1,"label":"Pepsi 1l","posId":"N124","price":5900,"isExtra":false}]</t>
   </si>
   <si>
-    <t>2026-04-11T21:57:10.088+02:00</t>
+    <t>Silviu</t>
   </si>
   <si>
-    <t>2026-04-11T22:04:55.571+02:00</t>
+    <t>2026-04-06T16:40:29.988+02:00</t>
   </si>
   <si>
-    <t>[{"id":"101","note":"","count":1,"label":"Capricciosa 40cm","posId":"101","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"X1000","note":"","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true}]</t>
+    <t>2026-04-06T16:52:49.957+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:56:04.509+02:00</t>
+    <t>[{"id":"109","note":"","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":32900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
   </si>
   <si>
-    <t>2026-04-11T22:02:08.638+02:00</t>
+    <t>2026-04-06T16:37:08.656+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:24:13.644+02:00</t>
+    <t>2026-04-06T16:46:41.912+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:56:43.803+02:00</t>
+    <t>[{"id":"c547f780-e6f1-4d3b-9918-8b0f0ac6fdac","count":2,"label":"Americano","posId":"N158","price":5500,"isExtra":false,"creatorId":"J1aQ7C76AynMCdNmNXvRl","isPackging":0,"actualLabel":"Americano"},{"id":"864ed54f-c99e-45ab-b65e-dc3c6ef3ae72","count":1,"label":"Pizza Quattro Formaggi 32","posId":"123","price":25900,"isExtra":false,"creatorId":"RHnfvtNIbDRa4oWEsnmk6","isPackging":0,"actualLabel":"Pizza Quattro Formaggi 32"}]</t>
   </si>
   <si>
-    <t>[{"id":"3a8b6a85-3b5c-4ee4-be2d-261ab8731d6e","note":"","count":1,"label":"Dip česnekový","posId":"P106","price":2000,"isExtra":false},{"id":"35e045f9-bc36-46e9-8142-6579de78a05b","note":"","count":1,"label":"Comeback 32 cm","posId":"121","price":24900,"isExtra":false}]</t>
+    <t>2026-04-06T16:04:17.207+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:50:06.048+02:00</t>
+    <t>2026-04-06T16:04:45.547+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:56:58.167+02:00</t>
+    <t>[{"id":"14ed2657-b58d-4efd-97ae-3a48a4555f3f","count":1,"label":"Guarana kiwi a jablko","posId":"N144","price":5500,"isExtra":false,"creatorId":"NAu9Isqf9uwRqUDoE98GE","isPackging":0,"actualLabel":"Guarana kiwi a jablko"}]</t>
   </si>
   <si>
-    <t>2026-04-11T22:17:09.114+02:00</t>
+    <t>2026-04-06T14:58:14.326+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:50:21.368+02:00</t>
+    <t>2026-04-06T14:58:19.733+02:00</t>
   </si>
   <si>
-    <t>[{"id":"bf8dc38b-6c8e-42b6-9da3-3170253a57d4","note":"","count":1,"label":"Hot &amp; Spicy 32 cm","posId":"122","price":24900,"isExtra":false},{"id":"169906cc-98ac-4101-a361-79ae530758c3","note":"","count":1,"label":"BEZ -cibule","posId":"X103","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"b3008ec8-24a5-4d30-bf46-9133028be7e4","note":"","count":1,"label":"Margherita 32 cm","posId":"136","price":20900,"isExtra":false},{"id":"57c816b2-3e3f-46c2-b126-b09910d79cb0","note":"","count":1,"label":"změna na Smetanový základ","posId":"57c816b2-3e3f-46c2-b126-b09910d79cb0","price":0,"isExtra":true},{"id":"c8019f80-065c-4f09-9e80-65b85dae2ae1","note":"","count":1,"label":"kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"38de8e38-e51e-422d-9a89-960ebc505f1b","note":"","count":1,"label":"šunka","posId":"B106","price":3000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+    <t>[{"id":"bbef59ce-896e-4add-acca-1c087f56506a","count":1,"label":"Pepsi 0,33l","posId":"N170","price":3900,"isExtra":false,"creatorId":"NZ8nH89V-A2wnJeLRSbCU","isPackging":0,"actualLabel":"Pepsi 0,33l"}]</t>
   </si>
   <si>
-    <t>2026-04-11T21:45:23.981+02:00</t>
+    <t>2026-04-06T14:31:45.477+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:52:36.568+02:00</t>
+    <t>2026-04-06T14:36:53.612+02:00</t>
   </si>
   <si>
-    <t>[{"id":"119","note":"","count":1,"label":"BBQ Texas 32cm","posId":"119","price":24900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"ZBR32","note":"","count":1,"label":"Rajčatový základ","posId":"ZBR32","price":0,"isExtra":true},{"id":"A117","note":"","count":1,"label":"okraj hotdog, hořčice","posId":"A117","price":5700,"isExtra":true}]</t>
+    <t>[{"id":"4696b740-51e2-4c8f-b903-bce803717f15","count":1,"label":"BIRGO grapefruit 0,5l","posId":"N131","price":4900,"isExtra":false,"creatorId":"eWHRWK0Rv4oJ8DHVWQs6M","isPackging":0,"actualLabel":"BIRGO grapefruit 0,5l"}]</t>
   </si>
   <si>
-    <t>2026-04-11T21:34:54.891+02:00</t>
+    <t>2026-04-06T14:11:24.553+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:44:27.421+02:00</t>
+    <t>2026-04-06T14:11:55.625+02:00</t>
   </si>
   <si>
-    <t>[{"id":"59610973","note":"","size":"Capricciosa 32cm","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59610976","note":"","count":1,"label":"USA těsto","posId":"17","price":1000,"isExtra":true},{"id":"57081176","note":"","count":1,"label":"okraj hotdog, bbq omáčka","posId":"A119","price":5700,"isExtra":true}]</t>
+    <t>[{"id":"34a0b831-1e92-45b3-8a4a-018d05baf41c","count":1,"label":"Pepsi zero 0,33l","posId":"N171","price":3900,"isExtra":false,"creatorId":"-KwU98--AtgdfAupWypf7","isPackging":0,"actualLabel":"Pepsi zero 0,33l"},{"id":"34a0b831-1e92-45b3-8a4a-018d05baf41c","count":1,"label":"Pepsi zero 0,33l","posId":"N171","price":3900,"isExtra":false,"creatorId":"_rcMeKQj7VOSwj6cOGUN6","isPackging":0,"actualLabel":"Pepsi zero 0,33l"}]</t>
   </si>
   <si>
-    <t>2026-04-11T21:33:11.000+02:00</t>
+    <t>2026-04-06T13:40:03.285+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:46:01.373+02:00</t>
+    <t>2026-04-06T13:51:02.851+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:46:01.372+02:00</t>
+    <t>[{"id":"a4efa812-1470-4ea2-a19d-39843abed3be","note":"","count":1,"label":"Comeback 32 cm","posId":"145","price":25900,"isExtra":false},{"id":"21fd0686-e8d1-43f1-84c9-d96f5842a3ca","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"21fd0686-e8d1-43f1-84c9-d96f5842a3ca","price":5900,"isExtra":true},{"id":"169906cc-98ac-4101-a361-79ae530758c3","note":"","count":1,"label":"BEZ -cibule","posId":"169906cc-98ac-4101-a361-79ae530758c3","price":0,"isExtra":true}]</t>
   </si>
   <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc09","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"674840e52b930230e954cea6","count":1,"label":"Smetanový základ","posId":"ZRS40","price":0,"isExtra":true},{"id":"69bfb59f31761dcca50835ea","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true},{"id":"684ae9784182d05e5daecb21","count":1,"label":"Bez mozzarelly","posId":"X113","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"69400db90dc626f6c3c3fc63","count":1,"label":"Choco Rolls","posId":"chr100","price":8900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+    <t>Oleksandr</t>
   </si>
   <si>
-    <t>2026-04-11T21:24:04.583+02:00</t>
+    <t>2026-04-06T13:33:11.599+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:34:35.262+02:00</t>
+    <t>2026-04-06T13:43:18.908+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T22:02:52.073+02:00</t>
+    <t>[{"id":"107","note":"","count":1,"label":"BBQ Texas 40cm","posId":"107","price":32900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
   </si>
   <si>
-    <t>2026-04-11T21:25:13.313+02:00</t>
+    <t>2026-04-06T13:08:40.537+02:00</t>
   </si>
   <si>
-    <t>[{"id":"95bce60f-e62f-4ae7-90e9-e09260893da5","note":"","count":1,"label":"Baby špenát &amp; kuře 18 cm","posId":"128","price":11900,"isExtra":false},{"id":"c5b474e6-18c7-4e68-bfba-30417cf8de0f","note":"","count":1,"label":"Kukuřice.","posId":"A115","price":1500,"isExtra":true},{"id":"28b3f739-f42a-4ef9-8499-ad66cad79c40","note":"","count":1,"label":"Hot &amp; Spicy 18 cm","posId":"134","price":11900,"isExtra":false}]</t>
+    <t>2026-04-06T13:12:01.167+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:21:06.902+02:00</t>
+    <t>[{"id":"d524a5a3-a53a-4542-a32f-c55dbe2cd1d4","count":2,"label":"Cappucino","posId":"N152","price":6500,"isExtra":false,"creatorId":"a-ZMNV0cMDeDOQ29QdMVP","isPackging":0,"actualLabel":"Cappucino"}]</t>
   </si>
   <si>
-    <t>2026-04-11T21:34:33.545+02:00</t>
+    <t>2026-04-06T11:46:49.229+02:00</t>
   </si>
   <si>
-    <t>[{"id":"57081029","note":"","size":"BBQ Meteor 40cm","count":1,"label":"BBQ Meteor 40cm","posId":"106","price":30900,"isExtra":false},{"id":"57081101","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"59555792","note":"","count":1,"label":"Rajčatový základ","posId":"ZBR40","price":0,"isExtra":true},{"id":"57081142","note":"","count":1,"label":"okraj mozzarella, bbq omáčka","posId":"A124","price":6500,"isExtra":true},{"id":"57081130","note":"","count":1,"label":"Jalapeňos","posId":"C102","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"57081032","note":"","size":"Hawai 40cm","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"57081101","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"57081099","note":"","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true},{"id":"57081204","note":"","count":1,"label":"Kukuřice","posId":"C115","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"57081212","note":"","count":1,"label":"Mozzarella","posId":"C113","price":4000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"57081230","note":"","count":1,"label":"Kuře","posId":"C114","price":4000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"57405790","note":"","size":"Pepsi 1l","count":1,"label":"Pepsi 1l","posId":"N124","price":5900,"isExtra":false},{"id":"59555779","note":"","size":"Choco Rolls","count":1,"label":"Choco Rolls","posId":"chr100","price":8900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59809071","note":"","size":"Jablečno-skořicové rolls","count":1,"label":"Jablečno-skořicové rolls","posId":"18","price":8900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59278384","note":"","size":"Spicy Wings 🌶️","count":1,"label":"Spicy Wings 🌶️","posId":"P101","price":11900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
+    <t>2026-04-06T11:53:59.673+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:20:03.902+02:00</t>
+    <t>[{"id":"62240209","note":"","size":"Baby Špenát &amp; kuře 32cm","count":1,"label":"Baby Špenát &amp; kuře 32cm","posId":"116","price":25900,"isExtra":false},{"id":"62240274","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"62240418","note":"","count":1,"label":"Rajčatový základ","posId":"ZSR32","price":0,"isExtra":true},{"id":"62240310","note":"","count":1,"label":"Bez špenátu s česnekem","posId":"X107","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"62240351","note":"","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
   </si>
   <si>
-    <t>2026-04-11T21:28:10.861+02:00</t>
+    <t>2026-04-06T11:44:03.741+02:00</t>
   </si>
   <si>
-    <t>ready_pickup</t>
+    <t>2026-04-06T11:52:45.294+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:08:06.650+02:00</t>
+    <t>2026-04-06T12:00:51.992+02:00</t>
   </si>
   <si>
-    <t>2026-04-11T21:19:11.513+02:00</t>
+    <t>2026-04-06T11:46:00.567+02:00</t>
   </si>
   <si>
-    <t>[{"id":"59809071","note":"","size":"Jablečno-skořicové rolls","count":1,"label":"Jablečno-skořicové rolls","posId":"18","price":8900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59610967","note":"","size":"Comeback 32cm 🌶️","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"57081202","note":"","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"59610968","note":"","size":"Pepperoni 32cm 🌶️🌶️","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"57094169","note":"","count":1,"label":"Smetanový základ","posId":"ZRS32","price":0,"isExtra":true},{"id":"57081105","note":"","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true},{"id":"57081202","note":"","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:59:04.085+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T21:10:28.087+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T21:38:02.809+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T21:00:49.330+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"85dc195f-7d7b-4fb5-b41d-eb1c9c76b3a3","note":"","count":1,"label":"Hot &amp; Spicy 32 cm","posId":"146","price":24900,"isExtra":false},{"id":"b3008ec8-24a5-4d30-bf46-9133028be7e4","note":"","count":1,"label":"Margherita 32 cm","posId":"136","price":20900,"isExtra":false},{"id":"3a8b6a85-3b5c-4ee4-be2d-261ab8731d6e","note":"","count":2,"label":"Dip česnekový","posId":"P106","price":2000,"isExtra":false},{"id":"96b5d091-fc97-4d1a-8602-51839892aa23","note":"","count":1,"label":"Dip jalapenos","posId":"P107","price":2000,"isExtra":false}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:57:49.911+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T21:08:18.389+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc23","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69400db90dc626f6c3c3fc5d","count":2,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69400db90dc626f6c3c3fc2d","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69bfb59f31761dcca50839dc","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:57:23.419+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T21:06:09.536+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc23","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"695458c28103d4672f51abc9","count":1,"label":"Mozzarella","posId":"B113","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"69400db90dc626f6c3c3fc1d","count":1,"label":"Quattro Formaggi 32cm","posId":"123","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"684ae9784182d05e5daecac2","count":1,"label":"Bez gorgonzoly","posId":"X101","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"695458c28103d4672f51abc8","count":1,"label":"Špenát s česnekem","posId":"B107","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"69400db90dc626f6c3c3fc5d","count":2,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":2,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:57:04.041+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T21:03:13.208+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"e8f571e6-dd36-42d7-8826-52c90315986b","note":"","count":1,"label":"Baby špenát &amp; kuře 40 cm","posId":"104","price":30900,"isExtra":false},{"id":"f61b7339-3b20-4583-b2b8-12e48de2876d","note":"","count":1,"label":"změna na Rajčatový základ","posId":"f61b7339-3b20-4583-b2b8-12e48de2876d","price":0,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:46:34.659+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:59:45.408+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:59:45.407+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"57081025","note":"","size":"Hot &amp; Spicy 40cm 🌶️🌶️","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":30900,"isExtra":false},{"id":"57081101","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"57081135","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"57081033","note":"","size":"Capricciosa 40cm","count":1,"label":"Capricciosa 40cm","posId":"101","price":30900,"isExtra":false},{"id":"57081101","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"57081135","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"57081163","note":"","count":1,"label":"Bez oliv","posId":"X112","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"57081216","note":"","count":1,"label":"Šunka","posId":"C106","price":4000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:46:09.215+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:56:27.365+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc2d","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69bfb59f31761dcca50839db","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true},{"id":"69400db90dc626f6c3c3fc25","count":1,"label":"BBQ Texas 32cm","posId":"119","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69bfb59f31761dcca50839db","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true},{"id":"69400db90dc626f6c3c3fc2b","count":1,"label":"Hawai 32cm","posId":"114","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69bfb59f31761dcca50839db","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:42:02.989+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:52:54.092+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"8c704055-e242-493d-b754-bb711e5a6c0b","note":"","count":1,"label":"Hawai 40 cm","posId":"102","price":30900,"isExtra":false},{"id":"eb426525-9181-4714-9963-380f5c0ae0e5","note":"","count":1,"label":"Okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"007c7303-045c-4866-882d-38e13564ff34","note":"","count":1,"label":"BEZ -ananas","posId":"X100","price":0,"KDSTags":["redhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:38:35.570+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:48:24.458+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc09","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"69bfb59f31761dcca50835ec","count":1,"label":"okraj mozzarella, bbq omáčka","posId":"A124","price":6500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:30:21.981+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:40:24.398+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc0b","count":1,"label":"BBQ Texas 40cm","posId":"107","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"674840e52b930230e954cfa0","count":1,"label":"Smetanový základ","posId":"ZBS40","price":0,"isExtra":true},{"id":"69bfb59f31761dcca50835eb","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"695458c28103d4672f51a9ec","count":1,"label":"Kuře","posId":"C114","price":4000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:21:44.396+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:33:00.243+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc05","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"69400db90dc626f6c3c3fc0d","count":1,"label":"BBQ Meteor 40cm","posId":"106","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"674840e52b930230e954cf9f","count":1,"label":"Rajčatový základ","posId":"ZBR40","price":0,"isExtra":true},{"id":"69bfb59f31761dcca50835eb","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:11:44.996+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:19:27.226+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc03","count":1,"label":"Quattro Formaggi 40cm","posId":"111","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"69bfb59f31761dcca50835ea","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:03:13.787+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:11:17.227+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc11","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:02:58.946+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T20:12:40.066+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"f30f2fb2-fb95-4178-8ce0-1adad0595bf2","count":1,"label":"Pizza Margherita 40","posId":"100","price":26900,"isExtra":false,"creatorId":"vLflJnpVpNGLwvefRJQ52","isPackging":0,"actualLabel":"Pizza Margherita 40"}]</t>
-  </si>
-  <si>
-    <t>Erik</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:33:29.541+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:50:55.636+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"104","note":"","count":1,"label":"Baby špenát &amp; kuře 40cm","posId":"104","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"A122","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"C105","note":"","count":1,"label":"Žampiony","posId":"C105","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"C108","note":"","count":1,"label":"Slanina","posId":"C108","price":4000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"119","note":"","count":1,"label":"BBQ Texas 32cm","posId":"119","price":24900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"17","note":"","count":1,"label":"USA těsto","posId":"17","price":1000,"isExtra":true},{"id":"A123","note":"","count":1,"label":"okraj mozzarella, bbq omáčka","posId":"A123","price":5700,"isExtra":true},{"id":"X111","note":"","count":1,"label":"Bez papriky","posId":"X111","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"X103","note":"","count":1,"label":"Bez cibule","posId":"X103","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"B106","note":"","count":1,"label":"Šunka","posId":"B106","price":3000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:33:17.015+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:44:30.044+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"57081030","note":"","size":"Baby špenát &amp; kuře 40cm","count":2,"label":"Baby špenát &amp; kuře 40cm","posId":"104","price":30900,"isExtra":false},{"id":"57081101","note":"","count":2,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:29:13.399+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:40:40.284+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc21","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69400db90dc626f6c3c3fc21","count":1,"label":"Comeback 32cm 🌶️","posId":"121","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"695458c28103d4672f51abc2","count":1,"label":"Žampiony","posId":"B105","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"69400db90dc626f6c3c3fc23","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>Omadbek</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:17:08.440+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:29:28.121+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"P101","note":"","count":1,"label":"Spicy Wings 🌶️","posId":"P101","price":11900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"118","note":"","count":1,"label":"BBQ Meteor 32cm","posId":"118","price":24900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"17","note":"","count":1,"label":"USA těsto","posId":"17","price":1000,"isExtra":true},{"id":"A123","note":"","count":1,"label":"okraj mozzarella, bbq omáčka","posId":"A123","price":5700,"isExtra":true},{"id":"P106","note":"","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:15:42.764+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:23:52.757+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:23:52.756+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc1b","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"6977bf4da1da98ea63c3a718","count":1,"label":"USA těsto","posId":"17","price":1000,"isExtra":true},{"id":"69400db90dc626f6c3c3fc2f","count":1,"label":"Baby Špenát &amp; kuře 32cm","posId":"116","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"6977bf4da1da98ea63c3a718","count":1,"label":"USA těsto","posId":"17","price":1000,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:13:21.837+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:19:52.725+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc2b","count":1,"label":"Hawai 32cm","posId":"114","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:05:22.017+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:14:27.301+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc07","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:03:44.403+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:13:22.349+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"100","note":"","count":1,"label":"Margherita 40cm","posId":"100","price":26900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"X1000","note":"","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true},{"id":"C106","note":"","count":1,"label":"Šunka","posId":"C106","price":4000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:53:10.038+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:02:23.257+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"57081026","note":"","size":"Comeback 40cm 🌶️","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"57081101","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"57081135","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:46:36.890+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:55:28.585+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc09","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"69bfb59f31761dcca50835eb","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"69400db90dc626f6c3c3fc5d","count":1,"label":"Česnekový dip","posId":"P106","price":2000,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:45:55.890+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:53:06.379+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"59610973","note":"","size":"Capricciosa 32cm","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"57081140","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true},{"id":"57081163","note":"","count":1,"label":"Bez oliv","posId":"X112","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"57081234","note":"","count":1,"label":"Grana padano, pecorino, parmazán","posId":"B130","price":3000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:40:04.043+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:52:00.111+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T19:07:21.721+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:41:38.173+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"603b435c-3b64-461f-97f3-c365eb50fd2a","note":"","count":1,"label":"Sweet passion 18 cm","posId":"30","price":11900,"isExtra":false},{"id":"ff8bc446-e047-44f1-bae5-423b565e0123","note":"","count":1,"label":"Capricciosa 32 cm","posId":"137","price":24900,"isExtra":false},{"id":"21fd0686-e8d1-43f1-84c9-d96f5842a3ca","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A121","price":5700,"isExtra":true},{"id":"bd8e2f82-3d11-4ada-88ad-67191c012d18","note":"","count":1,"label":"BEZ -olivy","posId":"X112","price":0,"KDSTags":["redhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:36:28.327+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:42:11.063+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"a902d94b-4667-4702-ad71-4744adfe8fad","count":1,"label":"Pizza Quattro Formaggi 32","posId":"123","price":24900,"isExtra":false,"creatorId":"yLEa_cXWJHbx5yM8oySov","isPackging":0,"actualLabel":"Pizza Quattro Formaggi 32"}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:31:32.626+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:39:28.381+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"57081023","note":"","size":"Margherita 40cm","count":1,"label":"Margherita 40cm","posId":"100","price":26900,"isExtra":false},{"id":"57081101","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"57081135","note":"","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"57081152","note":"","count":1,"label":"Žampiony","posId":"C105","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"57081204","note":"","count":1,"label":"Kukuřice","posId":"C115","price":3500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"57081216","note":"","count":1,"label":"Šunka","posId":"C106","price":4000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"57405791","note":"","size":"Pepsi zero sugar 1l","count":1,"label":"Pepsi zero sugar 1l","posId":"N125","price":5900,"isExtra":false}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:17:30.085+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:27:51.243+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"59610973","note":"","size":"Capricciosa 32cm","count":1,"label":"Capricciosa 32cm","posId":"113","price":24900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"59610964","note":"","size":"Margherita 32cm","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:02:08.745+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:11:34.196+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:00:07.967+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:10:56.377+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"59610964","note":"","size":"Margherita 32cm","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"57081111","note":"","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"57081105","note":"","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true},{"id":"57081202","note":"","count":1,"label":"Kukuřice","posId":"B115","price":2500,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"57081219","note":"","count":1,"label":"Šunka","posId":"B106","price":3000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:58:04.213+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:10:12.307+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:14:39.056+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:58:21.729+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"8c704055-e242-493d-b754-bb711e5a6c0b","note":"","count":1,"label":"Hawai 40 cm","posId":"102","price":30900,"isExtra":false},{"id":"eb426525-9181-4714-9963-380f5c0ae0e5","note":"","count":1,"label":"Okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"1e281388-c78a-4b3d-874d-346d699d1a35","note":"","count":1,"label":"Grana padano","posId":"C130","price":4000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"007c7303-045c-4866-882d-38e13564ff34","note":"","count":1,"label":"BEZ -ananas","posId":"X100","price":0,"KDSTags":["redhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:49:14.407+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:55:18.202+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"faba40d0-295e-4d0a-bb09-2edf9b61a61a","count":1,"label":"Pizza Hawai 40 cm","posId":"102","price":30900,"isExtra":false,"creatorId":"upGpHqpnMTYV9s0oq_2gD","isPackging":0,"actualLabel":"Pizza Hawai 40 cm"}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:49:03.314+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:58:24.979+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T18:15:04.513+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:49:54.613+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"0b867b16-3995-4b4a-9deb-1c0d8cecf8d6","note":"","count":1,"label":"Pepperoni 32 cm","posId":"120","price":24900,"isExtra":false},{"id":"35e045f9-bc36-46e9-8142-6579de78a05b","note":"","count":1,"label":"Comeback 32 cm","posId":"121","price":24900,"isExtra":false}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:32:03.611+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:43:33.927+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"35e045f9-bc36-46e9-8142-6579de78a05b","note":"","count":1,"label":"Comeback 32 cm","posId":"121","price":24900,"isExtra":false},{"id":"adb25a98-2836-4da5-82f5-82c3fc24d621","note":"","count":1,"label":"grana padano","posId":"B130","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"99710cd8-fa1f-4712-84a8-85da37e18dd0","note":"","count":1,"label":"Česnekový chléb","posId":"P104","price":7900,"isExtra":false}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:31:17.678+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:40:07.377+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc09","count":1,"label":"Pepperoni 40cm 🌶️🌶️","posId":"108","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"69400db90dc626f6c3c3fc11","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"695458c28103d4672f51a9ea","count":1,"label":"Slanina","posId":"C108","price":4000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:12:24.612+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:21:11.091+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"57081032","note":"","size":"Hawai 40cm","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"57081101","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"57405791","note":"","size":"Pepsi zero sugar 1l","count":1,"label":"Pepsi zero sugar 1l","posId":"N125","price":5900,"isExtra":false}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:10:06.041+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T17:22:58.069+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc07","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"69bfb59f31761dcca50835eb","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"69400db90dc626f6c3c3fc55","count":1,"label":"Masové kuličky","posId":"P102","price":9900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69400db90dc626f6c3c3fc5b","count":1,"label":"Pepperoni Rolls 🌶️","posId":"P100","price":8900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T16:32:13.750+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T16:41:44.105+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T16:26:07.103+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T16:37:19.332+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc1b","count":1,"label":"Margherita 32cm","posId":"112","price":20900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"69bfb59f31761dcca50839de","count":1,"label":"okraj hotdog, hořčice","posId":"A117","price":5700,"isExtra":true},{"id":"695458c28103d4672f51abca","count":1,"label":"Šunka","posId":"B106","price":3000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T16:05:21.894+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T16:16:59.126+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc0b","count":1,"label":"BBQ Texas 40cm","posId":"107","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"69bfb59f31761dcca50835ec","count":1,"label":"okraj mozzarella, bbq omáčka","posId":"A124","price":6500,"isExtra":true},{"id":"684ae9784182d05e5daecb41","count":1,"label":"Bez papriky","posId":"X111","price":0,"KDSTags":["redhighlight"],"isExtra":true},{"id":"695458c28103d4672f51a9e6","count":1,"label":"Kukuřice","posId":"C115","price":3500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>Mykola</t>
-  </si>
-  <si>
-    <t>2026-04-11T15:53:53.546+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T16:01:31.133+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"102","note":"","count":1,"label":"Hawai 40cm","posId":"102","price":30900,"isExtra":false},{"id":"K0000","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"ZRS40","note":"","count":1,"label":"Smetanový základ","posId":"ZRS40","price":0,"isExtra":true},{"id":"C100","note":"","count":1,"label":"Ananas","posId":"C100","price":3500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T15:35:04.033+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T15:55:14.023+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc07","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"695458c28103d4672f51a9e6","count":1,"label":"Kukuřice","posId":"C115","price":3500,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T15:05:50.892+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T15:15:56.907+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc0d","count":1,"label":"BBQ Meteor 40cm","posId":"106","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"69bfb59f31761dcca50835eb","count":1,"label":"okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T14:47:07.699+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T14:55:14.954+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc13","count":1,"label":"Capricciosa 40cm","posId":"101","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"674840e52b930230e954cea6","count":1,"label":"Smetanový základ","posId":"ZRS40","price":0,"isExtra":true},{"id":"69bfb59f31761dcca50835ea","count":1,"label":"bez plněných okrajů","posId":"X1000","price":0,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T14:43:00.269+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T14:52:21.649+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"3d349fca-a560-44e4-966f-e75699784d8e","count":1,"label":"Pizza Comeback 40","posId":"109","price":30900,"isExtra":false,"creatorId":"LX9oinMJmWYV6_7VF_Y1Q","isPackging":0,"actualLabel":"Pizza Comeback 40"}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T12:48:06.046+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T12:59:56.602+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc03","count":1,"label":"Quattro Formaggi 40cm","posId":"111","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"695458c28103d4672f51a9ea","count":1,"label":"Slanina","posId":"C108","price":4000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T12:29:12.704+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T12:43:39.233+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"a902d94b-4667-4702-ad71-4744adfe8fad","count":1,"label":"Pizza Quattro Formaggi 32","posId":"123","price":24900,"isExtra":false,"creatorId":"-n0yBAbJ4tJCJ7_B8ppzQ","isPackging":0,"actualLabel":"Pizza Quattro Formaggi 32"},{"id":"31c0dfca-6f85-4bc6-9421-409b4483b607","count":1,"label":"Pizza Pepperoni 32","posId":"120","price":24900,"isExtra":false,"creatorId":"6Il0T12Kvu-RWQFhAuObH","isPackging":0,"actualLabel":"Pizza Pepperoni 32"},{"id":"97205e8a-60b5-439e-8af0-7f8def52aeb6","count":1,"label":"Pizza Hawai 32 cm","posId":"114","price":24900,"isExtra":false,"creatorId":"X3rOfPOsoaMdA2TEf6SUb","isPackging":0,"actualLabel":"Pizza Hawai 32 cm"},{"id":"cd7798b9-deb2-4229-a68e-ebefba7ee9e4","count":1,"label":"Pizza Comeback 32","posId":"121","price":24900,"isExtra":false,"creatorId":"H99clsTfDUL_xpBi47XBw","isPackging":0,"actualLabel":"Pizza Comeback 32"}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T12:21:22.086+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T12:31:55.340+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"31cc2dec-1acd-4403-88c1-9561117576d8","count":1,"label":"Pizza Špenát kuře 40 cm","posId":"104","price":30900,"isExtra":false,"creatorId":"ofKJotOzqVkVLPN7VbHt3","isPackging":0,"actualLabel":"Pizza Špenát kuře 40 cm"},{"id":"2258641d-2e03-4608-b20f-749a219f4c12","count":1,"label":"Pizza BBQ Texas 32","posId":"119","price":24900,"isExtra":false,"creatorId":"0fQfH5AG6yrlgTepf8-qO","isPackging":0,"actualLabel":"Pizza BBQ Texas 32"}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T12:19:15.259+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T12:26:38.232+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"a902d94b-4667-4702-ad71-4744adfe8fad","count":1,"label":"Pizza Quattro Formaggi 32","posId":"123","price":24900,"isExtra":false,"creatorId":"Q42Bh8Xhzc6k3ysNEWyk-","isPackging":0,"actualLabel":"Pizza Quattro Formaggi 32"},{"id":"31c0dfca-6f85-4bc6-9421-409b4483b607","count":1,"label":"Pizza Pepperoni 32","posId":"120","price":24900,"isExtra":false,"creatorId":"x_PKngZSHSXB8Jdc92gtS","isPackging":0,"actualLabel":"Pizza Pepperoni 32"}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:33:02.747+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:46:31.187+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T12:03:55.190+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:37:31.361+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"03dae282-4cd4-4fa2-9169-2178ea3ed325","note":"","count":1,"label":"Quattro Formaggi 40 cm","posId":"111","price":30900,"isExtra":false},{"id":"5b1f2843-926a-4dd1-a5f0-4fddc7b45013","note":"","count":1,"label":"Margherita 32 cm","posId":"112","price":20900,"isExtra":false},{"id":"38de8e38-e51e-422d-9a89-960ebc505f1b","note":"","count":1,"label":"šunka","posId":"B106","price":3000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"0b867b16-3995-4b4a-9deb-1c0d8cecf8d6","note":"","count":1,"label":"Pepperoni 32 cm","posId":"120","price":24900,"isExtra":false}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:29:25.413+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:41:50.263+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc07","count":1,"label":"Comeback 40cm 🌶️","posId":"109","price":30900,"isExtra":false},{"id":"01f1f771ad243e9a3e1e67cc","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true},{"id":"674840e52b930230e954cea6","count":1,"label":"Smetanový základ","posId":"ZRS40","price":0,"isExtra":true},{"id":"69bfb59f31761dcca50835ee","count":1,"label":"okraj hotdog, bbq omáčka","posId":"A120","price":6500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:22:22.510+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:28:55.319+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"57081025","note":"","size":"Hot &amp; Spicy 40cm 🌶️🌶️","count":1,"label":"Hot &amp; Spicy 40cm 🌶️🌶️","posId":"110","price":30900,"isExtra":false},{"id":"57081101","note":"","count":1,"label":"Balné","posId":"K0000","price":2000,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:21:52.879+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:28:30.247+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc23","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true},{"id":"6977bf4da1da98ea63c3a718","count":1,"label":"USA těsto","posId":"17","price":1000,"isExtra":true},{"id":"69400db90dc626f6c3c3fc7b","count":1,"label":"Mirinda 1l","posId":"N126","price":5900,"isExtra":false}]</t>
-  </si>
-  <si>
-    <t>Kačena Stanislav</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:14:03.262+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:26:14.973+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:35:20.909+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:14:03.764+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"35e045f9-bc36-46e9-8142-6579de78a05b","note":"","count":1,"label":"Comeback 32 cm","posId":"121","price":24900,"isExtra":false},{"id":"e12521cc-9391-4513-be27-f090014536cf","note":"","count":1,"label":"BBQ Texas 32 cm","posId":"143","price":24900,"isExtra":false}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:01:36.866+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:08:55.154+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"69400db90dc626f6c3c3fc23","count":1,"label":"Pepperoni 32cm 🌶️🌶️","posId":"120","price":24900,"isExtra":false},{"id":"0828382bbc0f39abdadd9b99","count":1,"label":"Balné","posId":"K0000","price":1500,"isExtra":true}]</t>
-  </si>
-  <si>
-    <t>2026-04-11T10:54:02.650+02:00</t>
-  </si>
-  <si>
-    <t>2026-04-11T11:06:36.266+02:00</t>
-  </si>
-  <si>
-    <t>[{"id":"8c704055-e242-493d-b754-bb711e5a6c0b","note":"","count":1,"label":"Hawai 40 cm","posId":"102","price":30900,"isExtra":false},{"id":"eb426525-9181-4714-9963-380f5c0ae0e5","note":"","count":1,"label":"Okraj mozzarella, bylinky","posId":"A122","price":6500,"isExtra":true},{"id":"ed9751e1-1886-4b0f-b8dd-d3c6488dfd29","note":"","count":1,"label":"Mozzarella","posId":"C113","price":4000,"KDSTags":["greenhighlight"],"isExtra":true},{"id":"f315e3ea-4d99-415a-ab21-4d8aa27beec9","note":"","count":1,"label":"Kuře","posId":"C114","price":4000,"KDSTags":["greenhighlight"],"isExtra":true}]</t>
+    <t>[{"id":"e8f571e6-dd36-42d7-8826-52c90315986b","note":"","count":1,"label":"Baby špenát &amp; kuře 40 cm","posId":"104","price":32900,"isExtra":false}]</t>
   </si>
   <si>
     <t>Název</t>
@@ -1358,16 +698,13 @@
     <t>Ahurieva Viktoriia</t>
   </si>
   <si>
-    <t>01:00</t>
-  </si>
-  <si>
     <t>12:00</t>
   </si>
   <si>
     <t>Ondřej Navrátil</t>
   </si>
   <si>
-    <t>11:00</t>
+    <t>18:00</t>
   </si>
   <si>
     <t>07:00</t>
@@ -1380,6 +717,9 @@
   </si>
   <si>
     <t>06:00</t>
+  </si>
+  <si>
+    <t>Pešová Hana</t>
   </si>
   <si>
     <t>08:00</t>
@@ -3268,7 +2608,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="4">
-        <v>46123.0</v>
+        <v>46118.0</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="6" t="s">
@@ -3293,13 +2633,13 @@
       <c r="D2" s="12"/>
       <c r="E2" s="13"/>
       <c r="F2" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IF(I2&gt;0, 100 / (I2 / 112 * 100 / ((SUM(A12:A21, A25:A31) + (M17 + I32) + IFERROR(SUM(FILTER(HR!W5:W48, LEN(HR!A5:A48) &gt; 0)), 0)) / 100)), ""Zadej tržbu"")"),0.340836981123415)</f>
-        <v>0.3408369811</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IF(I2&gt;0, 100 / (I2 / 112 * 100 / ((SUM(A12:A21, A25:A31) + (M17 + I32) + IFERROR(SUM(FILTER(HR!W5:W48, LEN(HR!A5:A48) &gt; 0)), 0)) / 100)), ""Zadej tržbu"")"),1.207404622675621)</f>
+        <v>1.207404623</v>
       </c>
       <c r="H2" s="15"/>
       <c r="I2" s="16">
         <f>SUM(RestiaCSV!C:C) - SUMIFS(RestiaCSV!C:C, RestiaCSV!B:B, "canceled")</f>
-        <v>43572.5</v>
+        <v>6691</v>
       </c>
       <c r="K2" s="15"/>
       <c r="L2" s="17" t="s">
@@ -3307,14 +2647,14 @@
       </c>
       <c r="M2" s="18">
         <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!A:A, Report!L2, RestiaCSV!B:B, "&lt;&gt;canceled")</f>
-        <v>17084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1"/>
       <c r="B3" s="19" t="str">
         <f>CHOOSE(WEEKDAY(D1), "Neděle", "Pondělí", "Úterý", "Středa", "Čtvrtek", "Pátek", "Sobota")</f>
-        <v>Sobota</v>
+        <v>Pondělí</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -3326,7 +2666,7 @@
       </c>
       <c r="M3" s="18">
         <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!A:A, Report!L3, RestiaCSV!B:B, "&lt;&gt;canceled")</f>
-        <v>7401</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="4">
@@ -3346,7 +2686,7 @@
       </c>
       <c r="M4" s="18">
         <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!A:A, "damejidlo", RestiaCSV!G:G, "online", RestiaCSV!B:B, "&lt;&gt;canceled")</f>
-        <v>8208</v>
+        <v>950</v>
       </c>
     </row>
     <row r="5">
@@ -3368,7 +2708,7 @@
       </c>
       <c r="M5" s="18">
         <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!A:A, "generic", RestiaCSV!G:G, "online", RestiaCSV!B:B, "&lt;&gt;canceled") </f>
-        <v>5273</v>
+        <v>591</v>
       </c>
     </row>
     <row r="6">
@@ -3405,7 +2745,7 @@
       </c>
       <c r="M7" s="28">
         <f>SUMIFS(RestiaCSV!C:C, RestiaCSV!A:A, "damejidlo", RestiaCSV!G:G, "cash", RestiaCSV!B:B, "&lt;&gt;canceled") </f>
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8">
@@ -3435,7 +2775,7 @@
         <v>13</v>
       </c>
       <c r="M9" s="31">
-        <v>3726.0</v>
+        <v>1399.0</v>
       </c>
     </row>
     <row r="10">
@@ -3481,20 +2821,20 @@
       <c r="I11" s="15"/>
       <c r="J11" s="40">
         <f>M2+M3+M4+M5+M6+M13+M14+M15+M16+M17+M9+M10+M11-I2</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="41" t="s">
         <v>12</v>
       </c>
       <c r="M11" s="31">
-        <v>1881.0</v>
+        <v>1822.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="42">
         <f t="array" ref="A12">IF(ISBLANK(B12), 0, IF(ISNUMBER(MATCH(B12, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B12, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B12, HR!B:B, 0)) * (F12 * 24), 0)))</f>
-        <v>2126.751</v>
+        <v>1751.442</v>
       </c>
       <c r="B12" s="43" t="s">
         <v>23</v>
@@ -3509,7 +2849,7 @@
       <c r="F12" s="46" t="str">
         <f t="shared" ref="F12:F21" si="1">IF(OR(ISBLANK(B12), ISBLANK(D12), D12=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))+1, TIMEVALUE(IF(ISBLANK(D12), "00:00", D12))) - TIMEVALUE(IF(ISBLANK(C12), "00:00", C12)) - TIMEVALUE(IF(ISBLANK(E12), "00:00", E12))), "hh:mm"))
 </f>
-        <v>08:30</v>
+        <v>07:00</v>
       </c>
       <c r="I12" s="15"/>
       <c r="J12" s="29"/>
@@ -3522,7 +2862,7 @@
     <row r="13">
       <c r="A13" s="42">
         <f t="array" ref="A13">IF(ISBLANK(B13), 0, IF(ISNUMBER(MATCH(B13, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B13, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B13, HR!B:B, 0)) * (F13 * 24), 0)))</f>
-        <v>3582.495</v>
+        <v>0</v>
       </c>
       <c r="B13" s="48" t="s">
         <v>27</v>
@@ -3536,7 +2876,7 @@
       <c r="E13" s="49"/>
       <c r="F13" s="46" t="str">
         <f t="shared" si="1"/>
-        <v>10:30</v>
+        <v>08:00</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
@@ -3551,28 +2891,28 @@
     <row r="14">
       <c r="A14" s="42">
         <f t="array" ref="A14">IF(ISBLANK(B14), 0, IF(ISNUMBER(MATCH(B14, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B14, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B14, HR!B:B, 0)) * (F14 * 24), 0)))</f>
-        <v>1251.03</v>
+        <v>0</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="44" t="s">
         <v>32</v>
-      </c>
-      <c r="D14" s="44" t="s">
-        <v>33</v>
       </c>
       <c r="E14" s="45"/>
       <c r="F14" s="52" t="str">
         <f t="shared" si="1"/>
-        <v>05:00</v>
+        <v>08:00</v>
       </c>
       <c r="G14" s="53"/>
       <c r="I14" s="15"/>
       <c r="J14" s="29"/>
       <c r="K14" s="15"/>
       <c r="L14" s="54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M14" s="50"/>
     </row>
@@ -3593,7 +2933,7 @@
       <c r="J15" s="29"/>
       <c r="K15" s="15"/>
       <c r="L15" s="54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M15" s="50"/>
     </row>
@@ -3614,9 +2954,11 @@
       <c r="J16" s="29"/>
       <c r="K16" s="15"/>
       <c r="L16" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="M16" s="50"/>
+        <v>35</v>
+      </c>
+      <c r="M16" s="50">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="42">
@@ -3637,11 +2979,11 @@
       <c r="J17" s="12"/>
       <c r="K17" s="13"/>
       <c r="L17" s="57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M17" s="58">
         <f>SUM(I25:I31)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" ht="21.75" customHeight="1">
@@ -3658,7 +3000,7 @@
         <v>0:00</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="13"/>
@@ -3678,9 +3020,7 @@
         <f t="shared" si="1"/>
         <v>0:00</v>
       </c>
-      <c r="G19" s="39" t="s">
-        <v>27</v>
-      </c>
+      <c r="G19" s="39"/>
       <c r="I19" s="15"/>
       <c r="M19" s="62"/>
     </row>
@@ -3729,22 +3069,22 @@
       <c r="H22" s="21"/>
       <c r="I22" s="13"/>
       <c r="J22" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="K22" s="71" t="s">
+      <c r="L22" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="L22" s="72" t="s">
+      <c r="M22" s="72" t="s">
         <v>41</v>
-      </c>
-      <c r="M22" s="72" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="69"/>
       <c r="B23" s="32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I23" s="15"/>
       <c r="J23" s="73">
@@ -3757,12 +3097,12 @@
       </c>
       <c r="L23" s="75">
         <f>COUNTIFS(RestiaCSV!L:L, "&gt;5", RestiaCSV!F:F, "delivery")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" s="73" t="str">
         <f>INT(AVERAGE(RestiaCSV!N2:N32)) &amp; " min " &amp; TEXT(MOD(AVERAGE(RestiaCSV!N2:N32) * 60, 60), "00") &amp; " s"
 </f>
-        <v>11 min 19 s</v>
+        <v>9 min 35 s</v>
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1">
@@ -3783,49 +3123,57 @@
         <v>22</v>
       </c>
       <c r="G24" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="76" t="s">
+      <c r="I24" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="I24" s="77" t="s">
+      <c r="J24" s="78" t="s">
         <v>46</v>
       </c>
-      <c r="J24" s="78" t="s">
+      <c r="K24" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="K24" s="79" t="s">
+      <c r="L24" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="L24" s="78" t="s">
+      <c r="M24" s="79" t="s">
         <v>49</v>
-      </c>
-      <c r="M24" s="79" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="42">
         <f t="array" ref="A25">IF(ISBLANK(B25), 0, IF(ISNUMBER(MATCH(B25, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B25, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B25, HR!B:B, 0)) * (F25 * 24), 0)))</f>
-        <v>0</v>
-      </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
+        <v>1284.48</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>25</v>
+      </c>
       <c r="E25" s="80"/>
       <c r="F25" s="46" t="str">
         <f t="shared" ref="F25:F31" si="2">IF(OR(ISBLANK(B25), ISBLANK(D25), D25=0), "0:00", TEXT((IF(AND(TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))&gt;=TIMEVALUE("00:00"), TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))&lt;=TIMEVALUE("06:00")), TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))+1, TIMEVALUE(IF(ISBLANK(D25), "00:00", D25))) - TIMEVALUE(IF(ISBLANK(C25), "00:00", C25)) - TIMEVALUE(IF(ISBLANK(E25), "00:00", E25))), "hh:mm"))
 </f>
-        <v>0:00</v>
+        <v>06:00</v>
       </c>
       <c r="G25" s="81">
         <f>COUNTIF(RestiaCSV!E:E, B25)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="82"/>
+        <v>1</v>
+      </c>
+      <c r="H25" s="82" t="b">
+        <v>1</v>
+      </c>
       <c r="I25" s="83">
         <f t="shared" ref="I25:I31" si="3">IF(H25,G25*40, 0)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J25" s="84"/>
       <c r="K25" s="84"/>
@@ -3835,36 +3183,44 @@
     <row r="26">
       <c r="A26" s="42">
         <f t="array" ref="A26">IF(ISBLANK(B26), 0, IF(ISNUMBER(MATCH(B26, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B26, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B26, HR!B:B, 0)) * (F26 * 24), 0)))</f>
-        <v>0</v>
-      </c>
-      <c r="B26" s="85"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
+        <v>428.16</v>
+      </c>
+      <c r="B26" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>32</v>
+      </c>
       <c r="E26" s="86"/>
       <c r="F26" s="46" t="str">
         <f t="shared" si="2"/>
-        <v>0:00</v>
+        <v>02:00</v>
       </c>
       <c r="G26" s="81">
         <f>COUNTIF(RestiaCSV!E:E, B26)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="82"/>
+      <c r="H26" s="82" t="b">
+        <v>1</v>
+      </c>
       <c r="I26" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J26" s="88">
         <f>COUNTIF(I25:I31, "&gt;0")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" s="75">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("COUNTA(FILTER(RestiaCSV!B2:B32, RestiaCSV!B2:B32 &lt;&gt; ""canceled""))"),97.0)</f>
-        <v>97</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("COUNTA(FILTER(RestiaCSV!B2:B32, RestiaCSV!B2:B32 &lt;&gt; ""canceled""))"),30.0)</f>
+        <v>30</v>
       </c>
       <c r="L26" s="75">
         <f>COUNTIF(RestiaCSV!F1:F32, "delivery")</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M26" s="89">
         <f>COUNTIF(RestiaCSV!M:M, "&gt;5")</f>
@@ -3874,34 +3230,42 @@
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="42">
         <f t="array" ref="A27">IF(ISBLANK(B27), 0, IF(ISNUMBER(MATCH(B27, HR!A:A, 0)), 0, IF(ISNUMBER(MATCH(B27, HR!B:B, 0)), INDEX(HR!V:V, MATCH(B27, HR!B:B, 0)) * (F27 * 24), 0)))</f>
-        <v>0</v>
-      </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="90"/>
-      <c r="D27" s="91"/>
+        <v>840</v>
+      </c>
+      <c r="B27" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="90" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="91" t="s">
+        <v>52</v>
+      </c>
       <c r="E27" s="86"/>
       <c r="F27" s="52" t="str">
         <f t="shared" si="2"/>
-        <v>0:00</v>
+        <v>06:00</v>
       </c>
       <c r="G27" s="81">
         <f>COUNTIF(RestiaCSV!E:E, B27)</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="82"/>
+        <v>2</v>
+      </c>
+      <c r="H27" s="82" t="b">
+        <v>1</v>
+      </c>
       <c r="I27" s="87">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J27" s="92" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K27" s="93"/>
       <c r="L27" s="94" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M27" s="79" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
@@ -3955,16 +3319,16 @@
       </c>
       <c r="J29" s="98">
         <f>COUNTIFS(RestiaCSV!M:M, "&gt;5", RestiaCSV!L:L, "&gt;5")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="99"/>
       <c r="L29" s="100">
         <f>L23/L26</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M29" s="75">
         <f>COUNTIFS(RestiaCSV!L:L, "&gt;5", RestiaCSV!F:F, "delivery", RestiaCSV!E:E, "Wolt Kurýr")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3992,10 +3356,10 @@
       <c r="J30" s="102"/>
       <c r="K30" s="102"/>
       <c r="L30" s="103" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M30" s="103" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" ht="21.75" customHeight="1">
@@ -4028,34 +3392,34 @@
     <row r="32">
       <c r="A32" s="35"/>
       <c r="B32" s="109" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C32" s="110" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D32" s="21"/>
       <c r="E32" s="21"/>
       <c r="F32" s="111"/>
       <c r="G32" s="112">
         <f>COUNTIFS(RestiaCSV!E:E, "wolt kurýr", RestiaCSV!A:A, "&lt;&gt;wolt")</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H32" s="113" t="b">
         <v>1</v>
       </c>
       <c r="I32" s="114">
         <f>G32*127</f>
-        <v>1143</v>
+        <v>0</v>
       </c>
       <c r="J32" s="115"/>
       <c r="K32" s="115"/>
       <c r="L32" s="100">
         <f>100%-L29</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M32" s="100">
         <f>M29/L26</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4115,16 +3479,16 @@
   </conditionalFormatting>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="B25:B31">
-      <formula1>"Hanibal Filip,Mikuš Pavel,Šmídová Sabina,Kormash Liubov,Vychivskyi Volodymyr,Dvořák Radim,Hřebík Martin,Reischl Jan,Kináč Jozef,Bednařík Peter,Kulinič Michail,Čonka Ludovít,Kačena Stanislav,Novák Dalibor"</formula1>
+      <formula1>"Mikešová Adéla,Kaločai Rudolf,Vopatová Anna,Vopatová Šárka,Světlík František,Ženíšek Lukáš,Roth Stanislav st.,Irena Kovacsova"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B12:B21">
-      <formula1>"Nedbal Michal,Ahurieva Viktoriia,Pešová Hana,Šebesta Tomáš,Nováková Adéla,Makula Radek,Bušek Pavel,Putna Jaroslav,Kopic Jakub,Fáberová Kateřina"</formula1>
+      <formula1>"Rothová Anastasia,Roth Stanislav ml.,Raboch Tomáš,Kratochvíl Kryštof,Tůma Vladimír"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G11 G19">
+      <formula1>"Tůma Vladimír,Vostrý Daniel,Roth Stanislav ml."</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B1">
       <formula1>"Bolevec,Malešice,Prosek,Zličín,Libuš,Chodov,Výroba,Předloha"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G11 G19">
-      <formula1>"Mirga Simon,Yarushynskyi Vladyslav,Kopic Jakub"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
@@ -4152,13 +3516,13 @@
       <c r="A1" s="116"/>
       <c r="B1" s="117" t="str">
         <f>Report!B1</f>
-        <v>Prosek</v>
+        <v>Bolevec</v>
       </c>
       <c r="C1" s="118">
         <v>46028.0</v>
       </c>
       <c r="D1" s="119" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" s="120">
         <v>46028.0</v>
@@ -5268,13 +4632,13 @@
     <row r="5">
       <c r="A5" s="133"/>
       <c r="B5" s="134" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
       <c r="E5" s="5"/>
       <c r="F5" s="135" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G5" s="20"/>
       <c r="H5" s="20"/>
@@ -6109,7 +5473,7 @@
       <c r="D8" s="20"/>
       <c r="E8" s="5"/>
       <c r="F8" s="144" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G8" s="20"/>
       <c r="H8" s="20"/>
@@ -6387,7 +5751,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="149" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D9" s="149" t="s">
         <v>22</v>
@@ -6397,13 +5761,13 @@
         <v>18</v>
       </c>
       <c r="G9" s="149" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H9" s="149" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="151" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J9" s="152">
         <v>-1.0</v>
@@ -6678,7 +6042,7 @@
       <c r="C10" s="155"/>
       <c r="D10" s="155"/>
       <c r="E10" s="156" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F10" s="155"/>
       <c r="G10" s="155"/>
@@ -6954,7 +6318,7 @@
       <c r="C11" s="155"/>
       <c r="D11" s="155"/>
       <c r="E11" s="156" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="F11" s="155"/>
       <c r="G11" s="155"/>
@@ -7230,7 +6594,7 @@
       <c r="C12" s="155"/>
       <c r="D12" s="155"/>
       <c r="E12" s="156" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F12" s="155"/>
       <c r="G12" s="155"/>
@@ -7506,7 +6870,7 @@
       <c r="C13" s="155"/>
       <c r="D13" s="155"/>
       <c r="E13" s="156" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F13" s="155"/>
       <c r="G13" s="155"/>
@@ -7782,7 +7146,7 @@
       <c r="C14" s="155"/>
       <c r="D14" s="155"/>
       <c r="E14" s="156" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F14" s="155"/>
       <c r="G14" s="155"/>
@@ -7790,7 +7154,7 @@
       <c r="I14" s="155"/>
       <c r="K14" s="15"/>
       <c r="L14" s="159" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M14" s="132"/>
       <c r="N14" s="128"/>
@@ -8058,7 +7422,7 @@
       <c r="C15" s="155"/>
       <c r="D15" s="155"/>
       <c r="E15" s="156" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F15" s="155"/>
       <c r="G15" s="155"/>
@@ -8066,7 +7430,7 @@
       <c r="I15" s="155"/>
       <c r="K15" s="15"/>
       <c r="L15" s="159" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M15" s="126"/>
       <c r="N15" s="128"/>
@@ -8340,7 +7704,7 @@
       <c r="I16" s="155"/>
       <c r="K16" s="15"/>
       <c r="L16" s="159" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M16" s="132"/>
       <c r="N16" s="128"/>
@@ -8615,7 +7979,7 @@
       <c r="J17" s="21"/>
       <c r="K17" s="13"/>
       <c r="L17" s="161" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M17" s="132"/>
       <c r="N17" s="128"/>
@@ -9161,16 +8525,16 @@
       <c r="H19" s="155"/>
       <c r="I19" s="155"/>
       <c r="J19" s="164" t="s">
+        <v>38</v>
+      </c>
+      <c r="K19" s="165" t="s">
         <v>39</v>
       </c>
-      <c r="K19" s="165" t="s">
+      <c r="L19" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="L19" s="166" t="s">
+      <c r="M19" s="167" t="s">
         <v>41</v>
-      </c>
-      <c r="M19" s="167" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
@@ -9208,7 +8572,7 @@
         <v>2.0</v>
       </c>
       <c r="M21" s="173" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="N21" s="163"/>
       <c r="O21" s="163"/>
@@ -9480,16 +8844,16 @@
       <c r="H22" s="155"/>
       <c r="I22" s="155"/>
       <c r="J22" s="174" t="s">
+        <v>46</v>
+      </c>
+      <c r="K22" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="K22" s="175" t="s">
+      <c r="L22" s="176" t="s">
         <v>48</v>
       </c>
-      <c r="L22" s="176" t="s">
+      <c r="M22" s="177" t="s">
         <v>49</v>
-      </c>
-      <c r="M22" s="177" t="s">
-        <v>50</v>
       </c>
       <c r="N22" s="163"/>
       <c r="O22" s="163"/>
@@ -10315,14 +9679,14 @@
       <c r="H25" s="155"/>
       <c r="I25" s="155"/>
       <c r="J25" s="180" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K25" s="93"/>
       <c r="L25" s="176" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M25" s="177" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N25" s="163"/>
       <c r="O25" s="163"/>
@@ -11147,10 +10511,10 @@
       <c r="I28" s="155"/>
       <c r="J28" s="185"/>
       <c r="L28" s="175" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M28" s="177" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N28" s="163"/>
       <c r="O28" s="163"/>
@@ -12041,52 +11405,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="190" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B1" s="190" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C1" s="190" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D1" s="190" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E1" s="190" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F1" s="190" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G1" s="190" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H1" s="190" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I1" s="190" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J1" s="190" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K1" s="190" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L1" s="190" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M1" s="190" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N1" s="190" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O1" s="190" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P1" s="190" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q1" s="191"/>
       <c r="R1" s="191"/>
@@ -12107,48 +11471,52 @@
     </row>
     <row r="2">
       <c r="A2" s="190" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B2" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C2" s="190">
-        <v>373.0</v>
+        <v>259.0</v>
       </c>
       <c r="D2" s="190">
         <v>0.0</v>
       </c>
       <c r="E2" s="190" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="F2" s="190" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G2" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H2" s="190" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I2" s="190" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J2" s="190" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2" s="191"/>
+        <v>90</v>
+      </c>
+      <c r="K2" s="190" t="s">
+        <v>91</v>
+      </c>
       <c r="L2" s="190">
         <v>-7.0</v>
       </c>
-      <c r="M2" s="190"/>
+      <c r="M2" s="190">
+        <v>11.164783333333334</v>
+      </c>
       <c r="N2" s="190">
-        <v>7.621483333333333</v>
+        <v>11.400633333333333</v>
       </c>
       <c r="O2" s="190" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P2" s="190" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="Q2" s="191"/>
       <c r="R2" s="191"/>
@@ -12169,46 +11537,46 @@
     </row>
     <row r="3">
       <c r="A3" s="190" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B3" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C3" s="190">
-        <v>69.0</v>
+        <v>368.0</v>
       </c>
       <c r="D3" s="190">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="E3" s="191"/>
       <c r="F3" s="190" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G3" s="190" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H3" s="190" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I3" s="190" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J3" s="190" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K3" s="191"/>
       <c r="L3" s="190">
-        <v>2.0</v>
+        <v>-4.0</v>
       </c>
       <c r="M3" s="190"/>
       <c r="N3" s="190">
-        <v>7.2219</v>
+        <v>10.0636</v>
       </c>
       <c r="O3" s="190" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="P3" s="190" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="Q3" s="191"/>
       <c r="R3" s="191"/>
@@ -12229,48 +11597,46 @@
     </row>
     <row r="4">
       <c r="A4" s="190" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B4" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C4" s="192">
-        <v>329.0</v>
+        <v>207.0</v>
       </c>
       <c r="D4" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="190" t="s">
-        <v>83</v>
-      </c>
+        <v>52.0</v>
+      </c>
+      <c r="E4" s="191"/>
       <c r="F4" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G4" s="190" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H4" s="190" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="I4" s="190" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="J4" s="190" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K4" s="191"/>
       <c r="L4" s="190">
-        <v>-1.0</v>
+        <v>-10.0</v>
       </c>
       <c r="M4" s="190"/>
       <c r="N4" s="190">
-        <v>13.4872</v>
+        <v>8.838733333333334</v>
       </c>
       <c r="O4" s="190" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="P4" s="190" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="Q4" s="191"/>
       <c r="R4" s="191"/>
@@ -12290,48 +11656,46 @@
     </row>
     <row r="5">
       <c r="A5" s="190" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C5" s="190">
-        <v>662.0</v>
+        <v>332.0</v>
       </c>
       <c r="D5" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="190" t="s">
-        <v>56</v>
-      </c>
+        <v>61.0</v>
+      </c>
+      <c r="E5" s="191"/>
       <c r="F5" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G5" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H5" s="190" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="I5" s="190" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="J5" s="190" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K5" s="191"/>
       <c r="L5" s="190">
-        <v>-8.0</v>
+        <v>-12.0</v>
       </c>
       <c r="M5" s="190"/>
       <c r="N5" s="190">
-        <v>11.710583333333334</v>
+        <v>14.08845</v>
       </c>
       <c r="O5" s="190" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="P5" s="190" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="Q5" s="191"/>
       <c r="R5" s="191"/>
@@ -12352,48 +11716,46 @@
     </row>
     <row r="6">
       <c r="A6" s="190" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B6" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C6" s="192">
-        <v>369.0</v>
+        <v>259.0</v>
       </c>
       <c r="D6" s="190">
         <v>0.0</v>
       </c>
-      <c r="E6" s="190" t="s">
-        <v>104</v>
-      </c>
+      <c r="E6" s="191"/>
       <c r="F6" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G6" s="190" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H6" s="190" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I6" s="190" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J6" s="190" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K6" s="191"/>
       <c r="L6" s="190">
-        <v>-5.0</v>
+        <v>1.0</v>
       </c>
       <c r="M6" s="190"/>
       <c r="N6" s="190">
-        <v>9.2686</v>
+        <v>6.53025</v>
       </c>
       <c r="O6" s="190" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P6" s="190" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="Q6" s="191"/>
       <c r="R6" s="191"/>
@@ -12414,48 +11776,48 @@
     </row>
     <row r="7">
       <c r="A7" s="190" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B7" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C7" s="192">
-        <v>499.0</v>
+        <v>349.0</v>
       </c>
       <c r="D7" s="190">
         <v>0.0</v>
       </c>
       <c r="E7" s="190" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="F7" s="190" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G7" s="190" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="H7" s="190" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I7" s="190" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="J7" s="190" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="K7" s="191"/>
       <c r="L7" s="190">
-        <v>-3.0</v>
+        <v>-5.0</v>
       </c>
       <c r="M7" s="190"/>
       <c r="N7" s="190">
-        <v>11.6501</v>
+        <v>9.391766666666667</v>
       </c>
       <c r="O7" s="190" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="P7" s="190" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="Q7" s="191"/>
       <c r="R7" s="191"/>
@@ -12476,48 +11838,46 @@
     </row>
     <row r="8">
       <c r="A8" s="190" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B8" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C8" s="190">
-        <v>495.0</v>
+        <v>88.0</v>
       </c>
       <c r="D8" s="190">
         <v>0.0</v>
       </c>
-      <c r="E8" s="190" t="s">
-        <v>56</v>
-      </c>
+      <c r="E8" s="191"/>
       <c r="F8" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G8" s="190" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H8" s="190" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="I8" s="190" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J8" s="190" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K8" s="191"/>
       <c r="L8" s="190">
-        <v>-5.0</v>
+        <v>18.0</v>
       </c>
       <c r="M8" s="190"/>
       <c r="N8" s="190">
-        <v>9.443283333333333</v>
+        <v>23.682416666666665</v>
       </c>
       <c r="O8" s="190" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P8" s="190" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="Q8" s="191"/>
       <c r="R8" s="191"/>
@@ -12538,48 +11898,48 @@
     </row>
     <row r="9">
       <c r="A9" s="190" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="B9" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C9" s="190">
-        <v>507.0</v>
+        <v>398.0</v>
       </c>
       <c r="D9" s="190">
         <v>0.0</v>
       </c>
       <c r="E9" s="190" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F9" s="190" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G9" s="190" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="H9" s="190" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I9" s="190" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="J9" s="190" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="K9" s="191"/>
       <c r="L9" s="190">
-        <v>-8.0</v>
+        <v>-9.0</v>
       </c>
       <c r="M9" s="190"/>
       <c r="N9" s="190">
-        <v>11.236516666666667</v>
+        <v>5.962033333333333</v>
       </c>
       <c r="O9" s="190" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="P9" s="190" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="Q9" s="191"/>
       <c r="R9" s="191"/>
@@ -12600,48 +11960,46 @@
     </row>
     <row r="10">
       <c r="A10" s="190" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B10" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C10" s="192">
-        <v>648.0</v>
+        <v>59.0</v>
       </c>
       <c r="D10" s="190">
         <v>0.0</v>
       </c>
-      <c r="E10" s="190" t="s">
-        <v>118</v>
-      </c>
+      <c r="E10" s="191"/>
       <c r="F10" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G10" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H10" s="190" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="I10" s="190" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J10" s="190" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="K10" s="191"/>
       <c r="L10" s="190">
-        <v>-10.0</v>
+        <v>46.0</v>
       </c>
       <c r="M10" s="190"/>
       <c r="N10" s="190">
-        <v>9.420816666666667</v>
+        <v>51.83145</v>
       </c>
       <c r="O10" s="190" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P10" s="190" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="Q10" s="191"/>
       <c r="R10" s="191"/>
@@ -12662,48 +12020,48 @@
     </row>
     <row r="11">
       <c r="A11" s="190" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="B11" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C11" s="190">
-        <v>472.0</v>
+        <v>349.0</v>
       </c>
       <c r="D11" s="190">
         <v>0.0</v>
       </c>
       <c r="E11" s="190" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="F11" s="190" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G11" s="190" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="H11" s="190" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="I11" s="190" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J11" s="190" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K11" s="191"/>
       <c r="L11" s="190">
-        <v>-7.0</v>
+        <v>-6.0</v>
       </c>
       <c r="M11" s="190"/>
       <c r="N11" s="190">
-        <v>7.27045</v>
+        <v>8.61055</v>
       </c>
       <c r="O11" s="190" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="P11" s="190" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="Q11" s="191"/>
       <c r="R11" s="191"/>
@@ -12724,48 +12082,46 @@
     </row>
     <row r="12">
       <c r="A12" s="190" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B12" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="190">
-        <v>321.0</v>
+        <v>85</v>
+      </c>
+      <c r="C12" s="192">
+        <v>39.0</v>
       </c>
       <c r="D12" s="190">
         <v>0.0</v>
       </c>
-      <c r="E12" s="190" t="s">
-        <v>56</v>
-      </c>
+      <c r="E12" s="191"/>
       <c r="F12" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G12" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H12" s="190" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="I12" s="190" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J12" s="190" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="K12" s="191"/>
       <c r="L12" s="190">
-        <v>-5.0</v>
+        <v>-1.0</v>
       </c>
       <c r="M12" s="190"/>
       <c r="N12" s="190">
-        <v>9.143666666666666</v>
+        <v>3.2737666666666665</v>
       </c>
       <c r="O12" s="190" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P12" s="190" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="Q12" s="191"/>
       <c r="R12" s="191"/>
@@ -12786,46 +12142,46 @@
     </row>
     <row r="13">
       <c r="A13" s="190" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="B13" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C13" s="190">
-        <v>523.0</v>
+        <v>139.0</v>
       </c>
       <c r="D13" s="190">
         <v>0.0</v>
       </c>
       <c r="E13" s="191"/>
       <c r="F13" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G13" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H13" s="190" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="I13" s="190" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="J13" s="190" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="K13" s="191"/>
       <c r="L13" s="190">
-        <v>-10.0</v>
+        <v>-1.0</v>
       </c>
       <c r="M13" s="190"/>
       <c r="N13" s="190">
-        <v>9.136666666666667</v>
+        <v>3.5630166666666665</v>
       </c>
       <c r="O13" s="190" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P13" s="190" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="Q13" s="191"/>
       <c r="R13" s="191"/>
@@ -12845,48 +12201,46 @@
     </row>
     <row r="14">
       <c r="A14" s="190" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B14" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C14" s="190">
-        <v>289.0</v>
+        <v>259.0</v>
       </c>
       <c r="D14" s="190">
         <v>0.0</v>
       </c>
-      <c r="E14" s="190" t="s">
-        <v>56</v>
-      </c>
+      <c r="E14" s="191"/>
       <c r="F14" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G14" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H14" s="190" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="I14" s="190" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="J14" s="190" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="K14" s="191"/>
       <c r="L14" s="190">
-        <v>-8.0</v>
+        <v>10.0</v>
       </c>
       <c r="M14" s="190"/>
       <c r="N14" s="190">
-        <v>6.588133333333333</v>
+        <v>15.219966666666666</v>
       </c>
       <c r="O14" s="190" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P14" s="190" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="Q14" s="191"/>
       <c r="R14" s="191"/>
@@ -12907,48 +12261,46 @@
     </row>
     <row r="15">
       <c r="A15" s="190" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B15" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C15" s="192">
-        <v>329.0</v>
+        <v>39.0</v>
       </c>
       <c r="D15" s="190">
         <v>0.0</v>
       </c>
-      <c r="E15" s="190" t="s">
-        <v>118</v>
-      </c>
+      <c r="E15" s="191"/>
       <c r="F15" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G15" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H15" s="190" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I15" s="190" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="J15" s="190" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="K15" s="191"/>
       <c r="L15" s="190">
-        <v>-6.0</v>
+        <v>-3.0</v>
       </c>
       <c r="M15" s="190"/>
       <c r="N15" s="190">
-        <v>8.85415</v>
+        <v>1.4798166666666666</v>
       </c>
       <c r="O15" s="190" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P15" s="190" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q15" s="191"/>
       <c r="R15" s="191"/>
@@ -12969,46 +12321,46 @@
     </row>
     <row r="16">
       <c r="A16" s="190" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="B16" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C16" s="192">
-        <v>247.0</v>
+        <v>274.0</v>
       </c>
       <c r="D16" s="190">
-        <v>62.0</v>
+        <v>100.0</v>
       </c>
       <c r="E16" s="191"/>
       <c r="F16" s="190" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G16" s="190" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="H16" s="190" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="I16" s="190" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="J16" s="190" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K16" s="191"/>
       <c r="L16" s="190">
-        <v>3.0</v>
+        <v>-3.0</v>
       </c>
       <c r="M16" s="190"/>
       <c r="N16" s="190">
-        <v>22.5321</v>
+        <v>11.740983333333334</v>
       </c>
       <c r="O16" s="190" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="P16" s="190" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="Q16" s="191"/>
       <c r="R16" s="191"/>
@@ -13029,46 +12381,46 @@
     </row>
     <row r="17">
       <c r="A17" s="190" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B17" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C17" s="192">
-        <v>238.0</v>
+        <v>98.0</v>
       </c>
       <c r="D17" s="190">
         <v>0.0</v>
       </c>
       <c r="E17" s="191"/>
       <c r="F17" s="190" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="G17" s="190" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="H17" s="190" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I17" s="190" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J17" s="190" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="K17" s="191"/>
       <c r="L17" s="190">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="M17" s="190"/>
       <c r="N17" s="190">
-        <v>12.514733333333334</v>
+        <v>5.622466666666667</v>
       </c>
       <c r="O17" s="190" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P17" s="190" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="Q17" s="191"/>
       <c r="R17" s="191"/>
@@ -13089,46 +12441,52 @@
     </row>
     <row r="18">
       <c r="A18" s="190" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="B18" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C18" s="190">
-        <v>593.0</v>
+        <v>296.0</v>
       </c>
       <c r="D18" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E18" s="191"/>
+        <v>12.0</v>
+      </c>
+      <c r="E18" s="190" t="s">
+        <v>53</v>
+      </c>
       <c r="F18" s="190" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G18" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H18" s="190" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I18" s="190" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J18" s="190" t="s">
-        <v>148</v>
-      </c>
-      <c r="K18" s="191"/>
+        <v>154</v>
+      </c>
+      <c r="K18" s="190" t="s">
+        <v>155</v>
+      </c>
       <c r="L18" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="M18" s="190"/>
+        <v>1.0</v>
+      </c>
+      <c r="M18" s="190">
+        <v>3.9423833333333334</v>
+      </c>
       <c r="N18" s="190">
-        <v>19.43265</v>
+        <v>8.794466666666667</v>
       </c>
       <c r="O18" s="190" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="P18" s="190" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="Q18" s="191"/>
       <c r="R18" s="191"/>
@@ -13149,46 +12507,46 @@
     </row>
     <row r="19">
       <c r="A19" s="190" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B19" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C19" s="192">
-        <v>134.0</v>
+        <v>318.0</v>
       </c>
       <c r="D19" s="190">
         <v>0.0</v>
       </c>
       <c r="E19" s="191"/>
       <c r="F19" s="190" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="G19" s="190" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H19" s="190" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="I19" s="190" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="J19" s="190" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="K19" s="191"/>
       <c r="L19" s="190">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="M19" s="190"/>
       <c r="N19" s="190">
-        <v>14.82625</v>
+        <v>8.607383333333333</v>
       </c>
       <c r="O19" s="190" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P19" s="190" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="Q19" s="191"/>
       <c r="R19" s="191"/>
@@ -13209,46 +12567,46 @@
     </row>
     <row r="20">
       <c r="A20" s="190" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B20" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C20" s="190">
-        <v>249.0</v>
+        <v>308.0</v>
       </c>
       <c r="D20" s="190">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="E20" s="191"/>
       <c r="F20" s="190" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G20" s="190" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H20" s="190" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I20" s="190" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="J20" s="190" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="K20" s="191"/>
       <c r="L20" s="190">
-        <v>11.0</v>
+        <v>-4.0</v>
       </c>
       <c r="M20" s="190"/>
       <c r="N20" s="190">
-        <v>16.515933333333333</v>
+        <v>10.371833333333333</v>
       </c>
       <c r="O20" s="190" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="P20" s="190" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="Q20" s="191"/>
       <c r="R20" s="191"/>
@@ -13269,48 +12627,48 @@
     </row>
     <row r="21">
       <c r="A21" s="190" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="B21" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C21" s="192">
-        <v>493.0</v>
+        <v>349.0</v>
       </c>
       <c r="D21" s="190">
         <v>0.0</v>
       </c>
       <c r="E21" s="190" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F21" s="190" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G21" s="190" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="H21" s="190" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="I21" s="190" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="J21" s="190" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="K21" s="191"/>
       <c r="L21" s="190">
-        <v>11.0</v>
+        <v>-2.0</v>
       </c>
       <c r="M21" s="190"/>
       <c r="N21" s="190">
-        <v>26.94485</v>
+        <v>12.332816666666666</v>
       </c>
       <c r="O21" s="190" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="P21" s="190" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="Q21" s="191"/>
       <c r="R21" s="191"/>
@@ -13331,48 +12689,46 @@
     </row>
     <row r="22">
       <c r="A22" s="190" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B22" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C22" s="190">
-        <v>438.0</v>
+        <v>369.0</v>
       </c>
       <c r="D22" s="190">
         <v>0.0</v>
       </c>
-      <c r="E22" s="190" t="s">
-        <v>56</v>
-      </c>
+      <c r="E22" s="191"/>
       <c r="F22" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G22" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H22" s="190" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="I22" s="190" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="J22" s="190" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="K22" s="191"/>
       <c r="L22" s="190">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="M22" s="190"/>
       <c r="N22" s="190">
-        <v>18.441066666666668</v>
+        <v>9.554266666666667</v>
       </c>
       <c r="O22" s="190" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P22" s="190" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="Q22" s="191"/>
       <c r="R22" s="191"/>
@@ -13393,48 +12749,46 @@
     </row>
     <row r="23">
       <c r="A23" s="190" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B23" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C23" s="190">
-        <v>321.0</v>
+        <v>50.0</v>
       </c>
       <c r="D23" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E23" s="190" t="s">
-        <v>163</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="E23" s="191"/>
       <c r="F23" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G23" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H23" s="190" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I23" s="190" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J23" s="190" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="K23" s="191"/>
       <c r="L23" s="190">
-        <v>0.0</v>
+        <v>-4.0</v>
       </c>
       <c r="M23" s="190"/>
       <c r="N23" s="190">
-        <v>14.34055</v>
+        <v>0.4723333333333333</v>
       </c>
       <c r="O23" s="190" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P23" s="190" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="Q23" s="191"/>
       <c r="R23" s="191"/>
@@ -13455,52 +12809,46 @@
     </row>
     <row r="24">
       <c r="A24" s="190" t="s">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="B24" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C24" s="190">
-        <v>664.0</v>
+        <v>39.0</v>
       </c>
       <c r="D24" s="190">
         <v>0.0</v>
       </c>
-      <c r="E24" s="190" t="s">
-        <v>56</v>
-      </c>
+      <c r="E24" s="191"/>
       <c r="F24" s="190" t="s">
-        <v>167</v>
+        <v>102</v>
       </c>
       <c r="G24" s="190" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H24" s="190" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="I24" s="190" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J24" s="190" t="s">
-        <v>170</v>
-      </c>
-      <c r="K24" s="190" t="s">
-        <v>171</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="K24" s="191"/>
       <c r="L24" s="190">
-        <v>16.0</v>
-      </c>
-      <c r="M24" s="190">
-        <v>5.529416666666667</v>
-      </c>
+        <v>-4.0</v>
+      </c>
+      <c r="M24" s="190"/>
       <c r="N24" s="190">
-        <v>27.10695</v>
+        <v>0.09011666666666666</v>
       </c>
       <c r="O24" s="190" t="s">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="P24" s="190" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q24" s="191"/>
       <c r="R24" s="191"/>
@@ -13521,48 +12869,46 @@
     </row>
     <row r="25">
       <c r="A25" s="190" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B25" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C25" s="190">
-        <v>321.0</v>
+        <v>49.0</v>
       </c>
       <c r="D25" s="190">
         <v>0.0</v>
       </c>
-      <c r="E25" s="190" t="s">
-        <v>56</v>
-      </c>
+      <c r="E25" s="191"/>
       <c r="F25" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G25" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H25" s="190" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I25" s="190" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J25" s="190" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K25" s="191"/>
       <c r="L25" s="190">
-        <v>-5.0</v>
+        <v>0.0</v>
       </c>
       <c r="M25" s="190"/>
       <c r="N25" s="190">
-        <v>9.599516666666666</v>
+        <v>5.135583333333333</v>
       </c>
       <c r="O25" s="190" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P25" s="190" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q25" s="191"/>
       <c r="R25" s="191"/>
@@ -13583,48 +12929,46 @@
     </row>
     <row r="26">
       <c r="A26" s="190" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B26" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C26" s="190">
-        <v>391.0</v>
+        <v>78.0</v>
       </c>
       <c r="D26" s="190">
         <v>0.0</v>
       </c>
-      <c r="E26" s="190" t="s">
-        <v>56</v>
-      </c>
+      <c r="E26" s="191"/>
       <c r="F26" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G26" s="190" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H26" s="190" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I26" s="190" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J26" s="190" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K26" s="191"/>
       <c r="L26" s="190">
-        <v>-7.0</v>
+        <v>-4.0</v>
       </c>
       <c r="M26" s="190"/>
       <c r="N26" s="190">
-        <v>7.959583333333334</v>
+        <v>0.5178666666666667</v>
       </c>
       <c r="O26" s="190" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P26" s="190" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q26" s="191"/>
       <c r="R26" s="191"/>
@@ -13645,48 +12989,46 @@
     </row>
     <row r="27">
       <c r="A27" s="190" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C27" s="192">
-        <v>1424.0</v>
+        <v>232.0</v>
       </c>
       <c r="D27" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E27" s="190" t="s">
-        <v>56</v>
-      </c>
+        <v>86.0</v>
+      </c>
+      <c r="E27" s="191"/>
       <c r="F27" s="190" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G27" s="190" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="H27" s="190" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I27" s="190" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J27" s="190" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K27" s="191"/>
       <c r="L27" s="190">
-        <v>5.0</v>
+        <v>-8.0</v>
       </c>
       <c r="M27" s="190"/>
       <c r="N27" s="190">
-        <v>30.063716666666668</v>
+        <v>10.992766666666666</v>
       </c>
       <c r="O27" s="190" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="P27" s="190" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q27" s="191"/>
       <c r="R27" s="191"/>
@@ -13706,46 +13048,48 @@
     </row>
     <row r="28">
       <c r="A28" s="190" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B28" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C28" s="192">
-        <v>124.5</v>
+        <v>349.0</v>
       </c>
       <c r="D28" s="190">
-        <v>124.5</v>
-      </c>
-      <c r="E28" s="191"/>
+        <v>0.0</v>
+      </c>
+      <c r="E28" s="190" t="s">
+        <v>185</v>
+      </c>
       <c r="F28" s="190" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G28" s="190" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H28" s="190" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I28" s="190" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J28" s="190" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="K28" s="191"/>
       <c r="L28" s="190">
-        <v>20.0</v>
+        <v>-4.0</v>
       </c>
       <c r="M28" s="190"/>
       <c r="N28" s="190">
-        <v>25.914916666666667</v>
+        <v>10.121816666666666</v>
       </c>
       <c r="O28" s="190" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="P28" s="190" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q28" s="191"/>
       <c r="R28" s="191"/>
@@ -13766,46 +13110,46 @@
     </row>
     <row r="29">
       <c r="A29" s="190" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B29" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C29" s="192">
-        <v>249.0</v>
+        <v>130.0</v>
       </c>
       <c r="D29" s="190">
         <v>0.0</v>
       </c>
       <c r="E29" s="191"/>
       <c r="F29" s="190" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="G29" s="190" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="H29" s="190" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="I29" s="190" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J29" s="190" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K29" s="191"/>
       <c r="L29" s="190">
-        <v>-33.0</v>
+        <v>-1.0</v>
       </c>
       <c r="M29" s="190"/>
       <c r="N29" s="190">
-        <v>27.1798</v>
+        <v>3.3438333333333334</v>
       </c>
       <c r="O29" s="190" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P29" s="190" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q29" s="191"/>
       <c r="R29" s="191"/>
@@ -13826,48 +13170,46 @@
     </row>
     <row r="30">
       <c r="A30" s="190" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="B30" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C30" s="192">
-        <v>558.0</v>
+        <v>249.0</v>
       </c>
       <c r="D30" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E30" s="190" t="s">
-        <v>188</v>
-      </c>
+        <v>50.0</v>
+      </c>
+      <c r="E30" s="191"/>
       <c r="F30" s="190" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G30" s="190" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H30" s="190" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I30" s="190" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="J30" s="190" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K30" s="191"/>
       <c r="L30" s="190">
-        <v>-5.0</v>
+        <v>-7.0</v>
       </c>
       <c r="M30" s="190"/>
       <c r="N30" s="190">
-        <v>14.155583333333333</v>
+        <v>7.174066666666667</v>
       </c>
       <c r="O30" s="190" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="P30" s="190" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q30" s="191"/>
       <c r="R30" s="191"/>
@@ -13888,46 +13230,52 @@
     </row>
     <row r="31">
       <c r="A31" s="190" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="B31" s="190" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C31" s="190">
-        <v>567.0</v>
+        <v>359.0</v>
       </c>
       <c r="D31" s="190">
         <v>0.0</v>
       </c>
-      <c r="E31" s="191"/>
+      <c r="E31" s="190" t="s">
+        <v>50</v>
+      </c>
       <c r="F31" s="190" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G31" s="190" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="H31" s="190" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I31" s="190" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="J31" s="190" t="s">
-        <v>193</v>
-      </c>
-      <c r="K31" s="191"/>
+        <v>197</v>
+      </c>
+      <c r="K31" s="190" t="s">
+        <v>198</v>
+      </c>
       <c r="L31" s="190">
-        <v>-9.0</v>
-      </c>
-      <c r="M31" s="190"/>
+        <v>-12.0</v>
+      </c>
+      <c r="M31" s="190">
+        <v>1.9471</v>
+      </c>
       <c r="N31" s="190">
-        <v>10.649766666666666</v>
+        <v>8.69255</v>
       </c>
       <c r="O31" s="190" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="P31" s="190" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="Q31" s="191"/>
       <c r="R31" s="191"/>
@@ -13947,50 +13295,22 @@
       <c r="AF31" s="191"/>
     </row>
     <row r="32">
-      <c r="A32" s="190" t="s">
-        <v>81</v>
-      </c>
-      <c r="B32" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="190">
-        <v>329.0</v>
-      </c>
-      <c r="D32" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E32" s="190" t="s">
-        <v>195</v>
-      </c>
-      <c r="F32" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G32" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H32" s="190" t="s">
-        <v>196</v>
-      </c>
-      <c r="I32" s="190" t="s">
-        <v>197</v>
-      </c>
-      <c r="J32" s="190" t="s">
-        <v>197</v>
-      </c>
+      <c r="A32" s="191"/>
+      <c r="B32" s="191"/>
+      <c r="C32" s="191"/>
+      <c r="D32" s="191"/>
+      <c r="E32" s="191"/>
+      <c r="F32" s="191"/>
+      <c r="G32" s="191"/>
+      <c r="H32" s="191"/>
+      <c r="I32" s="191"/>
+      <c r="J32" s="191"/>
       <c r="K32" s="191"/>
-      <c r="L32" s="190">
-        <v>-8.0</v>
-      </c>
-      <c r="M32" s="190"/>
-      <c r="N32" s="190">
-        <v>6.304616666666667</v>
-      </c>
-      <c r="O32" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P32" s="190" t="s">
-        <v>198</v>
-      </c>
+      <c r="L32" s="191"/>
+      <c r="M32" s="191"/>
+      <c r="N32" s="191"/>
+      <c r="O32" s="191"/>
+      <c r="P32" s="191"/>
       <c r="Q32" s="191"/>
       <c r="R32" s="191"/>
       <c r="S32" s="191"/>
@@ -14009,50 +13329,22 @@
       <c r="AF32" s="191"/>
     </row>
     <row r="33">
-      <c r="A33" s="190" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="190">
-        <v>329.0</v>
-      </c>
-      <c r="D33" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E33" s="190" t="s">
-        <v>114</v>
-      </c>
-      <c r="F33" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G33" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H33" s="190" t="s">
-        <v>199</v>
-      </c>
-      <c r="I33" s="190" t="s">
-        <v>200</v>
-      </c>
-      <c r="J33" s="190" t="s">
-        <v>200</v>
-      </c>
+      <c r="A33" s="191"/>
+      <c r="B33" s="191"/>
+      <c r="C33" s="191"/>
+      <c r="D33" s="191"/>
+      <c r="E33" s="191"/>
+      <c r="F33" s="191"/>
+      <c r="G33" s="191"/>
+      <c r="H33" s="191"/>
+      <c r="I33" s="191"/>
+      <c r="J33" s="191"/>
       <c r="K33" s="191"/>
-      <c r="L33" s="190">
-        <v>-7.0</v>
-      </c>
-      <c r="M33" s="190"/>
-      <c r="N33" s="190">
-        <v>7.75805</v>
-      </c>
-      <c r="O33" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P33" s="190" t="s">
-        <v>201</v>
-      </c>
+      <c r="L33" s="191"/>
+      <c r="M33" s="191"/>
+      <c r="N33" s="191"/>
+      <c r="O33" s="191"/>
+      <c r="P33" s="191"/>
       <c r="Q33" s="191"/>
       <c r="R33" s="191"/>
       <c r="S33" s="191"/>
@@ -14071,54 +13363,22 @@
       <c r="AF33" s="191"/>
     </row>
     <row r="34">
-      <c r="A34" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B34" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="190">
-        <v>269.0</v>
-      </c>
-      <c r="D34" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E34" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F34" s="190" t="s">
-        <v>167</v>
-      </c>
-      <c r="G34" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H34" s="190" t="s">
-        <v>202</v>
-      </c>
-      <c r="I34" s="190" t="s">
-        <v>203</v>
-      </c>
-      <c r="J34" s="190" t="s">
-        <v>204</v>
-      </c>
-      <c r="K34" s="190" t="s">
-        <v>205</v>
-      </c>
-      <c r="L34" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="190">
-        <v>0.6549</v>
-      </c>
-      <c r="N34" s="190">
-        <v>6.068816666666667</v>
-      </c>
-      <c r="O34" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P34" s="190" t="s">
-        <v>206</v>
-      </c>
+      <c r="A34" s="191"/>
+      <c r="B34" s="191"/>
+      <c r="C34" s="191"/>
+      <c r="D34" s="191"/>
+      <c r="E34" s="191"/>
+      <c r="F34" s="191"/>
+      <c r="G34" s="191"/>
+      <c r="H34" s="191"/>
+      <c r="I34" s="191"/>
+      <c r="J34" s="191"/>
+      <c r="K34" s="191"/>
+      <c r="L34" s="191"/>
+      <c r="M34" s="191"/>
+      <c r="N34" s="191"/>
+      <c r="O34" s="191"/>
+      <c r="P34" s="191"/>
       <c r="Q34" s="191"/>
       <c r="R34" s="191"/>
       <c r="S34" s="191"/>
@@ -14137,54 +13397,22 @@
       <c r="AF34" s="191"/>
     </row>
     <row r="35">
-      <c r="A35" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B35" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="192">
-        <v>513.0</v>
-      </c>
-      <c r="D35" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F35" s="190" t="s">
-        <v>167</v>
-      </c>
-      <c r="G35" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H35" s="190" t="s">
-        <v>207</v>
-      </c>
-      <c r="I35" s="190" t="s">
-        <v>208</v>
-      </c>
-      <c r="J35" s="190" t="s">
-        <v>209</v>
-      </c>
-      <c r="K35" s="190" t="s">
-        <v>210</v>
-      </c>
-      <c r="L35" s="190">
-        <v>-6.0</v>
-      </c>
-      <c r="M35" s="190">
-        <v>0.25533333333333336</v>
-      </c>
-      <c r="N35" s="190">
-        <v>6.86865</v>
-      </c>
-      <c r="O35" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P35" s="190" t="s">
-        <v>211</v>
-      </c>
+      <c r="A35" s="191"/>
+      <c r="B35" s="191"/>
+      <c r="C35" s="193"/>
+      <c r="D35" s="191"/>
+      <c r="E35" s="191"/>
+      <c r="F35" s="191"/>
+      <c r="G35" s="191"/>
+      <c r="H35" s="191"/>
+      <c r="I35" s="191"/>
+      <c r="J35" s="191"/>
+      <c r="K35" s="191"/>
+      <c r="L35" s="191"/>
+      <c r="M35" s="191"/>
+      <c r="N35" s="191"/>
+      <c r="O35" s="191"/>
+      <c r="P35" s="191"/>
       <c r="Q35" s="191"/>
       <c r="R35" s="191"/>
       <c r="S35" s="191"/>
@@ -14203,50 +13431,22 @@
       <c r="AF35" s="191"/>
     </row>
     <row r="36">
-      <c r="A36" s="190" t="s">
-        <v>81</v>
-      </c>
-      <c r="B36" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" s="192">
-        <v>321.0</v>
-      </c>
-      <c r="D36" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E36" s="190" t="s">
-        <v>195</v>
-      </c>
-      <c r="F36" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G36" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H36" s="190" t="s">
-        <v>212</v>
-      </c>
-      <c r="I36" s="190" t="s">
-        <v>213</v>
-      </c>
-      <c r="J36" s="190" t="s">
-        <v>213</v>
-      </c>
+      <c r="A36" s="191"/>
+      <c r="B36" s="191"/>
+      <c r="C36" s="193"/>
+      <c r="D36" s="191"/>
+      <c r="E36" s="191"/>
+      <c r="F36" s="191"/>
+      <c r="G36" s="191"/>
+      <c r="H36" s="191"/>
+      <c r="I36" s="191"/>
+      <c r="J36" s="191"/>
       <c r="K36" s="191"/>
-      <c r="L36" s="190">
-        <v>-7.0</v>
-      </c>
-      <c r="M36" s="190"/>
-      <c r="N36" s="190">
-        <v>7.209783333333333</v>
-      </c>
-      <c r="O36" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P36" s="190" t="s">
-        <v>214</v>
-      </c>
+      <c r="L36" s="191"/>
+      <c r="M36" s="191"/>
+      <c r="N36" s="191"/>
+      <c r="O36" s="191"/>
+      <c r="P36" s="191"/>
       <c r="Q36" s="191"/>
       <c r="R36" s="191"/>
       <c r="S36" s="191"/>
@@ -14265,48 +13465,22 @@
       <c r="AF36" s="191"/>
     </row>
     <row r="37">
-      <c r="A37" s="190" t="s">
-        <v>128</v>
-      </c>
-      <c r="B37" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C37" s="190">
-        <v>331.0</v>
-      </c>
-      <c r="D37" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A37" s="191"/>
+      <c r="B37" s="191"/>
+      <c r="C37" s="191"/>
+      <c r="D37" s="191"/>
       <c r="E37" s="191"/>
-      <c r="F37" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G37" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H37" s="190" t="s">
-        <v>215</v>
-      </c>
-      <c r="I37" s="190" t="s">
-        <v>216</v>
-      </c>
-      <c r="J37" s="190" t="s">
-        <v>216</v>
-      </c>
+      <c r="F37" s="191"/>
+      <c r="G37" s="191"/>
+      <c r="H37" s="191"/>
+      <c r="I37" s="191"/>
+      <c r="J37" s="191"/>
       <c r="K37" s="191"/>
-      <c r="L37" s="190">
-        <v>-5.0</v>
-      </c>
-      <c r="M37" s="190"/>
-      <c r="N37" s="190">
-        <v>9.542166666666667</v>
-      </c>
-      <c r="O37" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P37" s="190" t="s">
-        <v>217</v>
-      </c>
+      <c r="L37" s="191"/>
+      <c r="M37" s="191"/>
+      <c r="N37" s="191"/>
+      <c r="O37" s="191"/>
+      <c r="P37" s="191"/>
       <c r="Q37" s="191"/>
       <c r="R37" s="191"/>
       <c r="S37" s="191"/>
@@ -14325,50 +13499,22 @@
       <c r="AF37" s="191"/>
     </row>
     <row r="38">
-      <c r="A38" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B38" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" s="192">
-        <v>433.0</v>
-      </c>
-      <c r="D38" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E38" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F38" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G38" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H38" s="190" t="s">
-        <v>218</v>
-      </c>
-      <c r="I38" s="190" t="s">
-        <v>219</v>
-      </c>
-      <c r="J38" s="190" t="s">
-        <v>220</v>
-      </c>
+      <c r="A38" s="191"/>
+      <c r="B38" s="191"/>
+      <c r="C38" s="193"/>
+      <c r="D38" s="191"/>
+      <c r="E38" s="191"/>
+      <c r="F38" s="191"/>
+      <c r="G38" s="191"/>
+      <c r="H38" s="191"/>
+      <c r="I38" s="191"/>
+      <c r="J38" s="191"/>
       <c r="K38" s="191"/>
-      <c r="L38" s="190">
-        <v>-2.0</v>
-      </c>
-      <c r="M38" s="190"/>
-      <c r="N38" s="190">
-        <v>12.83955</v>
-      </c>
-      <c r="O38" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P38" s="190" t="s">
-        <v>221</v>
-      </c>
+      <c r="L38" s="191"/>
+      <c r="M38" s="191"/>
+      <c r="N38" s="191"/>
+      <c r="O38" s="191"/>
+      <c r="P38" s="191"/>
       <c r="Q38" s="191"/>
       <c r="R38" s="191"/>
       <c r="S38" s="191"/>
@@ -14387,54 +13533,22 @@
       <c r="AF38" s="191"/>
     </row>
     <row r="39">
-      <c r="A39" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B39" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" s="190">
-        <v>258.0</v>
-      </c>
-      <c r="D39" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E39" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F39" s="190" t="s">
-        <v>167</v>
-      </c>
-      <c r="G39" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H39" s="190" t="s">
-        <v>222</v>
-      </c>
-      <c r="I39" s="190" t="s">
-        <v>223</v>
-      </c>
-      <c r="J39" s="190" t="s">
-        <v>224</v>
-      </c>
-      <c r="K39" s="190" t="s">
-        <v>225</v>
-      </c>
-      <c r="L39" s="190">
-        <v>9.0</v>
-      </c>
-      <c r="M39" s="190">
-        <v>1.1455</v>
-      </c>
-      <c r="N39" s="190">
-        <v>10.511316666666668</v>
-      </c>
-      <c r="O39" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P39" s="190" t="s">
-        <v>226</v>
-      </c>
+      <c r="A39" s="191"/>
+      <c r="B39" s="191"/>
+      <c r="C39" s="191"/>
+      <c r="D39" s="191"/>
+      <c r="E39" s="191"/>
+      <c r="F39" s="191"/>
+      <c r="G39" s="191"/>
+      <c r="H39" s="191"/>
+      <c r="I39" s="191"/>
+      <c r="J39" s="191"/>
+      <c r="K39" s="191"/>
+      <c r="L39" s="191"/>
+      <c r="M39" s="191"/>
+      <c r="N39" s="191"/>
+      <c r="O39" s="191"/>
+      <c r="P39" s="191"/>
       <c r="Q39" s="191"/>
       <c r="R39" s="191"/>
       <c r="S39" s="191"/>
@@ -14453,48 +13567,22 @@
       <c r="AF39" s="191"/>
     </row>
     <row r="40">
-      <c r="A40" s="190" t="s">
-        <v>128</v>
-      </c>
-      <c r="B40" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="190">
-        <v>1274.0</v>
-      </c>
-      <c r="D40" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A40" s="191"/>
+      <c r="B40" s="191"/>
+      <c r="C40" s="191"/>
+      <c r="D40" s="191"/>
       <c r="E40" s="191"/>
-      <c r="F40" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G40" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H40" s="190" t="s">
-        <v>227</v>
-      </c>
-      <c r="I40" s="190" t="s">
-        <v>228</v>
-      </c>
-      <c r="J40" s="190" t="s">
-        <v>228</v>
-      </c>
+      <c r="F40" s="191"/>
+      <c r="G40" s="191"/>
+      <c r="H40" s="191"/>
+      <c r="I40" s="191"/>
+      <c r="J40" s="191"/>
       <c r="K40" s="191"/>
-      <c r="L40" s="190">
-        <v>-6.0</v>
-      </c>
-      <c r="M40" s="190"/>
-      <c r="N40" s="190">
-        <v>13.44405</v>
-      </c>
-      <c r="O40" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P40" s="190" t="s">
-        <v>229</v>
-      </c>
+      <c r="L40" s="191"/>
+      <c r="M40" s="191"/>
+      <c r="N40" s="191"/>
+      <c r="O40" s="191"/>
+      <c r="P40" s="191"/>
       <c r="Q40" s="191"/>
       <c r="R40" s="191"/>
       <c r="S40" s="191"/>
@@ -14513,48 +13601,22 @@
       <c r="AF40" s="191"/>
     </row>
     <row r="41">
-      <c r="A41" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B41" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" s="192">
-        <v>223.0</v>
-      </c>
-      <c r="D41" s="190">
-        <v>86.0</v>
-      </c>
+      <c r="A41" s="191"/>
+      <c r="B41" s="191"/>
+      <c r="C41" s="193"/>
+      <c r="D41" s="191"/>
       <c r="E41" s="191"/>
-      <c r="F41" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G41" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H41" s="190" t="s">
-        <v>230</v>
-      </c>
-      <c r="I41" s="190" t="s">
-        <v>231</v>
-      </c>
-      <c r="J41" s="190" t="s">
-        <v>231</v>
-      </c>
+      <c r="F41" s="191"/>
+      <c r="G41" s="191"/>
+      <c r="H41" s="191"/>
+      <c r="I41" s="191"/>
+      <c r="J41" s="191"/>
       <c r="K41" s="191"/>
-      <c r="L41" s="190">
-        <v>-9.0</v>
-      </c>
-      <c r="M41" s="190"/>
-      <c r="N41" s="190">
-        <v>8.115983333333334</v>
-      </c>
-      <c r="O41" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P41" s="190" t="s">
-        <v>143</v>
-      </c>
+      <c r="L41" s="191"/>
+      <c r="M41" s="191"/>
+      <c r="N41" s="191"/>
+      <c r="O41" s="191"/>
+      <c r="P41" s="191"/>
       <c r="Q41" s="191"/>
       <c r="R41" s="191"/>
       <c r="S41" s="191"/>
@@ -14573,48 +13635,22 @@
       <c r="AF41" s="191"/>
     </row>
     <row r="42">
-      <c r="A42" s="190" t="s">
-        <v>128</v>
-      </c>
-      <c r="B42" s="190" t="s">
-        <v>232</v>
-      </c>
-      <c r="C42" s="192">
-        <v>682.0</v>
-      </c>
-      <c r="D42" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A42" s="191"/>
+      <c r="B42" s="191"/>
+      <c r="C42" s="193"/>
+      <c r="D42" s="191"/>
       <c r="E42" s="191"/>
-      <c r="F42" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G42" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H42" s="190" t="s">
-        <v>233</v>
-      </c>
-      <c r="I42" s="190" t="s">
-        <v>234</v>
-      </c>
-      <c r="J42" s="190" t="s">
-        <v>234</v>
-      </c>
+      <c r="F42" s="191"/>
+      <c r="G42" s="191"/>
+      <c r="H42" s="191"/>
+      <c r="I42" s="191"/>
+      <c r="J42" s="191"/>
       <c r="K42" s="191"/>
-      <c r="L42" s="190">
-        <v>-8.0</v>
-      </c>
-      <c r="M42" s="190"/>
-      <c r="N42" s="190">
-        <v>11.08105</v>
-      </c>
-      <c r="O42" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P42" s="190" t="s">
-        <v>235</v>
-      </c>
+      <c r="L42" s="191"/>
+      <c r="M42" s="191"/>
+      <c r="N42" s="191"/>
+      <c r="O42" s="191"/>
+      <c r="P42" s="191"/>
       <c r="Q42" s="191"/>
       <c r="R42" s="191"/>
       <c r="S42" s="191"/>
@@ -14633,54 +13669,22 @@
       <c r="AF42" s="191"/>
     </row>
     <row r="43">
-      <c r="A43" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B43" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C43" s="190">
-        <v>518.0</v>
-      </c>
-      <c r="D43" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E43" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F43" s="190" t="s">
-        <v>167</v>
-      </c>
-      <c r="G43" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H43" s="190" t="s">
-        <v>236</v>
-      </c>
-      <c r="I43" s="190" t="s">
-        <v>237</v>
-      </c>
-      <c r="J43" s="190" t="s">
-        <v>238</v>
-      </c>
-      <c r="K43" s="190" t="s">
-        <v>239</v>
-      </c>
-      <c r="L43" s="190">
-        <v>4.0</v>
-      </c>
-      <c r="M43" s="190">
-        <v>1.7540833333333334</v>
-      </c>
-      <c r="N43" s="190">
-        <v>11.400033333333333</v>
-      </c>
-      <c r="O43" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P43" s="190" t="s">
-        <v>240</v>
-      </c>
+      <c r="A43" s="191"/>
+      <c r="B43" s="191"/>
+      <c r="C43" s="191"/>
+      <c r="D43" s="191"/>
+      <c r="E43" s="191"/>
+      <c r="F43" s="191"/>
+      <c r="G43" s="191"/>
+      <c r="H43" s="191"/>
+      <c r="I43" s="191"/>
+      <c r="J43" s="191"/>
+      <c r="K43" s="191"/>
+      <c r="L43" s="191"/>
+      <c r="M43" s="191"/>
+      <c r="N43" s="191"/>
+      <c r="O43" s="191"/>
+      <c r="P43" s="191"/>
       <c r="Q43" s="191"/>
       <c r="R43" s="191"/>
       <c r="S43" s="191"/>
@@ -14699,50 +13703,22 @@
       <c r="AF43" s="191"/>
     </row>
     <row r="44">
-      <c r="A44" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B44" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C44" s="192">
-        <v>655.0</v>
-      </c>
-      <c r="D44" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E44" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F44" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G44" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H44" s="190" t="s">
-        <v>241</v>
-      </c>
-      <c r="I44" s="190" t="s">
-        <v>242</v>
-      </c>
-      <c r="J44" s="190" t="s">
-        <v>242</v>
-      </c>
+      <c r="A44" s="191"/>
+      <c r="B44" s="191"/>
+      <c r="C44" s="193"/>
+      <c r="D44" s="191"/>
+      <c r="E44" s="191"/>
+      <c r="F44" s="191"/>
+      <c r="G44" s="191"/>
+      <c r="H44" s="191"/>
+      <c r="I44" s="191"/>
+      <c r="J44" s="191"/>
       <c r="K44" s="191"/>
-      <c r="L44" s="190">
-        <v>-9.0</v>
-      </c>
-      <c r="M44" s="190"/>
-      <c r="N44" s="190">
-        <v>10.474633333333333</v>
-      </c>
-      <c r="O44" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P44" s="190" t="s">
-        <v>243</v>
-      </c>
+      <c r="L44" s="191"/>
+      <c r="M44" s="191"/>
+      <c r="N44" s="191"/>
+      <c r="O44" s="191"/>
+      <c r="P44" s="191"/>
       <c r="Q44" s="191"/>
       <c r="R44" s="191"/>
       <c r="S44" s="191"/>
@@ -14761,50 +13737,22 @@
       <c r="AF44" s="191"/>
     </row>
     <row r="45">
-      <c r="A45" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B45" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C45" s="190">
-        <v>653.0</v>
-      </c>
-      <c r="D45" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E45" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F45" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G45" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H45" s="190" t="s">
-        <v>244</v>
-      </c>
-      <c r="I45" s="190" t="s">
-        <v>245</v>
-      </c>
-      <c r="J45" s="190" t="s">
-        <v>245</v>
-      </c>
+      <c r="A45" s="191"/>
+      <c r="B45" s="191"/>
+      <c r="C45" s="191"/>
+      <c r="D45" s="191"/>
+      <c r="E45" s="191"/>
+      <c r="F45" s="191"/>
+      <c r="G45" s="191"/>
+      <c r="H45" s="191"/>
+      <c r="I45" s="191"/>
+      <c r="J45" s="191"/>
       <c r="K45" s="191"/>
-      <c r="L45" s="190">
-        <v>-11.0</v>
-      </c>
-      <c r="M45" s="190"/>
-      <c r="N45" s="190">
-        <v>8.768616666666667</v>
-      </c>
-      <c r="O45" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P45" s="190" t="s">
-        <v>246</v>
-      </c>
+      <c r="L45" s="191"/>
+      <c r="M45" s="191"/>
+      <c r="N45" s="191"/>
+      <c r="O45" s="191"/>
+      <c r="P45" s="191"/>
       <c r="Q45" s="191"/>
       <c r="R45" s="191"/>
       <c r="S45" s="191"/>
@@ -14823,48 +13771,22 @@
       <c r="AF45" s="191"/>
     </row>
     <row r="46">
-      <c r="A46" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B46" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="192">
-        <v>247.0</v>
-      </c>
-      <c r="D46" s="190">
-        <v>62.0</v>
-      </c>
+      <c r="A46" s="191"/>
+      <c r="B46" s="191"/>
+      <c r="C46" s="193"/>
+      <c r="D46" s="191"/>
       <c r="E46" s="191"/>
-      <c r="F46" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G46" s="190" t="s">
-        <v>139</v>
-      </c>
-      <c r="H46" s="190" t="s">
-        <v>247</v>
-      </c>
-      <c r="I46" s="190" t="s">
-        <v>248</v>
-      </c>
-      <c r="J46" s="190" t="s">
-        <v>248</v>
-      </c>
+      <c r="F46" s="191"/>
+      <c r="G46" s="191"/>
+      <c r="H46" s="191"/>
+      <c r="I46" s="191"/>
+      <c r="J46" s="191"/>
       <c r="K46" s="191"/>
-      <c r="L46" s="190">
-        <v>-13.0</v>
-      </c>
-      <c r="M46" s="190"/>
-      <c r="N46" s="190">
-        <v>6.152783333333334</v>
-      </c>
-      <c r="O46" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P46" s="190" t="s">
-        <v>249</v>
-      </c>
+      <c r="L46" s="191"/>
+      <c r="M46" s="191"/>
+      <c r="N46" s="191"/>
+      <c r="O46" s="191"/>
+      <c r="P46" s="191"/>
       <c r="Q46" s="191"/>
       <c r="R46" s="191"/>
       <c r="S46" s="191"/>
@@ -14883,48 +13805,22 @@
       <c r="AF46" s="191"/>
     </row>
     <row r="47">
-      <c r="A47" s="190" t="s">
-        <v>128</v>
-      </c>
-      <c r="B47" s="190" t="s">
-        <v>232</v>
-      </c>
-      <c r="C47" s="192">
-        <v>828.0</v>
-      </c>
-      <c r="D47" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A47" s="191"/>
+      <c r="B47" s="191"/>
+      <c r="C47" s="193"/>
+      <c r="D47" s="191"/>
       <c r="E47" s="191"/>
-      <c r="F47" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G47" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H47" s="190" t="s">
-        <v>250</v>
-      </c>
-      <c r="I47" s="190" t="s">
-        <v>251</v>
-      </c>
-      <c r="J47" s="190" t="s">
-        <v>252</v>
-      </c>
+      <c r="F47" s="191"/>
+      <c r="G47" s="191"/>
+      <c r="H47" s="191"/>
+      <c r="I47" s="191"/>
+      <c r="J47" s="191"/>
       <c r="K47" s="191"/>
-      <c r="L47" s="190">
-        <v>-6.0</v>
-      </c>
-      <c r="M47" s="190"/>
-      <c r="N47" s="190">
-        <v>13.17915</v>
-      </c>
-      <c r="O47" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P47" s="190" t="s">
-        <v>253</v>
-      </c>
+      <c r="L47" s="191"/>
+      <c r="M47" s="191"/>
+      <c r="N47" s="191"/>
+      <c r="O47" s="191"/>
+      <c r="P47" s="191"/>
       <c r="Q47" s="191"/>
       <c r="R47" s="191"/>
       <c r="S47" s="191"/>
@@ -14943,50 +13839,22 @@
       <c r="AF47" s="191"/>
     </row>
     <row r="48">
-      <c r="A48" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B48" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C48" s="192">
-        <v>792.0</v>
-      </c>
-      <c r="D48" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E48" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F48" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G48" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H48" s="190" t="s">
-        <v>254</v>
-      </c>
-      <c r="I48" s="190" t="s">
-        <v>255</v>
-      </c>
-      <c r="J48" s="190" t="s">
-        <v>255</v>
-      </c>
+      <c r="A48" s="191"/>
+      <c r="B48" s="191"/>
+      <c r="C48" s="193"/>
+      <c r="D48" s="191"/>
+      <c r="E48" s="191"/>
+      <c r="F48" s="191"/>
+      <c r="G48" s="191"/>
+      <c r="H48" s="191"/>
+      <c r="I48" s="191"/>
+      <c r="J48" s="191"/>
       <c r="K48" s="191"/>
-      <c r="L48" s="190">
-        <v>-9.0</v>
-      </c>
-      <c r="M48" s="190"/>
-      <c r="N48" s="190">
-        <v>10.3025</v>
-      </c>
-      <c r="O48" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P48" s="190" t="s">
-        <v>256</v>
-      </c>
+      <c r="L48" s="191"/>
+      <c r="M48" s="191"/>
+      <c r="N48" s="191"/>
+      <c r="O48" s="191"/>
+      <c r="P48" s="191"/>
       <c r="Q48" s="191"/>
       <c r="R48" s="191"/>
       <c r="S48" s="191"/>
@@ -15005,48 +13873,22 @@
       <c r="AF48" s="191"/>
     </row>
     <row r="49">
-      <c r="A49" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B49" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" s="190">
-        <v>299.0</v>
-      </c>
-      <c r="D49" s="190">
-        <v>75.0</v>
-      </c>
+      <c r="A49" s="191"/>
+      <c r="B49" s="191"/>
+      <c r="C49" s="191"/>
+      <c r="D49" s="191"/>
       <c r="E49" s="191"/>
-      <c r="F49" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G49" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H49" s="190" t="s">
-        <v>257</v>
-      </c>
-      <c r="I49" s="190" t="s">
-        <v>258</v>
-      </c>
-      <c r="J49" s="190" t="s">
-        <v>258</v>
-      </c>
+      <c r="F49" s="191"/>
+      <c r="G49" s="191"/>
+      <c r="H49" s="191"/>
+      <c r="I49" s="191"/>
+      <c r="J49" s="191"/>
       <c r="K49" s="191"/>
-      <c r="L49" s="190">
-        <v>-8.0</v>
-      </c>
-      <c r="M49" s="190"/>
-      <c r="N49" s="190">
-        <v>10.851716666666666</v>
-      </c>
-      <c r="O49" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P49" s="190" t="s">
-        <v>259</v>
-      </c>
+      <c r="L49" s="191"/>
+      <c r="M49" s="191"/>
+      <c r="N49" s="191"/>
+      <c r="O49" s="191"/>
+      <c r="P49" s="191"/>
       <c r="Q49" s="191"/>
       <c r="R49" s="191"/>
       <c r="S49" s="191"/>
@@ -15065,50 +13907,22 @@
       <c r="AF49" s="191"/>
     </row>
     <row r="50">
-      <c r="A50" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B50" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C50" s="190">
-        <v>394.0</v>
-      </c>
-      <c r="D50" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E50" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F50" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G50" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H50" s="190" t="s">
-        <v>260</v>
-      </c>
-      <c r="I50" s="190" t="s">
-        <v>261</v>
-      </c>
-      <c r="J50" s="190" t="s">
-        <v>261</v>
-      </c>
+      <c r="A50" s="191"/>
+      <c r="B50" s="191"/>
+      <c r="C50" s="191"/>
+      <c r="D50" s="191"/>
+      <c r="E50" s="191"/>
+      <c r="F50" s="191"/>
+      <c r="G50" s="191"/>
+      <c r="H50" s="191"/>
+      <c r="I50" s="191"/>
+      <c r="J50" s="191"/>
       <c r="K50" s="191"/>
-      <c r="L50" s="190">
-        <v>-5.0</v>
-      </c>
-      <c r="M50" s="190"/>
-      <c r="N50" s="190">
-        <v>9.8148</v>
-      </c>
-      <c r="O50" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P50" s="190" t="s">
-        <v>262</v>
-      </c>
+      <c r="L50" s="191"/>
+      <c r="M50" s="191"/>
+      <c r="N50" s="191"/>
+      <c r="O50" s="191"/>
+      <c r="P50" s="191"/>
       <c r="Q50" s="191"/>
       <c r="R50" s="191"/>
       <c r="S50" s="191"/>
@@ -15127,50 +13941,22 @@
       <c r="AF50" s="191"/>
     </row>
     <row r="51">
-      <c r="A51" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B51" s="192" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" s="190">
-        <v>434.0</v>
-      </c>
-      <c r="D51" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E51" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F51" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G51" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H51" s="190" t="s">
-        <v>263</v>
-      </c>
-      <c r="I51" s="190" t="s">
-        <v>264</v>
-      </c>
-      <c r="J51" s="190" t="s">
-        <v>264</v>
-      </c>
+      <c r="A51" s="191"/>
+      <c r="B51" s="193"/>
+      <c r="C51" s="191"/>
+      <c r="D51" s="191"/>
+      <c r="E51" s="191"/>
+      <c r="F51" s="191"/>
+      <c r="G51" s="191"/>
+      <c r="H51" s="191"/>
+      <c r="I51" s="191"/>
+      <c r="J51" s="191"/>
       <c r="K51" s="191"/>
-      <c r="L51" s="190">
-        <v>-4.0</v>
-      </c>
-      <c r="M51" s="190"/>
-      <c r="N51" s="190">
-        <v>10.040283333333333</v>
-      </c>
-      <c r="O51" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P51" s="190" t="s">
-        <v>265</v>
-      </c>
+      <c r="L51" s="191"/>
+      <c r="M51" s="191"/>
+      <c r="N51" s="191"/>
+      <c r="O51" s="191"/>
+      <c r="P51" s="191"/>
       <c r="Q51" s="191"/>
       <c r="R51" s="191"/>
       <c r="S51" s="191"/>
@@ -15189,50 +13975,22 @@
       <c r="AF51" s="191"/>
     </row>
     <row r="52">
-      <c r="A52" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B52" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C52" s="192">
-        <v>723.0</v>
-      </c>
-      <c r="D52" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E52" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F52" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G52" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H52" s="190" t="s">
-        <v>266</v>
-      </c>
-      <c r="I52" s="190" t="s">
-        <v>267</v>
-      </c>
-      <c r="J52" s="190" t="s">
-        <v>267</v>
-      </c>
+      <c r="A52" s="191"/>
+      <c r="B52" s="191"/>
+      <c r="C52" s="193"/>
+      <c r="D52" s="191"/>
+      <c r="E52" s="191"/>
+      <c r="F52" s="191"/>
+      <c r="G52" s="191"/>
+      <c r="H52" s="191"/>
+      <c r="I52" s="191"/>
+      <c r="J52" s="191"/>
       <c r="K52" s="191"/>
-      <c r="L52" s="190">
-        <v>-8.0</v>
-      </c>
-      <c r="M52" s="190"/>
-      <c r="N52" s="190">
-        <v>11.264116666666666</v>
-      </c>
-      <c r="O52" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P52" s="190" t="s">
-        <v>268</v>
-      </c>
+      <c r="L52" s="191"/>
+      <c r="M52" s="191"/>
+      <c r="N52" s="191"/>
+      <c r="O52" s="191"/>
+      <c r="P52" s="191"/>
       <c r="Q52" s="191"/>
       <c r="R52" s="191"/>
       <c r="S52" s="191"/>
@@ -15251,50 +14009,22 @@
       <c r="AF52" s="191"/>
     </row>
     <row r="53">
-      <c r="A53" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B53" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C53" s="192">
-        <v>329.0</v>
-      </c>
-      <c r="D53" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E53" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F53" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G53" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H53" s="190" t="s">
-        <v>269</v>
-      </c>
-      <c r="I53" s="190" t="s">
-        <v>270</v>
-      </c>
-      <c r="J53" s="190" t="s">
-        <v>270</v>
-      </c>
+      <c r="A53" s="191"/>
+      <c r="B53" s="191"/>
+      <c r="C53" s="193"/>
+      <c r="D53" s="191"/>
+      <c r="E53" s="191"/>
+      <c r="F53" s="191"/>
+      <c r="G53" s="191"/>
+      <c r="H53" s="191"/>
+      <c r="I53" s="191"/>
+      <c r="J53" s="191"/>
       <c r="K53" s="191"/>
-      <c r="L53" s="190">
-        <v>-8.0</v>
-      </c>
-      <c r="M53" s="190"/>
-      <c r="N53" s="190">
-        <v>7.703833333333334</v>
-      </c>
-      <c r="O53" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P53" s="190" t="s">
-        <v>271</v>
-      </c>
+      <c r="L53" s="191"/>
+      <c r="M53" s="191"/>
+      <c r="N53" s="191"/>
+      <c r="O53" s="191"/>
+      <c r="P53" s="191"/>
       <c r="Q53" s="191"/>
       <c r="R53" s="191"/>
       <c r="S53" s="191"/>
@@ -15313,50 +14043,22 @@
       <c r="AF53" s="191"/>
     </row>
     <row r="54">
-      <c r="A54" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B54" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C54" s="190">
-        <v>329.0</v>
-      </c>
-      <c r="D54" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E54" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F54" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G54" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H54" s="190" t="s">
-        <v>272</v>
-      </c>
-      <c r="I54" s="190" t="s">
-        <v>273</v>
-      </c>
-      <c r="J54" s="190" t="s">
-        <v>273</v>
-      </c>
+      <c r="A54" s="191"/>
+      <c r="B54" s="191"/>
+      <c r="C54" s="191"/>
+      <c r="D54" s="191"/>
+      <c r="E54" s="191"/>
+      <c r="F54" s="191"/>
+      <c r="G54" s="191"/>
+      <c r="H54" s="191"/>
+      <c r="I54" s="191"/>
+      <c r="J54" s="191"/>
       <c r="K54" s="191"/>
-      <c r="L54" s="190">
-        <v>-6.0</v>
-      </c>
-      <c r="M54" s="190"/>
-      <c r="N54" s="190">
-        <v>8.057333333333334</v>
-      </c>
-      <c r="O54" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P54" s="190" t="s">
-        <v>274</v>
-      </c>
+      <c r="L54" s="191"/>
+      <c r="M54" s="191"/>
+      <c r="N54" s="191"/>
+      <c r="O54" s="191"/>
+      <c r="P54" s="191"/>
       <c r="Q54" s="191"/>
       <c r="R54" s="191"/>
       <c r="S54" s="191"/>
@@ -15375,48 +14077,22 @@
       <c r="AF54" s="191"/>
     </row>
     <row r="55">
-      <c r="A55" s="190" t="s">
-        <v>90</v>
-      </c>
-      <c r="B55" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C55" s="192">
-        <v>269.0</v>
-      </c>
-      <c r="D55" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A55" s="191"/>
+      <c r="B55" s="191"/>
+      <c r="C55" s="193"/>
+      <c r="D55" s="191"/>
       <c r="E55" s="191"/>
-      <c r="F55" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G55" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="H55" s="190" t="s">
-        <v>275</v>
-      </c>
-      <c r="I55" s="190" t="s">
-        <v>276</v>
-      </c>
-      <c r="J55" s="190" t="s">
-        <v>276</v>
-      </c>
+      <c r="F55" s="191"/>
+      <c r="G55" s="191"/>
+      <c r="H55" s="191"/>
+      <c r="I55" s="191"/>
+      <c r="J55" s="191"/>
       <c r="K55" s="191"/>
-      <c r="L55" s="190">
-        <v>4.0</v>
-      </c>
-      <c r="M55" s="190"/>
-      <c r="N55" s="190">
-        <v>9.685333333333332</v>
-      </c>
-      <c r="O55" s="190" t="s">
-        <v>95</v>
-      </c>
-      <c r="P55" s="190" t="s">
-        <v>277</v>
-      </c>
+      <c r="L55" s="191"/>
+      <c r="M55" s="191"/>
+      <c r="N55" s="191"/>
+      <c r="O55" s="191"/>
+      <c r="P55" s="191"/>
       <c r="Q55" s="191"/>
       <c r="R55" s="191"/>
       <c r="S55" s="191"/>
@@ -15435,50 +14111,22 @@
       <c r="AF55" s="191"/>
     </row>
     <row r="56">
-      <c r="A56" s="190" t="s">
-        <v>81</v>
-      </c>
-      <c r="B56" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C56" s="192">
-        <v>830.0</v>
-      </c>
-      <c r="D56" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E56" s="190" t="s">
-        <v>278</v>
-      </c>
-      <c r="F56" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G56" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H56" s="190" t="s">
-        <v>279</v>
-      </c>
-      <c r="I56" s="190" t="s">
-        <v>280</v>
-      </c>
-      <c r="J56" s="190" t="s">
-        <v>280</v>
-      </c>
+      <c r="A56" s="191"/>
+      <c r="B56" s="191"/>
+      <c r="C56" s="193"/>
+      <c r="D56" s="191"/>
+      <c r="E56" s="191"/>
+      <c r="F56" s="191"/>
+      <c r="G56" s="191"/>
+      <c r="H56" s="191"/>
+      <c r="I56" s="191"/>
+      <c r="J56" s="191"/>
       <c r="K56" s="191"/>
-      <c r="L56" s="190">
-        <v>-2.0</v>
-      </c>
-      <c r="M56" s="190"/>
-      <c r="N56" s="190">
-        <v>17.434916666666666</v>
-      </c>
-      <c r="O56" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P56" s="190" t="s">
-        <v>281</v>
-      </c>
+      <c r="L56" s="191"/>
+      <c r="M56" s="191"/>
+      <c r="N56" s="191"/>
+      <c r="O56" s="191"/>
+      <c r="P56" s="191"/>
       <c r="Q56" s="191"/>
       <c r="R56" s="191"/>
       <c r="S56" s="191"/>
@@ -15497,48 +14145,22 @@
       <c r="AF56" s="191"/>
     </row>
     <row r="57">
-      <c r="A57" s="190" t="s">
-        <v>128</v>
-      </c>
-      <c r="B57" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C57" s="192">
-        <v>658.0</v>
-      </c>
-      <c r="D57" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A57" s="191"/>
+      <c r="B57" s="191"/>
+      <c r="C57" s="193"/>
+      <c r="D57" s="191"/>
       <c r="E57" s="191"/>
-      <c r="F57" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G57" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H57" s="190" t="s">
-        <v>282</v>
-      </c>
-      <c r="I57" s="190" t="s">
-        <v>283</v>
-      </c>
-      <c r="J57" s="190" t="s">
-        <v>283</v>
-      </c>
+      <c r="F57" s="191"/>
+      <c r="G57" s="191"/>
+      <c r="H57" s="191"/>
+      <c r="I57" s="191"/>
+      <c r="J57" s="191"/>
       <c r="K57" s="191"/>
-      <c r="L57" s="190">
-        <v>-8.0</v>
-      </c>
-      <c r="M57" s="190"/>
-      <c r="N57" s="190">
-        <v>11.21715</v>
-      </c>
-      <c r="O57" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P57" s="190" t="s">
-        <v>284</v>
-      </c>
+      <c r="L57" s="191"/>
+      <c r="M57" s="191"/>
+      <c r="N57" s="191"/>
+      <c r="O57" s="191"/>
+      <c r="P57" s="191"/>
       <c r="Q57" s="191"/>
       <c r="R57" s="191"/>
       <c r="S57" s="191"/>
@@ -15557,50 +14179,22 @@
       <c r="AF57" s="191"/>
     </row>
     <row r="58">
-      <c r="A58" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B58" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C58" s="190">
-        <v>817.0</v>
-      </c>
-      <c r="D58" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E58" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F58" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G58" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H58" s="190" t="s">
-        <v>285</v>
-      </c>
-      <c r="I58" s="190" t="s">
-        <v>286</v>
-      </c>
-      <c r="J58" s="190" t="s">
-        <v>286</v>
-      </c>
+      <c r="A58" s="191"/>
+      <c r="B58" s="191"/>
+      <c r="C58" s="191"/>
+      <c r="D58" s="191"/>
+      <c r="E58" s="191"/>
+      <c r="F58" s="191"/>
+      <c r="G58" s="191"/>
+      <c r="H58" s="191"/>
+      <c r="I58" s="191"/>
+      <c r="J58" s="191"/>
       <c r="K58" s="191"/>
-      <c r="L58" s="190">
-        <v>-9.0</v>
-      </c>
-      <c r="M58" s="190"/>
-      <c r="N58" s="190">
-        <v>11.448083333333333</v>
-      </c>
-      <c r="O58" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P58" s="190" t="s">
-        <v>287</v>
-      </c>
+      <c r="L58" s="191"/>
+      <c r="M58" s="191"/>
+      <c r="N58" s="191"/>
+      <c r="O58" s="191"/>
+      <c r="P58" s="191"/>
       <c r="Q58" s="191"/>
       <c r="R58" s="191"/>
       <c r="S58" s="191"/>
@@ -15619,50 +14213,22 @@
       <c r="AF58" s="191"/>
     </row>
     <row r="59">
-      <c r="A59" s="190" t="s">
-        <v>81</v>
-      </c>
-      <c r="B59" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C59" s="192">
-        <v>500.0</v>
-      </c>
-      <c r="D59" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E59" s="190" t="s">
-        <v>288</v>
-      </c>
-      <c r="F59" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G59" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H59" s="190" t="s">
-        <v>289</v>
-      </c>
-      <c r="I59" s="190" t="s">
-        <v>290</v>
-      </c>
-      <c r="J59" s="190" t="s">
-        <v>290</v>
-      </c>
+      <c r="A59" s="191"/>
+      <c r="B59" s="191"/>
+      <c r="C59" s="193"/>
+      <c r="D59" s="191"/>
+      <c r="E59" s="191"/>
+      <c r="F59" s="191"/>
+      <c r="G59" s="191"/>
+      <c r="H59" s="191"/>
+      <c r="I59" s="191"/>
+      <c r="J59" s="191"/>
       <c r="K59" s="191"/>
-      <c r="L59" s="190">
-        <v>-7.0</v>
-      </c>
-      <c r="M59" s="190"/>
-      <c r="N59" s="190">
-        <v>12.328016666666667</v>
-      </c>
-      <c r="O59" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P59" s="190" t="s">
-        <v>291</v>
-      </c>
+      <c r="L59" s="191"/>
+      <c r="M59" s="191"/>
+      <c r="N59" s="191"/>
+      <c r="O59" s="191"/>
+      <c r="P59" s="191"/>
       <c r="Q59" s="191"/>
       <c r="R59" s="191"/>
       <c r="S59" s="191"/>
@@ -15681,50 +14247,22 @@
       <c r="AF59" s="191"/>
     </row>
     <row r="60">
-      <c r="A60" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B60" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C60" s="190">
-        <v>508.0</v>
-      </c>
-      <c r="D60" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E60" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F60" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G60" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H60" s="190" t="s">
-        <v>292</v>
-      </c>
-      <c r="I60" s="190" t="s">
-        <v>293</v>
-      </c>
-      <c r="J60" s="190" t="s">
-        <v>294</v>
-      </c>
+      <c r="A60" s="191"/>
+      <c r="B60" s="191"/>
+      <c r="C60" s="191"/>
+      <c r="D60" s="191"/>
+      <c r="E60" s="191"/>
+      <c r="F60" s="191"/>
+      <c r="G60" s="191"/>
+      <c r="H60" s="191"/>
+      <c r="I60" s="191"/>
+      <c r="J60" s="191"/>
       <c r="K60" s="191"/>
-      <c r="L60" s="190">
-        <v>-11.0</v>
-      </c>
-      <c r="M60" s="190"/>
-      <c r="N60" s="190">
-        <v>8.16655</v>
-      </c>
-      <c r="O60" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P60" s="190" t="s">
-        <v>295</v>
-      </c>
+      <c r="L60" s="191"/>
+      <c r="M60" s="191"/>
+      <c r="N60" s="191"/>
+      <c r="O60" s="191"/>
+      <c r="P60" s="191"/>
       <c r="Q60" s="191"/>
       <c r="R60" s="191"/>
       <c r="S60" s="191"/>
@@ -15743,50 +14281,22 @@
       <c r="AF60" s="191"/>
     </row>
     <row r="61">
-      <c r="A61" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B61" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C61" s="192">
-        <v>264.0</v>
-      </c>
-      <c r="D61" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E61" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F61" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G61" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H61" s="190" t="s">
-        <v>296</v>
-      </c>
-      <c r="I61" s="190" t="s">
-        <v>297</v>
-      </c>
-      <c r="J61" s="190" t="s">
-        <v>297</v>
-      </c>
+      <c r="A61" s="191"/>
+      <c r="B61" s="191"/>
+      <c r="C61" s="193"/>
+      <c r="D61" s="191"/>
+      <c r="E61" s="191"/>
+      <c r="F61" s="191"/>
+      <c r="G61" s="191"/>
+      <c r="H61" s="191"/>
+      <c r="I61" s="191"/>
+      <c r="J61" s="191"/>
       <c r="K61" s="191"/>
-      <c r="L61" s="190">
-        <v>-8.0</v>
-      </c>
-      <c r="M61" s="190"/>
-      <c r="N61" s="190">
-        <v>6.5148</v>
-      </c>
-      <c r="O61" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P61" s="190" t="s">
-        <v>298</v>
-      </c>
+      <c r="L61" s="191"/>
+      <c r="M61" s="191"/>
+      <c r="N61" s="191"/>
+      <c r="O61" s="191"/>
+      <c r="P61" s="191"/>
       <c r="Q61" s="191"/>
       <c r="R61" s="191"/>
       <c r="S61" s="191"/>
@@ -15805,50 +14315,22 @@
       <c r="AF61" s="191"/>
     </row>
     <row r="62">
-      <c r="A62" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B62" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C62" s="190">
-        <v>329.0</v>
-      </c>
-      <c r="D62" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E62" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F62" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G62" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H62" s="190" t="s">
-        <v>299</v>
-      </c>
-      <c r="I62" s="190" t="s">
-        <v>300</v>
-      </c>
-      <c r="J62" s="190" t="s">
-        <v>300</v>
-      </c>
+      <c r="A62" s="191"/>
+      <c r="B62" s="191"/>
+      <c r="C62" s="191"/>
+      <c r="D62" s="191"/>
+      <c r="E62" s="191"/>
+      <c r="F62" s="191"/>
+      <c r="G62" s="191"/>
+      <c r="H62" s="191"/>
+      <c r="I62" s="191"/>
+      <c r="J62" s="191"/>
       <c r="K62" s="191"/>
-      <c r="L62" s="190">
-        <v>-5.0</v>
-      </c>
-      <c r="M62" s="190"/>
-      <c r="N62" s="190">
-        <v>9.088066666666666</v>
-      </c>
-      <c r="O62" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P62" s="190" t="s">
-        <v>301</v>
-      </c>
+      <c r="L62" s="191"/>
+      <c r="M62" s="191"/>
+      <c r="N62" s="191"/>
+      <c r="O62" s="191"/>
+      <c r="P62" s="191"/>
       <c r="Q62" s="191"/>
       <c r="R62" s="191"/>
       <c r="S62" s="191"/>
@@ -15867,48 +14349,22 @@
       <c r="AF62" s="191"/>
     </row>
     <row r="63">
-      <c r="A63" s="190" t="s">
-        <v>81</v>
-      </c>
-      <c r="B63" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C63" s="190">
-        <v>329.0</v>
-      </c>
-      <c r="D63" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A63" s="191"/>
+      <c r="B63" s="191"/>
+      <c r="C63" s="191"/>
+      <c r="D63" s="191"/>
       <c r="E63" s="191"/>
-      <c r="F63" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G63" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H63" s="190" t="s">
-        <v>302</v>
-      </c>
-      <c r="I63" s="190" t="s">
-        <v>303</v>
-      </c>
-      <c r="J63" s="190" t="s">
-        <v>303</v>
-      </c>
+      <c r="F63" s="191"/>
+      <c r="G63" s="191"/>
+      <c r="H63" s="191"/>
+      <c r="I63" s="191"/>
+      <c r="J63" s="191"/>
       <c r="K63" s="191"/>
-      <c r="L63" s="190">
-        <v>-5.0</v>
-      </c>
-      <c r="M63" s="190"/>
-      <c r="N63" s="190">
-        <v>9.632433333333333</v>
-      </c>
-      <c r="O63" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P63" s="190" t="s">
-        <v>304</v>
-      </c>
+      <c r="L63" s="191"/>
+      <c r="M63" s="191"/>
+      <c r="N63" s="191"/>
+      <c r="O63" s="191"/>
+      <c r="P63" s="191"/>
       <c r="Q63" s="191"/>
       <c r="R63" s="191"/>
       <c r="S63" s="191"/>
@@ -15927,48 +14383,22 @@
       <c r="AF63" s="191"/>
     </row>
     <row r="64">
-      <c r="A64" s="190" t="s">
-        <v>128</v>
-      </c>
-      <c r="B64" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C64" s="190">
-        <v>394.0</v>
-      </c>
-      <c r="D64" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A64" s="191"/>
+      <c r="B64" s="191"/>
+      <c r="C64" s="191"/>
+      <c r="D64" s="191"/>
       <c r="E64" s="191"/>
-      <c r="F64" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G64" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H64" s="190" t="s">
-        <v>305</v>
-      </c>
-      <c r="I64" s="190" t="s">
-        <v>306</v>
-      </c>
-      <c r="J64" s="190" t="s">
-        <v>306</v>
-      </c>
+      <c r="F64" s="191"/>
+      <c r="G64" s="191"/>
+      <c r="H64" s="191"/>
+      <c r="I64" s="191"/>
+      <c r="J64" s="191"/>
       <c r="K64" s="191"/>
-      <c r="L64" s="190">
-        <v>-5.0</v>
-      </c>
-      <c r="M64" s="190"/>
-      <c r="N64" s="190">
-        <v>9.220316666666667</v>
-      </c>
-      <c r="O64" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P64" s="190" t="s">
-        <v>307</v>
-      </c>
+      <c r="L64" s="191"/>
+      <c r="M64" s="191"/>
+      <c r="N64" s="191"/>
+      <c r="O64" s="191"/>
+      <c r="P64" s="191"/>
       <c r="Q64" s="191"/>
       <c r="R64" s="191"/>
       <c r="S64" s="191"/>
@@ -15987,50 +14417,22 @@
       <c r="AF64" s="191"/>
     </row>
     <row r="65">
-      <c r="A65" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B65" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C65" s="192">
-        <v>429.0</v>
-      </c>
-      <c r="D65" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E65" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F65" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G65" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H65" s="190" t="s">
-        <v>308</v>
-      </c>
-      <c r="I65" s="190" t="s">
-        <v>309</v>
-      </c>
-      <c r="J65" s="190" t="s">
-        <v>309</v>
-      </c>
+      <c r="A65" s="191"/>
+      <c r="B65" s="191"/>
+      <c r="C65" s="193"/>
+      <c r="D65" s="191"/>
+      <c r="E65" s="191"/>
+      <c r="F65" s="191"/>
+      <c r="G65" s="191"/>
+      <c r="H65" s="191"/>
+      <c r="I65" s="191"/>
+      <c r="J65" s="191"/>
       <c r="K65" s="191"/>
-      <c r="L65" s="190">
-        <v>-6.0</v>
-      </c>
-      <c r="M65" s="190"/>
-      <c r="N65" s="190">
-        <v>8.861583333333334</v>
-      </c>
-      <c r="O65" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P65" s="190" t="s">
-        <v>310</v>
-      </c>
+      <c r="L65" s="191"/>
+      <c r="M65" s="191"/>
+      <c r="N65" s="191"/>
+      <c r="O65" s="191"/>
+      <c r="P65" s="191"/>
       <c r="Q65" s="191"/>
       <c r="R65" s="191"/>
       <c r="S65" s="191"/>
@@ -16049,48 +14451,22 @@
       <c r="AF65" s="191"/>
     </row>
     <row r="66">
-      <c r="A66" s="190" t="s">
-        <v>128</v>
-      </c>
-      <c r="B66" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C66" s="190">
-        <v>351.0</v>
-      </c>
-      <c r="D66" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A66" s="191"/>
+      <c r="B66" s="191"/>
+      <c r="C66" s="191"/>
+      <c r="D66" s="191"/>
       <c r="E66" s="191"/>
-      <c r="F66" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G66" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H66" s="190" t="s">
-        <v>311</v>
-      </c>
-      <c r="I66" s="190" t="s">
-        <v>312</v>
-      </c>
-      <c r="J66" s="190" t="s">
-        <v>312</v>
-      </c>
+      <c r="F66" s="191"/>
+      <c r="G66" s="191"/>
+      <c r="H66" s="191"/>
+      <c r="I66" s="191"/>
+      <c r="J66" s="191"/>
       <c r="K66" s="191"/>
-      <c r="L66" s="190">
-        <v>-7.0</v>
-      </c>
-      <c r="M66" s="190"/>
-      <c r="N66" s="190">
-        <v>7.174816666666667</v>
-      </c>
-      <c r="O66" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P66" s="190" t="s">
-        <v>313</v>
-      </c>
+      <c r="L66" s="191"/>
+      <c r="M66" s="191"/>
+      <c r="N66" s="191"/>
+      <c r="O66" s="191"/>
+      <c r="P66" s="191"/>
       <c r="Q66" s="191"/>
       <c r="R66" s="191"/>
       <c r="S66" s="191"/>
@@ -16109,54 +14485,22 @@
       <c r="AF66" s="191"/>
     </row>
     <row r="67">
-      <c r="A67" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B67" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C67" s="190">
-        <v>484.0</v>
-      </c>
-      <c r="D67" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E67" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F67" s="190" t="s">
-        <v>167</v>
-      </c>
-      <c r="G67" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H67" s="190" t="s">
-        <v>314</v>
-      </c>
-      <c r="I67" s="190" t="s">
-        <v>315</v>
-      </c>
-      <c r="J67" s="190" t="s">
-        <v>316</v>
-      </c>
-      <c r="K67" s="190" t="s">
-        <v>317</v>
-      </c>
-      <c r="L67" s="190">
-        <v>-21.0</v>
-      </c>
-      <c r="M67" s="190">
-        <v>1.5688333333333333</v>
-      </c>
-      <c r="N67" s="190">
-        <v>11.934466666666667</v>
-      </c>
-      <c r="O67" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P67" s="190" t="s">
-        <v>318</v>
-      </c>
+      <c r="A67" s="191"/>
+      <c r="B67" s="191"/>
+      <c r="C67" s="191"/>
+      <c r="D67" s="191"/>
+      <c r="E67" s="191"/>
+      <c r="F67" s="191"/>
+      <c r="G67" s="191"/>
+      <c r="H67" s="191"/>
+      <c r="I67" s="191"/>
+      <c r="J67" s="191"/>
+      <c r="K67" s="191"/>
+      <c r="L67" s="191"/>
+      <c r="M67" s="191"/>
+      <c r="N67" s="191"/>
+      <c r="O67" s="191"/>
+      <c r="P67" s="191"/>
       <c r="Q67" s="191"/>
       <c r="R67" s="191"/>
       <c r="S67" s="191"/>
@@ -16175,48 +14519,22 @@
       <c r="AF67" s="191"/>
     </row>
     <row r="68">
-      <c r="A68" s="190" t="s">
-        <v>90</v>
-      </c>
-      <c r="B68" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C68" s="190">
-        <v>249.0</v>
-      </c>
-      <c r="D68" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A68" s="191"/>
+      <c r="B68" s="191"/>
+      <c r="C68" s="191"/>
+      <c r="D68" s="191"/>
       <c r="E68" s="191"/>
-      <c r="F68" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G68" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="H68" s="190" t="s">
-        <v>319</v>
-      </c>
-      <c r="I68" s="190" t="s">
-        <v>320</v>
-      </c>
-      <c r="J68" s="190" t="s">
-        <v>320</v>
-      </c>
+      <c r="F68" s="191"/>
+      <c r="G68" s="191"/>
+      <c r="H68" s="191"/>
+      <c r="I68" s="191"/>
+      <c r="J68" s="191"/>
       <c r="K68" s="191"/>
-      <c r="L68" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="M68" s="190"/>
-      <c r="N68" s="190">
-        <v>5.712266666666666</v>
-      </c>
-      <c r="O68" s="190" t="s">
-        <v>95</v>
-      </c>
-      <c r="P68" s="190" t="s">
-        <v>321</v>
-      </c>
+      <c r="L68" s="191"/>
+      <c r="M68" s="191"/>
+      <c r="N68" s="191"/>
+      <c r="O68" s="191"/>
+      <c r="P68" s="191"/>
       <c r="Q68" s="191"/>
       <c r="R68" s="191"/>
       <c r="S68" s="191"/>
@@ -16235,48 +14553,22 @@
       <c r="AF68" s="191"/>
     </row>
     <row r="69">
-      <c r="A69" s="190" t="s">
-        <v>128</v>
-      </c>
-      <c r="B69" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C69" s="190">
-        <v>523.0</v>
-      </c>
-      <c r="D69" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A69" s="191"/>
+      <c r="B69" s="191"/>
+      <c r="C69" s="191"/>
+      <c r="D69" s="191"/>
       <c r="E69" s="191"/>
-      <c r="F69" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G69" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H69" s="190" t="s">
-        <v>322</v>
-      </c>
-      <c r="I69" s="190" t="s">
-        <v>323</v>
-      </c>
-      <c r="J69" s="190" t="s">
-        <v>323</v>
-      </c>
+      <c r="F69" s="191"/>
+      <c r="G69" s="191"/>
+      <c r="H69" s="191"/>
+      <c r="I69" s="191"/>
+      <c r="J69" s="191"/>
       <c r="K69" s="191"/>
-      <c r="L69" s="190">
-        <v>-12.0</v>
-      </c>
-      <c r="M69" s="190"/>
-      <c r="N69" s="190">
-        <v>7.92925</v>
-      </c>
-      <c r="O69" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P69" s="190" t="s">
-        <v>324</v>
-      </c>
+      <c r="L69" s="191"/>
+      <c r="M69" s="191"/>
+      <c r="N69" s="191"/>
+      <c r="O69" s="191"/>
+      <c r="P69" s="191"/>
       <c r="Q69" s="191"/>
       <c r="R69" s="191"/>
       <c r="S69" s="191"/>
@@ -16295,48 +14587,22 @@
       <c r="AF69" s="191"/>
     </row>
     <row r="70">
-      <c r="A70" s="190" t="s">
-        <v>128</v>
-      </c>
-      <c r="B70" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C70" s="192">
-        <v>488.0</v>
-      </c>
-      <c r="D70" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A70" s="191"/>
+      <c r="B70" s="191"/>
+      <c r="C70" s="193"/>
+      <c r="D70" s="191"/>
       <c r="E70" s="191"/>
-      <c r="F70" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G70" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H70" s="190" t="s">
-        <v>325</v>
-      </c>
-      <c r="I70" s="190" t="s">
-        <v>326</v>
-      </c>
-      <c r="J70" s="190" t="s">
-        <v>326</v>
-      </c>
+      <c r="F70" s="191"/>
+      <c r="G70" s="191"/>
+      <c r="H70" s="191"/>
+      <c r="I70" s="191"/>
+      <c r="J70" s="191"/>
       <c r="K70" s="191"/>
-      <c r="L70" s="190">
-        <v>-4.0</v>
-      </c>
-      <c r="M70" s="190"/>
-      <c r="N70" s="190">
-        <v>10.352633333333333</v>
-      </c>
-      <c r="O70" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P70" s="190" t="s">
-        <v>327</v>
-      </c>
+      <c r="L70" s="191"/>
+      <c r="M70" s="191"/>
+      <c r="N70" s="191"/>
+      <c r="O70" s="191"/>
+      <c r="P70" s="191"/>
       <c r="Q70" s="191"/>
       <c r="R70" s="191"/>
       <c r="S70" s="191"/>
@@ -16355,50 +14621,22 @@
       <c r="AF70" s="191"/>
     </row>
     <row r="71">
-      <c r="A71" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B71" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C71" s="190">
-        <v>329.0</v>
-      </c>
-      <c r="D71" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E71" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F71" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G71" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H71" s="190" t="s">
-        <v>328</v>
-      </c>
-      <c r="I71" s="190" t="s">
-        <v>329</v>
-      </c>
-      <c r="J71" s="190" t="s">
-        <v>329</v>
-      </c>
+      <c r="A71" s="191"/>
+      <c r="B71" s="191"/>
+      <c r="C71" s="191"/>
+      <c r="D71" s="191"/>
+      <c r="E71" s="191"/>
+      <c r="F71" s="191"/>
+      <c r="G71" s="191"/>
+      <c r="H71" s="191"/>
+      <c r="I71" s="191"/>
+      <c r="J71" s="191"/>
       <c r="K71" s="191"/>
-      <c r="L71" s="190">
-        <v>-5.0</v>
-      </c>
-      <c r="M71" s="190"/>
-      <c r="N71" s="190">
-        <v>9.424183333333334</v>
-      </c>
-      <c r="O71" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P71" s="190" t="s">
-        <v>274</v>
-      </c>
+      <c r="L71" s="191"/>
+      <c r="M71" s="191"/>
+      <c r="N71" s="191"/>
+      <c r="O71" s="191"/>
+      <c r="P71" s="191"/>
       <c r="Q71" s="191"/>
       <c r="R71" s="191"/>
       <c r="S71" s="191"/>
@@ -16417,48 +14655,22 @@
       <c r="AF71" s="191"/>
     </row>
     <row r="72">
-      <c r="A72" s="190" t="s">
-        <v>128</v>
-      </c>
-      <c r="B72" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C72" s="190">
-        <v>279.0</v>
-      </c>
-      <c r="D72" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A72" s="191"/>
+      <c r="B72" s="191"/>
+      <c r="C72" s="191"/>
+      <c r="D72" s="191"/>
       <c r="E72" s="191"/>
-      <c r="F72" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G72" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H72" s="190" t="s">
-        <v>330</v>
-      </c>
-      <c r="I72" s="190" t="s">
-        <v>331</v>
-      </c>
-      <c r="J72" s="190" t="s">
-        <v>331</v>
-      </c>
+      <c r="F72" s="191"/>
+      <c r="G72" s="191"/>
+      <c r="H72" s="191"/>
+      <c r="I72" s="191"/>
+      <c r="J72" s="191"/>
       <c r="K72" s="191"/>
-      <c r="L72" s="190">
-        <v>-4.0</v>
-      </c>
-      <c r="M72" s="190"/>
-      <c r="N72" s="190">
-        <v>10.806833333333334</v>
-      </c>
-      <c r="O72" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P72" s="190" t="s">
-        <v>332</v>
-      </c>
+      <c r="L72" s="191"/>
+      <c r="M72" s="191"/>
+      <c r="N72" s="191"/>
+      <c r="O72" s="191"/>
+      <c r="P72" s="191"/>
       <c r="Q72" s="191"/>
       <c r="R72" s="191"/>
       <c r="S72" s="191"/>
@@ -16477,54 +14689,22 @@
       <c r="AF72" s="191"/>
     </row>
     <row r="73">
-      <c r="A73" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B73" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C73" s="190">
-        <v>414.0</v>
-      </c>
-      <c r="D73" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E73" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F73" s="190" t="s">
-        <v>167</v>
-      </c>
-      <c r="G73" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H73" s="190" t="s">
-        <v>333</v>
-      </c>
-      <c r="I73" s="190" t="s">
-        <v>334</v>
-      </c>
-      <c r="J73" s="190" t="s">
-        <v>335</v>
-      </c>
-      <c r="K73" s="190" t="s">
-        <v>336</v>
-      </c>
-      <c r="L73" s="190">
-        <v>-12.0</v>
-      </c>
-      <c r="M73" s="190">
-        <v>0.2919333333333333</v>
-      </c>
-      <c r="N73" s="190">
-        <v>12.1349</v>
-      </c>
-      <c r="O73" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P73" s="190" t="s">
-        <v>337</v>
-      </c>
+      <c r="A73" s="191"/>
+      <c r="B73" s="191"/>
+      <c r="C73" s="191"/>
+      <c r="D73" s="191"/>
+      <c r="E73" s="191"/>
+      <c r="F73" s="191"/>
+      <c r="G73" s="191"/>
+      <c r="H73" s="191"/>
+      <c r="I73" s="191"/>
+      <c r="J73" s="191"/>
+      <c r="K73" s="191"/>
+      <c r="L73" s="191"/>
+      <c r="M73" s="191"/>
+      <c r="N73" s="191"/>
+      <c r="O73" s="191"/>
+      <c r="P73" s="191"/>
       <c r="Q73" s="191"/>
       <c r="R73" s="191"/>
       <c r="S73" s="191"/>
@@ -16543,48 +14723,22 @@
       <c r="AF73" s="191"/>
     </row>
     <row r="74">
-      <c r="A74" s="190" t="s">
-        <v>90</v>
-      </c>
-      <c r="B74" s="192" t="s">
-        <v>82</v>
-      </c>
-      <c r="C74" s="192">
-        <v>309.0</v>
-      </c>
-      <c r="D74" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A74" s="191"/>
+      <c r="B74" s="193"/>
+      <c r="C74" s="193"/>
+      <c r="D74" s="191"/>
       <c r="E74" s="191"/>
-      <c r="F74" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G74" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="H74" s="190" t="s">
-        <v>338</v>
-      </c>
-      <c r="I74" s="190" t="s">
-        <v>339</v>
-      </c>
-      <c r="J74" s="190" t="s">
-        <v>339</v>
-      </c>
+      <c r="F74" s="191"/>
+      <c r="G74" s="191"/>
+      <c r="H74" s="191"/>
+      <c r="I74" s="191"/>
+      <c r="J74" s="191"/>
       <c r="K74" s="191"/>
-      <c r="L74" s="190">
-        <v>1.0</v>
-      </c>
-      <c r="M74" s="190"/>
-      <c r="N74" s="190">
-        <v>6.06325</v>
-      </c>
-      <c r="O74" s="190" t="s">
-        <v>95</v>
-      </c>
-      <c r="P74" s="190" t="s">
-        <v>340</v>
-      </c>
+      <c r="L74" s="191"/>
+      <c r="M74" s="191"/>
+      <c r="N74" s="191"/>
+      <c r="O74" s="191"/>
+      <c r="P74" s="191"/>
       <c r="Q74" s="191"/>
       <c r="R74" s="191"/>
       <c r="S74" s="191"/>
@@ -16603,54 +14757,22 @@
       <c r="AF74" s="191"/>
     </row>
     <row r="75">
-      <c r="A75" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B75" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C75" s="190">
-        <v>527.0</v>
-      </c>
-      <c r="D75" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E75" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F75" s="190" t="s">
-        <v>167</v>
-      </c>
-      <c r="G75" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H75" s="190" t="s">
-        <v>341</v>
-      </c>
-      <c r="I75" s="190" t="s">
-        <v>342</v>
-      </c>
-      <c r="J75" s="190" t="s">
-        <v>343</v>
-      </c>
-      <c r="K75" s="190" t="s">
-        <v>344</v>
-      </c>
-      <c r="L75" s="190">
-        <v>-8.0</v>
-      </c>
-      <c r="M75" s="190">
-        <v>0.8549833333333333</v>
-      </c>
-      <c r="N75" s="190">
-        <v>9.361083333333333</v>
-      </c>
-      <c r="O75" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P75" s="190" t="s">
-        <v>345</v>
-      </c>
+      <c r="A75" s="191"/>
+      <c r="B75" s="191"/>
+      <c r="C75" s="191"/>
+      <c r="D75" s="191"/>
+      <c r="E75" s="191"/>
+      <c r="F75" s="191"/>
+      <c r="G75" s="191"/>
+      <c r="H75" s="191"/>
+      <c r="I75" s="191"/>
+      <c r="J75" s="191"/>
+      <c r="K75" s="191"/>
+      <c r="L75" s="191"/>
+      <c r="M75" s="191"/>
+      <c r="N75" s="191"/>
+      <c r="O75" s="191"/>
+      <c r="P75" s="191"/>
       <c r="Q75" s="191"/>
       <c r="R75" s="191"/>
       <c r="S75" s="191"/>
@@ -16669,48 +14791,22 @@
       <c r="AF75" s="191"/>
     </row>
     <row r="76">
-      <c r="A76" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B76" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C76" s="190">
-        <v>302.0</v>
-      </c>
-      <c r="D76" s="190">
-        <v>56.0</v>
-      </c>
+      <c r="A76" s="191"/>
+      <c r="B76" s="191"/>
+      <c r="C76" s="191"/>
+      <c r="D76" s="191"/>
       <c r="E76" s="191"/>
-      <c r="F76" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G76" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H76" s="190" t="s">
-        <v>346</v>
-      </c>
-      <c r="I76" s="190" t="s">
-        <v>347</v>
-      </c>
-      <c r="J76" s="190" t="s">
-        <v>347</v>
-      </c>
+      <c r="F76" s="191"/>
+      <c r="G76" s="191"/>
+      <c r="H76" s="191"/>
+      <c r="I76" s="191"/>
+      <c r="J76" s="191"/>
       <c r="K76" s="191"/>
-      <c r="L76" s="190">
-        <v>-7.0</v>
-      </c>
-      <c r="M76" s="190"/>
-      <c r="N76" s="190">
-        <v>11.505266666666667</v>
-      </c>
-      <c r="O76" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P76" s="190" t="s">
-        <v>348</v>
-      </c>
+      <c r="L76" s="191"/>
+      <c r="M76" s="191"/>
+      <c r="N76" s="191"/>
+      <c r="O76" s="191"/>
+      <c r="P76" s="191"/>
       <c r="Q76" s="191"/>
       <c r="R76" s="191"/>
       <c r="S76" s="191"/>
@@ -16729,50 +14825,22 @@
       <c r="AF76" s="191"/>
     </row>
     <row r="77">
-      <c r="A77" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B77" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C77" s="192">
-        <v>698.0</v>
-      </c>
-      <c r="D77" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E77" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F77" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G77" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H77" s="190" t="s">
-        <v>349</v>
-      </c>
-      <c r="I77" s="190" t="s">
-        <v>350</v>
-      </c>
-      <c r="J77" s="190" t="s">
-        <v>350</v>
-      </c>
+      <c r="A77" s="191"/>
+      <c r="B77" s="191"/>
+      <c r="C77" s="193"/>
+      <c r="D77" s="191"/>
+      <c r="E77" s="191"/>
+      <c r="F77" s="191"/>
+      <c r="G77" s="191"/>
+      <c r="H77" s="191"/>
+      <c r="I77" s="191"/>
+      <c r="J77" s="191"/>
       <c r="K77" s="191"/>
-      <c r="L77" s="190">
-        <v>-11.0</v>
-      </c>
-      <c r="M77" s="190"/>
-      <c r="N77" s="190">
-        <v>8.828316666666666</v>
-      </c>
-      <c r="O77" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P77" s="190" t="s">
-        <v>351</v>
-      </c>
+      <c r="L77" s="191"/>
+      <c r="M77" s="191"/>
+      <c r="N77" s="191"/>
+      <c r="O77" s="191"/>
+      <c r="P77" s="191"/>
       <c r="Q77" s="191"/>
       <c r="R77" s="191"/>
       <c r="S77" s="191"/>
@@ -16791,48 +14859,22 @@
       <c r="AF77" s="191"/>
     </row>
     <row r="78">
-      <c r="A78" s="190" t="s">
-        <v>128</v>
-      </c>
-      <c r="B78" s="190" t="s">
-        <v>232</v>
-      </c>
-      <c r="C78" s="190">
-        <v>388.0</v>
-      </c>
-      <c r="D78" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A78" s="191"/>
+      <c r="B78" s="191"/>
+      <c r="C78" s="191"/>
+      <c r="D78" s="191"/>
       <c r="E78" s="191"/>
-      <c r="F78" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G78" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H78" s="190" t="s">
-        <v>352</v>
-      </c>
-      <c r="I78" s="190" t="s">
-        <v>353</v>
-      </c>
-      <c r="J78" s="190" t="s">
-        <v>353</v>
-      </c>
+      <c r="F78" s="191"/>
+      <c r="G78" s="191"/>
+      <c r="H78" s="191"/>
+      <c r="I78" s="191"/>
+      <c r="J78" s="191"/>
       <c r="K78" s="191"/>
-      <c r="L78" s="190">
-        <v>-6.0</v>
-      </c>
-      <c r="M78" s="190"/>
-      <c r="N78" s="190">
-        <v>8.77465</v>
-      </c>
-      <c r="O78" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P78" s="190" t="s">
-        <v>354</v>
-      </c>
+      <c r="L78" s="191"/>
+      <c r="M78" s="191"/>
+      <c r="N78" s="191"/>
+      <c r="O78" s="191"/>
+      <c r="P78" s="191"/>
       <c r="Q78" s="191"/>
       <c r="R78" s="191"/>
       <c r="S78" s="191"/>
@@ -16851,50 +14893,22 @@
       <c r="AF78" s="191"/>
     </row>
     <row r="79">
-      <c r="A79" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B79" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C79" s="190">
-        <v>612.0</v>
-      </c>
-      <c r="D79" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E79" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F79" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G79" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H79" s="190" t="s">
-        <v>355</v>
-      </c>
-      <c r="I79" s="190" t="s">
-        <v>356</v>
-      </c>
-      <c r="J79" s="190" t="s">
-        <v>356</v>
-      </c>
+      <c r="A79" s="191"/>
+      <c r="B79" s="191"/>
+      <c r="C79" s="191"/>
+      <c r="D79" s="191"/>
+      <c r="E79" s="191"/>
+      <c r="F79" s="191"/>
+      <c r="G79" s="191"/>
+      <c r="H79" s="191"/>
+      <c r="I79" s="191"/>
+      <c r="J79" s="191"/>
       <c r="K79" s="191"/>
-      <c r="L79" s="190">
-        <v>-7.0</v>
-      </c>
-      <c r="M79" s="190"/>
-      <c r="N79" s="190">
-        <v>12.867133333333333</v>
-      </c>
-      <c r="O79" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P79" s="190" t="s">
-        <v>357</v>
-      </c>
+      <c r="L79" s="191"/>
+      <c r="M79" s="191"/>
+      <c r="N79" s="191"/>
+      <c r="O79" s="191"/>
+      <c r="P79" s="191"/>
       <c r="Q79" s="191"/>
       <c r="R79" s="191"/>
       <c r="S79" s="191"/>
@@ -16913,50 +14927,22 @@
       <c r="AF79" s="191"/>
     </row>
     <row r="80">
-      <c r="A80" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B80" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C80" s="192">
-        <v>329.0</v>
-      </c>
-      <c r="D80" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E80" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F80" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G80" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H80" s="190" t="s">
-        <v>358</v>
-      </c>
-      <c r="I80" s="190" t="s">
-        <v>359</v>
-      </c>
-      <c r="J80" s="190" t="s">
-        <v>359</v>
-      </c>
+      <c r="A80" s="191"/>
+      <c r="B80" s="191"/>
+      <c r="C80" s="193"/>
+      <c r="D80" s="191"/>
+      <c r="E80" s="191"/>
+      <c r="F80" s="191"/>
+      <c r="G80" s="191"/>
+      <c r="H80" s="191"/>
+      <c r="I80" s="191"/>
+      <c r="J80" s="191"/>
       <c r="K80" s="191"/>
-      <c r="L80" s="190">
-        <v>-10.0</v>
-      </c>
-      <c r="M80" s="190"/>
-      <c r="N80" s="190">
-        <v>9.505916666666666</v>
-      </c>
-      <c r="O80" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P80" s="190" t="s">
-        <v>301</v>
-      </c>
+      <c r="L80" s="191"/>
+      <c r="M80" s="191"/>
+      <c r="N80" s="191"/>
+      <c r="O80" s="191"/>
+      <c r="P80" s="191"/>
       <c r="Q80" s="191"/>
       <c r="R80" s="191"/>
       <c r="S80" s="191"/>
@@ -16975,50 +14961,22 @@
       <c r="AF80" s="191"/>
     </row>
     <row r="81">
-      <c r="A81" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B81" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C81" s="190">
-        <v>311.0</v>
-      </c>
-      <c r="D81" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E81" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F81" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G81" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H81" s="190" t="s">
-        <v>360</v>
-      </c>
-      <c r="I81" s="190" t="s">
-        <v>361</v>
-      </c>
-      <c r="J81" s="190" t="s">
-        <v>361</v>
-      </c>
+      <c r="A81" s="191"/>
+      <c r="B81" s="191"/>
+      <c r="C81" s="191"/>
+      <c r="D81" s="191"/>
+      <c r="E81" s="191"/>
+      <c r="F81" s="191"/>
+      <c r="G81" s="191"/>
+      <c r="H81" s="191"/>
+      <c r="I81" s="191"/>
+      <c r="J81" s="191"/>
       <c r="K81" s="191"/>
-      <c r="L81" s="190">
-        <v>-3.0</v>
-      </c>
-      <c r="M81" s="190"/>
-      <c r="N81" s="190">
-        <v>11.203816666666667</v>
-      </c>
-      <c r="O81" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P81" s="190" t="s">
-        <v>362</v>
-      </c>
+      <c r="L81" s="191"/>
+      <c r="M81" s="191"/>
+      <c r="N81" s="191"/>
+      <c r="O81" s="191"/>
+      <c r="P81" s="191"/>
       <c r="Q81" s="191"/>
       <c r="R81" s="191"/>
       <c r="S81" s="191"/>
@@ -17037,50 +14995,22 @@
       <c r="AF81" s="191"/>
     </row>
     <row r="82">
-      <c r="A82" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B82" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C82" s="192">
-        <v>429.0</v>
-      </c>
-      <c r="D82" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E82" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F82" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G82" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H82" s="190" t="s">
-        <v>363</v>
-      </c>
-      <c r="I82" s="190" t="s">
-        <v>364</v>
-      </c>
-      <c r="J82" s="190" t="s">
-        <v>364</v>
-      </c>
+      <c r="A82" s="191"/>
+      <c r="B82" s="191"/>
+      <c r="C82" s="193"/>
+      <c r="D82" s="191"/>
+      <c r="E82" s="191"/>
+      <c r="F82" s="191"/>
+      <c r="G82" s="191"/>
+      <c r="H82" s="191"/>
+      <c r="I82" s="191"/>
+      <c r="J82" s="191"/>
       <c r="K82" s="191"/>
-      <c r="L82" s="190">
-        <v>-3.0</v>
-      </c>
-      <c r="M82" s="190"/>
-      <c r="N82" s="190">
-        <v>11.620533333333332</v>
-      </c>
-      <c r="O82" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P82" s="190" t="s">
-        <v>365</v>
-      </c>
+      <c r="L82" s="191"/>
+      <c r="M82" s="191"/>
+      <c r="N82" s="191"/>
+      <c r="O82" s="191"/>
+      <c r="P82" s="191"/>
       <c r="Q82" s="191"/>
       <c r="R82" s="191"/>
       <c r="S82" s="191"/>
@@ -17099,50 +15029,22 @@
       <c r="AF82" s="191"/>
     </row>
     <row r="83">
-      <c r="A83" s="190" t="s">
-        <v>81</v>
-      </c>
-      <c r="B83" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C83" s="190">
-        <v>364.0</v>
-      </c>
-      <c r="D83" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E83" s="190" t="s">
-        <v>366</v>
-      </c>
-      <c r="F83" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G83" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H83" s="190" t="s">
-        <v>367</v>
-      </c>
-      <c r="I83" s="190" t="s">
-        <v>368</v>
-      </c>
-      <c r="J83" s="190" t="s">
-        <v>368</v>
-      </c>
+      <c r="A83" s="191"/>
+      <c r="B83" s="191"/>
+      <c r="C83" s="191"/>
+      <c r="D83" s="191"/>
+      <c r="E83" s="191"/>
+      <c r="F83" s="191"/>
+      <c r="G83" s="191"/>
+      <c r="H83" s="191"/>
+      <c r="I83" s="191"/>
+      <c r="J83" s="191"/>
       <c r="K83" s="191"/>
-      <c r="L83" s="190">
-        <v>-7.0</v>
-      </c>
-      <c r="M83" s="190"/>
-      <c r="N83" s="190">
-        <v>7.62645</v>
-      </c>
-      <c r="O83" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P83" s="190" t="s">
-        <v>369</v>
-      </c>
+      <c r="L83" s="191"/>
+      <c r="M83" s="191"/>
+      <c r="N83" s="191"/>
+      <c r="O83" s="191"/>
+      <c r="P83" s="191"/>
       <c r="Q83" s="191"/>
       <c r="R83" s="191"/>
       <c r="S83" s="191"/>
@@ -17161,50 +15063,22 @@
       <c r="AF83" s="191"/>
     </row>
     <row r="84">
-      <c r="A84" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B84" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C84" s="192">
-        <v>364.0</v>
-      </c>
-      <c r="D84" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E84" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F84" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G84" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H84" s="190" t="s">
-        <v>370</v>
-      </c>
-      <c r="I84" s="190" t="s">
-        <v>371</v>
-      </c>
-      <c r="J84" s="190" t="s">
-        <v>371</v>
-      </c>
+      <c r="A84" s="191"/>
+      <c r="B84" s="191"/>
+      <c r="C84" s="193"/>
+      <c r="D84" s="191"/>
+      <c r="E84" s="191"/>
+      <c r="F84" s="191"/>
+      <c r="G84" s="191"/>
+      <c r="H84" s="191"/>
+      <c r="I84" s="191"/>
+      <c r="J84" s="191"/>
       <c r="K84" s="191"/>
-      <c r="L84" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="M84" s="190"/>
-      <c r="N84" s="190">
-        <v>20.1665</v>
-      </c>
-      <c r="O84" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P84" s="190" t="s">
-        <v>372</v>
-      </c>
+      <c r="L84" s="191"/>
+      <c r="M84" s="191"/>
+      <c r="N84" s="191"/>
+      <c r="O84" s="191"/>
+      <c r="P84" s="191"/>
       <c r="Q84" s="191"/>
       <c r="R84" s="191"/>
       <c r="S84" s="191"/>
@@ -17223,50 +15097,22 @@
       <c r="AF84" s="191"/>
     </row>
     <row r="85">
-      <c r="A85" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B85" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C85" s="192">
-        <v>394.0</v>
-      </c>
-      <c r="D85" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E85" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F85" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G85" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H85" s="190" t="s">
-        <v>373</v>
-      </c>
-      <c r="I85" s="190" t="s">
-        <v>374</v>
-      </c>
-      <c r="J85" s="190" t="s">
-        <v>374</v>
-      </c>
+      <c r="A85" s="191"/>
+      <c r="B85" s="191"/>
+      <c r="C85" s="193"/>
+      <c r="D85" s="191"/>
+      <c r="E85" s="191"/>
+      <c r="F85" s="191"/>
+      <c r="G85" s="191"/>
+      <c r="H85" s="191"/>
+      <c r="I85" s="191"/>
+      <c r="J85" s="191"/>
       <c r="K85" s="191"/>
-      <c r="L85" s="190">
-        <v>-4.0</v>
-      </c>
-      <c r="M85" s="190"/>
-      <c r="N85" s="190">
-        <v>10.10025</v>
-      </c>
-      <c r="O85" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P85" s="190" t="s">
-        <v>375</v>
-      </c>
+      <c r="L85" s="191"/>
+      <c r="M85" s="191"/>
+      <c r="N85" s="191"/>
+      <c r="O85" s="191"/>
+      <c r="P85" s="191"/>
       <c r="Q85" s="191"/>
       <c r="R85" s="191"/>
       <c r="S85" s="191"/>
@@ -17285,50 +15131,22 @@
       <c r="AF85" s="191"/>
     </row>
     <row r="86">
-      <c r="A86" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B86" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C86" s="190">
-        <v>329.0</v>
-      </c>
-      <c r="D86" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E86" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F86" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G86" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H86" s="190" t="s">
-        <v>376</v>
-      </c>
-      <c r="I86" s="190" t="s">
-        <v>377</v>
-      </c>
-      <c r="J86" s="190" t="s">
-        <v>377</v>
-      </c>
+      <c r="A86" s="191"/>
+      <c r="B86" s="191"/>
+      <c r="C86" s="191"/>
+      <c r="D86" s="191"/>
+      <c r="E86" s="191"/>
+      <c r="F86" s="191"/>
+      <c r="G86" s="191"/>
+      <c r="H86" s="191"/>
+      <c r="I86" s="191"/>
+      <c r="J86" s="191"/>
       <c r="K86" s="191"/>
-      <c r="L86" s="190">
-        <v>-6.0</v>
-      </c>
-      <c r="M86" s="190"/>
-      <c r="N86" s="190">
-        <v>8.120916666666666</v>
-      </c>
-      <c r="O86" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P86" s="190" t="s">
-        <v>378</v>
-      </c>
+      <c r="L86" s="191"/>
+      <c r="M86" s="191"/>
+      <c r="N86" s="191"/>
+      <c r="O86" s="191"/>
+      <c r="P86" s="191"/>
       <c r="Q86" s="191"/>
       <c r="R86" s="191"/>
       <c r="S86" s="191"/>
@@ -17347,48 +15165,22 @@
       <c r="AF86" s="191"/>
     </row>
     <row r="87">
-      <c r="A87" s="190" t="s">
-        <v>90</v>
-      </c>
-      <c r="B87" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C87" s="190">
-        <v>309.0</v>
-      </c>
-      <c r="D87" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A87" s="191"/>
+      <c r="B87" s="191"/>
+      <c r="C87" s="191"/>
+      <c r="D87" s="191"/>
       <c r="E87" s="191"/>
-      <c r="F87" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G87" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="H87" s="190" t="s">
-        <v>379</v>
-      </c>
-      <c r="I87" s="190" t="s">
-        <v>380</v>
-      </c>
-      <c r="J87" s="190" t="s">
-        <v>380</v>
-      </c>
+      <c r="F87" s="191"/>
+      <c r="G87" s="191"/>
+      <c r="H87" s="191"/>
+      <c r="I87" s="191"/>
+      <c r="J87" s="191"/>
       <c r="K87" s="191"/>
-      <c r="L87" s="190">
-        <v>4.0</v>
-      </c>
-      <c r="M87" s="190"/>
-      <c r="N87" s="190">
-        <v>9.356333333333334</v>
-      </c>
-      <c r="O87" s="190" t="s">
-        <v>95</v>
-      </c>
-      <c r="P87" s="190" t="s">
-        <v>381</v>
-      </c>
+      <c r="L87" s="191"/>
+      <c r="M87" s="191"/>
+      <c r="N87" s="191"/>
+      <c r="O87" s="191"/>
+      <c r="P87" s="191"/>
       <c r="Q87" s="191"/>
       <c r="R87" s="191"/>
       <c r="S87" s="191"/>
@@ -17407,50 +15199,22 @@
       <c r="AF87" s="191"/>
     </row>
     <row r="88">
-      <c r="A88" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B88" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C88" s="190">
-        <v>369.0</v>
-      </c>
-      <c r="D88" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E88" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F88" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G88" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H88" s="190" t="s">
-        <v>382</v>
-      </c>
-      <c r="I88" s="190" t="s">
-        <v>383</v>
-      </c>
-      <c r="J88" s="190" t="s">
-        <v>383</v>
-      </c>
+      <c r="A88" s="191"/>
+      <c r="B88" s="191"/>
+      <c r="C88" s="191"/>
+      <c r="D88" s="191"/>
+      <c r="E88" s="191"/>
+      <c r="F88" s="191"/>
+      <c r="G88" s="191"/>
+      <c r="H88" s="191"/>
+      <c r="I88" s="191"/>
+      <c r="J88" s="191"/>
       <c r="K88" s="191"/>
-      <c r="L88" s="190">
-        <v>-3.0</v>
-      </c>
-      <c r="M88" s="190"/>
-      <c r="N88" s="190">
-        <v>11.8426</v>
-      </c>
-      <c r="O88" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P88" s="190" t="s">
-        <v>384</v>
-      </c>
+      <c r="L88" s="191"/>
+      <c r="M88" s="191"/>
+      <c r="N88" s="191"/>
+      <c r="O88" s="191"/>
+      <c r="P88" s="191"/>
       <c r="Q88" s="191"/>
       <c r="R88" s="191"/>
       <c r="S88" s="191"/>
@@ -17469,48 +15233,22 @@
       <c r="AF88" s="191"/>
     </row>
     <row r="89">
-      <c r="A89" s="190" t="s">
-        <v>90</v>
-      </c>
-      <c r="B89" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C89" s="192">
-        <v>996.0</v>
-      </c>
-      <c r="D89" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A89" s="191"/>
+      <c r="B89" s="191"/>
+      <c r="C89" s="193"/>
+      <c r="D89" s="191"/>
       <c r="E89" s="191"/>
-      <c r="F89" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G89" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="H89" s="190" t="s">
-        <v>385</v>
-      </c>
-      <c r="I89" s="190" t="s">
-        <v>386</v>
-      </c>
-      <c r="J89" s="190" t="s">
-        <v>386</v>
-      </c>
+      <c r="F89" s="191"/>
+      <c r="G89" s="191"/>
+      <c r="H89" s="191"/>
+      <c r="I89" s="191"/>
+      <c r="J89" s="191"/>
       <c r="K89" s="191"/>
-      <c r="L89" s="190">
-        <v>4.0</v>
-      </c>
-      <c r="M89" s="190"/>
-      <c r="N89" s="190">
-        <v>14.44215</v>
-      </c>
-      <c r="O89" s="190" t="s">
-        <v>95</v>
-      </c>
-      <c r="P89" s="190" t="s">
-        <v>387</v>
-      </c>
+      <c r="L89" s="191"/>
+      <c r="M89" s="191"/>
+      <c r="N89" s="191"/>
+      <c r="O89" s="191"/>
+      <c r="P89" s="191"/>
       <c r="Q89" s="191"/>
       <c r="R89" s="191"/>
       <c r="S89" s="191"/>
@@ -17529,48 +15267,22 @@
       <c r="AF89" s="191"/>
     </row>
     <row r="90">
-      <c r="A90" s="190" t="s">
-        <v>90</v>
-      </c>
-      <c r="B90" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C90" s="192">
-        <v>558.0</v>
-      </c>
-      <c r="D90" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A90" s="191"/>
+      <c r="B90" s="191"/>
+      <c r="C90" s="193"/>
+      <c r="D90" s="191"/>
       <c r="E90" s="191"/>
-      <c r="F90" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G90" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="H90" s="190" t="s">
-        <v>388</v>
-      </c>
-      <c r="I90" s="190" t="s">
-        <v>389</v>
-      </c>
-      <c r="J90" s="190" t="s">
-        <v>389</v>
-      </c>
+      <c r="F90" s="191"/>
+      <c r="G90" s="191"/>
+      <c r="H90" s="191"/>
+      <c r="I90" s="191"/>
+      <c r="J90" s="191"/>
       <c r="K90" s="191"/>
-      <c r="L90" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="M90" s="190"/>
-      <c r="N90" s="190">
-        <v>10.554233333333332</v>
-      </c>
-      <c r="O90" s="190" t="s">
-        <v>95</v>
-      </c>
-      <c r="P90" s="190" t="s">
-        <v>390</v>
-      </c>
+      <c r="L90" s="191"/>
+      <c r="M90" s="191"/>
+      <c r="N90" s="191"/>
+      <c r="O90" s="191"/>
+      <c r="P90" s="191"/>
       <c r="Q90" s="191"/>
       <c r="R90" s="191"/>
       <c r="S90" s="191"/>
@@ -17589,48 +15301,22 @@
       <c r="AF90" s="191"/>
     </row>
     <row r="91">
-      <c r="A91" s="190" t="s">
-        <v>90</v>
-      </c>
-      <c r="B91" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C91" s="190">
-        <v>498.0</v>
-      </c>
-      <c r="D91" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A91" s="191"/>
+      <c r="B91" s="191"/>
+      <c r="C91" s="191"/>
+      <c r="D91" s="191"/>
       <c r="E91" s="191"/>
-      <c r="F91" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G91" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="H91" s="190" t="s">
-        <v>391</v>
-      </c>
-      <c r="I91" s="190" t="s">
-        <v>392</v>
-      </c>
-      <c r="J91" s="190" t="s">
-        <v>392</v>
-      </c>
+      <c r="F91" s="191"/>
+      <c r="G91" s="191"/>
+      <c r="H91" s="191"/>
+      <c r="I91" s="191"/>
+      <c r="J91" s="191"/>
       <c r="K91" s="191"/>
-      <c r="L91" s="190">
-        <v>2.0</v>
-      </c>
-      <c r="M91" s="190"/>
-      <c r="N91" s="190">
-        <v>7.382883333333333</v>
-      </c>
-      <c r="O91" s="190" t="s">
-        <v>95</v>
-      </c>
-      <c r="P91" s="190" t="s">
-        <v>393</v>
-      </c>
+      <c r="L91" s="191"/>
+      <c r="M91" s="191"/>
+      <c r="N91" s="191"/>
+      <c r="O91" s="191"/>
+      <c r="P91" s="191"/>
       <c r="Q91" s="191"/>
       <c r="R91" s="191"/>
       <c r="S91" s="191"/>
@@ -17649,54 +15335,22 @@
       <c r="AF91" s="191"/>
     </row>
     <row r="92">
-      <c r="A92" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B92" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C92" s="190">
-        <v>802.0</v>
-      </c>
-      <c r="D92" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E92" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F92" s="190" t="s">
-        <v>167</v>
-      </c>
-      <c r="G92" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H92" s="190" t="s">
-        <v>394</v>
-      </c>
-      <c r="I92" s="190" t="s">
-        <v>395</v>
-      </c>
-      <c r="J92" s="190" t="s">
-        <v>396</v>
-      </c>
-      <c r="K92" s="190" t="s">
-        <v>397</v>
-      </c>
-      <c r="L92" s="190">
-        <v>-3.0</v>
-      </c>
-      <c r="M92" s="190">
-        <v>4.4769</v>
-      </c>
-      <c r="N92" s="190">
-        <v>13.474</v>
-      </c>
-      <c r="O92" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P92" s="190" t="s">
-        <v>398</v>
-      </c>
+      <c r="A92" s="191"/>
+      <c r="B92" s="191"/>
+      <c r="C92" s="191"/>
+      <c r="D92" s="191"/>
+      <c r="E92" s="191"/>
+      <c r="F92" s="191"/>
+      <c r="G92" s="191"/>
+      <c r="H92" s="191"/>
+      <c r="I92" s="191"/>
+      <c r="J92" s="191"/>
+      <c r="K92" s="191"/>
+      <c r="L92" s="191"/>
+      <c r="M92" s="191"/>
+      <c r="N92" s="191"/>
+      <c r="O92" s="191"/>
+      <c r="P92" s="191"/>
       <c r="Q92" s="191"/>
       <c r="R92" s="191"/>
       <c r="S92" s="191"/>
@@ -17715,50 +15369,22 @@
       <c r="AF92" s="191"/>
     </row>
     <row r="93">
-      <c r="A93" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B93" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C93" s="192">
-        <v>394.0</v>
-      </c>
-      <c r="D93" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E93" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F93" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G93" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H93" s="190" t="s">
-        <v>399</v>
-      </c>
-      <c r="I93" s="190" t="s">
-        <v>400</v>
-      </c>
-      <c r="J93" s="190" t="s">
-        <v>400</v>
-      </c>
+      <c r="A93" s="191"/>
+      <c r="B93" s="191"/>
+      <c r="C93" s="193"/>
+      <c r="D93" s="191"/>
+      <c r="E93" s="191"/>
+      <c r="F93" s="191"/>
+      <c r="G93" s="191"/>
+      <c r="H93" s="191"/>
+      <c r="I93" s="191"/>
+      <c r="J93" s="191"/>
       <c r="K93" s="191"/>
-      <c r="L93" s="190">
-        <v>-3.0</v>
-      </c>
-      <c r="M93" s="190"/>
-      <c r="N93" s="190">
-        <v>12.414166666666667</v>
-      </c>
-      <c r="O93" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P93" s="190" t="s">
-        <v>401</v>
-      </c>
+      <c r="L93" s="191"/>
+      <c r="M93" s="191"/>
+      <c r="N93" s="191"/>
+      <c r="O93" s="191"/>
+      <c r="P93" s="191"/>
       <c r="Q93" s="191"/>
       <c r="R93" s="191"/>
       <c r="S93" s="191"/>
@@ -17777,48 +15403,22 @@
       <c r="AF93" s="191"/>
     </row>
     <row r="94">
-      <c r="A94" s="190" t="s">
-        <v>128</v>
-      </c>
-      <c r="B94" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C94" s="190">
-        <v>329.0</v>
-      </c>
-      <c r="D94" s="190">
-        <v>0.0</v>
-      </c>
+      <c r="A94" s="191"/>
+      <c r="B94" s="191"/>
+      <c r="C94" s="191"/>
+      <c r="D94" s="191"/>
       <c r="E94" s="191"/>
-      <c r="F94" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G94" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H94" s="190" t="s">
-        <v>402</v>
-      </c>
-      <c r="I94" s="190" t="s">
-        <v>403</v>
-      </c>
-      <c r="J94" s="190" t="s">
-        <v>403</v>
-      </c>
+      <c r="F94" s="191"/>
+      <c r="G94" s="191"/>
+      <c r="H94" s="191"/>
+      <c r="I94" s="191"/>
+      <c r="J94" s="191"/>
       <c r="K94" s="191"/>
-      <c r="L94" s="190">
-        <v>-8.0</v>
-      </c>
-      <c r="M94" s="190"/>
-      <c r="N94" s="190">
-        <v>6.5468166666666665</v>
-      </c>
-      <c r="O94" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P94" s="190" t="s">
-        <v>404</v>
-      </c>
+      <c r="L94" s="191"/>
+      <c r="M94" s="191"/>
+      <c r="N94" s="191"/>
+      <c r="O94" s="191"/>
+      <c r="P94" s="191"/>
       <c r="Q94" s="191"/>
       <c r="R94" s="191"/>
       <c r="S94" s="191"/>
@@ -17837,50 +15437,22 @@
       <c r="AF94" s="191"/>
     </row>
     <row r="95">
-      <c r="A95" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B95" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C95" s="190">
-        <v>333.0</v>
-      </c>
-      <c r="D95" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E95" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F95" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G95" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H95" s="190" t="s">
-        <v>405</v>
-      </c>
-      <c r="I95" s="190" t="s">
-        <v>406</v>
-      </c>
-      <c r="J95" s="190" t="s">
-        <v>406</v>
-      </c>
+      <c r="A95" s="191"/>
+      <c r="B95" s="191"/>
+      <c r="C95" s="191"/>
+      <c r="D95" s="191"/>
+      <c r="E95" s="191"/>
+      <c r="F95" s="191"/>
+      <c r="G95" s="191"/>
+      <c r="H95" s="191"/>
+      <c r="I95" s="191"/>
+      <c r="J95" s="191"/>
       <c r="K95" s="191"/>
-      <c r="L95" s="190">
-        <v>-8.0</v>
-      </c>
-      <c r="M95" s="190"/>
-      <c r="N95" s="190">
-        <v>6.6228</v>
-      </c>
-      <c r="O95" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P95" s="190" t="s">
-        <v>407</v>
-      </c>
+      <c r="L95" s="191"/>
+      <c r="M95" s="191"/>
+      <c r="N95" s="191"/>
+      <c r="O95" s="191"/>
+      <c r="P95" s="191"/>
       <c r="Q95" s="191"/>
       <c r="R95" s="191"/>
       <c r="S95" s="191"/>
@@ -17899,54 +15471,22 @@
       <c r="AF95" s="191"/>
     </row>
     <row r="96">
-      <c r="A96" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B96" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C96" s="190">
-        <v>498.0</v>
-      </c>
-      <c r="D96" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E96" s="190" t="s">
-        <v>408</v>
-      </c>
-      <c r="F96" s="190" t="s">
-        <v>167</v>
-      </c>
-      <c r="G96" s="190" t="s">
-        <v>92</v>
-      </c>
-      <c r="H96" s="190" t="s">
-        <v>409</v>
-      </c>
-      <c r="I96" s="190" t="s">
-        <v>410</v>
-      </c>
-      <c r="J96" s="190" t="s">
-        <v>411</v>
-      </c>
-      <c r="K96" s="190" t="s">
-        <v>412</v>
-      </c>
-      <c r="L96" s="190">
-        <v>-9.0</v>
-      </c>
-      <c r="M96" s="190">
-        <v>0.008366666666666666</v>
-      </c>
-      <c r="N96" s="190">
-        <v>12.195183333333333</v>
-      </c>
-      <c r="O96" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P96" s="190" t="s">
-        <v>413</v>
-      </c>
+      <c r="A96" s="191"/>
+      <c r="B96" s="191"/>
+      <c r="C96" s="191"/>
+      <c r="D96" s="191"/>
+      <c r="E96" s="191"/>
+      <c r="F96" s="191"/>
+      <c r="G96" s="191"/>
+      <c r="H96" s="191"/>
+      <c r="I96" s="191"/>
+      <c r="J96" s="191"/>
+      <c r="K96" s="191"/>
+      <c r="L96" s="191"/>
+      <c r="M96" s="191"/>
+      <c r="N96" s="191"/>
+      <c r="O96" s="191"/>
+      <c r="P96" s="191"/>
       <c r="Q96" s="191"/>
       <c r="R96" s="191"/>
       <c r="S96" s="191"/>
@@ -17965,50 +15505,22 @@
       <c r="AF96" s="191"/>
     </row>
     <row r="97">
-      <c r="A97" s="190" t="s">
-        <v>100</v>
-      </c>
-      <c r="B97" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C97" s="192">
-        <v>264.0</v>
-      </c>
-      <c r="D97" s="190">
-        <v>0.0</v>
-      </c>
-      <c r="E97" s="190" t="s">
-        <v>56</v>
-      </c>
-      <c r="F97" s="190" t="s">
-        <v>84</v>
-      </c>
-      <c r="G97" s="190" t="s">
-        <v>85</v>
-      </c>
-      <c r="H97" s="190" t="s">
-        <v>414</v>
-      </c>
-      <c r="I97" s="190" t="s">
-        <v>415</v>
-      </c>
-      <c r="J97" s="190" t="s">
-        <v>415</v>
-      </c>
+      <c r="A97" s="191"/>
+      <c r="B97" s="191"/>
+      <c r="C97" s="193"/>
+      <c r="D97" s="191"/>
+      <c r="E97" s="191"/>
+      <c r="F97" s="191"/>
+      <c r="G97" s="191"/>
+      <c r="H97" s="191"/>
+      <c r="I97" s="191"/>
+      <c r="J97" s="191"/>
       <c r="K97" s="191"/>
-      <c r="L97" s="190">
-        <v>-10.0</v>
-      </c>
-      <c r="M97" s="190"/>
-      <c r="N97" s="190">
-        <v>7.3048</v>
-      </c>
-      <c r="O97" s="190" t="s">
-        <v>88</v>
-      </c>
-      <c r="P97" s="190" t="s">
-        <v>416</v>
-      </c>
+      <c r="L97" s="191"/>
+      <c r="M97" s="191"/>
+      <c r="N97" s="191"/>
+      <c r="O97" s="191"/>
+      <c r="P97" s="191"/>
       <c r="Q97" s="191"/>
       <c r="R97" s="191"/>
       <c r="S97" s="191"/>
@@ -18027,48 +15539,22 @@
       <c r="AF97" s="191"/>
     </row>
     <row r="98">
-      <c r="A98" s="190" t="s">
-        <v>138</v>
-      </c>
-      <c r="B98" s="190" t="s">
-        <v>82</v>
-      </c>
-      <c r="C98" s="190">
-        <v>363.0</v>
-      </c>
-      <c r="D98" s="190">
-        <v>91.0</v>
-      </c>
+      <c r="A98" s="191"/>
+      <c r="B98" s="191"/>
+      <c r="C98" s="191"/>
+      <c r="D98" s="191"/>
       <c r="E98" s="191"/>
-      <c r="F98" s="190" t="s">
-        <v>91</v>
-      </c>
-      <c r="G98" s="190" t="s">
-        <v>139</v>
-      </c>
-      <c r="H98" s="190" t="s">
-        <v>417</v>
-      </c>
-      <c r="I98" s="190" t="s">
-        <v>418</v>
-      </c>
-      <c r="J98" s="190" t="s">
-        <v>418</v>
-      </c>
+      <c r="F98" s="191"/>
+      <c r="G98" s="191"/>
+      <c r="H98" s="191"/>
+      <c r="I98" s="191"/>
+      <c r="J98" s="191"/>
       <c r="K98" s="191"/>
-      <c r="L98" s="190">
-        <v>-38.0</v>
-      </c>
-      <c r="M98" s="190"/>
-      <c r="N98" s="190">
-        <v>12.560266666666667</v>
-      </c>
-      <c r="O98" s="190" t="s">
-        <v>142</v>
-      </c>
-      <c r="P98" s="190" t="s">
-        <v>419</v>
-      </c>
+      <c r="L98" s="191"/>
+      <c r="M98" s="191"/>
+      <c r="N98" s="191"/>
+      <c r="O98" s="191"/>
+      <c r="P98" s="191"/>
       <c r="Q98" s="191"/>
       <c r="R98" s="191"/>
       <c r="S98" s="191"/>
@@ -27433,73 +24919,73 @@
         <v>1</v>
       </c>
       <c r="B1" s="190" t="s">
-        <v>420</v>
+        <v>200</v>
       </c>
       <c r="C1" s="190" t="s">
-        <v>421</v>
+        <v>201</v>
       </c>
       <c r="D1" s="190" t="s">
-        <v>422</v>
+        <v>202</v>
       </c>
       <c r="E1" s="190" t="s">
-        <v>423</v>
+        <v>203</v>
       </c>
       <c r="F1" s="190" t="s">
-        <v>424</v>
+        <v>204</v>
       </c>
       <c r="G1" s="190" t="s">
-        <v>425</v>
+        <v>205</v>
       </c>
       <c r="H1" s="190" t="s">
-        <v>426</v>
+        <v>206</v>
       </c>
       <c r="I1" s="190" t="s">
-        <v>427</v>
+        <v>207</v>
       </c>
       <c r="J1" s="190" t="s">
-        <v>428</v>
+        <v>208</v>
       </c>
       <c r="K1" s="190" t="s">
-        <v>429</v>
+        <v>209</v>
       </c>
       <c r="L1" s="190" t="s">
-        <v>430</v>
+        <v>210</v>
       </c>
       <c r="M1" s="190" t="s">
-        <v>431</v>
+        <v>211</v>
       </c>
       <c r="N1" s="190" t="s">
-        <v>432</v>
+        <v>212</v>
       </c>
       <c r="O1" s="190" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P1" s="190" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q1" s="190" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="190" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S1" s="190" t="s">
-        <v>433</v>
+        <v>213</v>
       </c>
       <c r="T1" s="190" t="s">
-        <v>434</v>
+        <v>214</v>
       </c>
       <c r="U1" s="190" t="s">
-        <v>435</v>
+        <v>215</v>
       </c>
       <c r="V1" s="190" t="s">
-        <v>436</v>
+        <v>216</v>
       </c>
       <c r="W1" s="190" t="s">
-        <v>437</v>
+        <v>217</v>
       </c>
       <c r="X1" s="190" t="s">
-        <v>438</v>
+        <v>218</v>
       </c>
       <c r="Y1" s="190" t="s">
         <v>13</v>
@@ -27514,7 +25000,7 @@
         <v>3</v>
       </c>
       <c r="AC1" s="190" t="s">
-        <v>439</v>
+        <v>219</v>
       </c>
       <c r="AD1" s="190" t="s">
         <v>2</v>
@@ -27523,55 +25009,55 @@
         <v>30</v>
       </c>
       <c r="AF1" s="190" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG1" s="190" t="s">
         <v>34</v>
       </c>
-      <c r="AG1" s="190" t="s">
+      <c r="AH1" s="190" t="s">
         <v>35</v>
       </c>
-      <c r="AH1" s="190" t="s">
+      <c r="AI1" s="190" t="s">
         <v>36</v>
       </c>
-      <c r="AI1" s="190" t="s">
-        <v>37</v>
-      </c>
       <c r="AJ1" s="190" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK1" s="190" t="s">
         <v>39</v>
       </c>
-      <c r="AK1" s="190" t="s">
-        <v>40</v>
-      </c>
       <c r="AL1" s="190" t="s">
-        <v>440</v>
+        <v>220</v>
       </c>
       <c r="AM1" s="190" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AN1" s="190" t="s">
-        <v>441</v>
+        <v>221</v>
       </c>
       <c r="AO1" s="190" t="s">
+        <v>47</v>
+      </c>
+      <c r="AP1" s="190" t="s">
         <v>48</v>
       </c>
-      <c r="AP1" s="190" t="s">
+      <c r="AQ1" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="AQ1" s="190" t="s">
-        <v>50</v>
-      </c>
       <c r="AR1" s="190" t="s">
-        <v>442</v>
+        <v>222</v>
       </c>
       <c r="AS1" s="190" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AT1" s="190" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AU1" s="190" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AV1" s="190" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
@@ -27579,19 +25065,19 @@
         <v>45524.0</v>
       </c>
       <c r="B2" s="190" t="s">
-        <v>443</v>
+        <v>223</v>
       </c>
       <c r="C2" s="190" t="s">
-        <v>444</v>
+        <v>224</v>
       </c>
       <c r="D2" s="195" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="195" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G2" s="195" t="s">
-        <v>445</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3">
@@ -27599,19 +25085,19 @@
         <v>45524.0</v>
       </c>
       <c r="B3" s="190" t="s">
-        <v>443</v>
+        <v>223</v>
       </c>
       <c r="C3" s="190" t="s">
-        <v>446</v>
+        <v>226</v>
       </c>
       <c r="D3" s="195" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E3" s="195" t="s">
-        <v>447</v>
+        <v>32</v>
       </c>
       <c r="G3" s="195" t="s">
-        <v>448</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
@@ -27619,19 +25105,19 @@
         <v>45524.0</v>
       </c>
       <c r="B4" s="190" t="s">
-        <v>443</v>
+        <v>223</v>
       </c>
       <c r="H4" s="190" t="s">
-        <v>449</v>
+        <v>228</v>
       </c>
       <c r="I4" s="195" t="s">
-        <v>450</v>
+        <v>28</v>
       </c>
       <c r="J4" s="195" t="s">
-        <v>32</v>
+        <v>229</v>
       </c>
       <c r="L4" s="195" t="s">
-        <v>451</v>
+        <v>230</v>
       </c>
       <c r="M4" s="196">
         <v>9.0</v>
@@ -27642,19 +25128,19 @@
         <v>45524.0</v>
       </c>
       <c r="B5" s="190" t="s">
-        <v>443</v>
+        <v>223</v>
       </c>
       <c r="H5" s="190" t="s">
-        <v>452</v>
+        <v>231</v>
       </c>
       <c r="I5" s="195" t="s">
-        <v>32</v>
+        <v>229</v>
       </c>
       <c r="J5" s="195" t="s">
-        <v>453</v>
+        <v>232</v>
       </c>
       <c r="L5" s="195" t="s">
-        <v>454</v>
+        <v>233</v>
       </c>
       <c r="M5" s="196">
         <v>13.0</v>
@@ -27671,19 +25157,19 @@
         <v>45524.0</v>
       </c>
       <c r="B6" s="190" t="s">
-        <v>443</v>
+        <v>223</v>
       </c>
       <c r="H6" s="190" t="s">
-        <v>27</v>
+        <v>234</v>
       </c>
       <c r="I6" s="195" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J6" s="195" t="s">
-        <v>447</v>
+        <v>32</v>
       </c>
       <c r="L6" s="195" t="s">
-        <v>455</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7">
@@ -27691,16 +25177,16 @@
         <v>45524.0</v>
       </c>
       <c r="B7" s="190" t="s">
-        <v>443</v>
+        <v>223</v>
       </c>
       <c r="P7" s="196">
         <v>7.0</v>
       </c>
       <c r="Q7" s="190" t="s">
-        <v>444</v>
+        <v>224</v>
       </c>
       <c r="R7" s="190" t="s">
-        <v>446</v>
+        <v>226</v>
       </c>
       <c r="S7" s="196">
         <v>8461.0</v>
@@ -27754,7 +25240,7 @@
         <v>7.0</v>
       </c>
       <c r="AM7" s="190" t="s">
-        <v>456</v>
+        <v>236</v>
       </c>
       <c r="AN7" s="196">
         <v>1.0</v>
@@ -27822,8 +25308,8 @@
       <c r="T1" s="197"/>
       <c r="U1" s="197"/>
       <c r="V1" s="199">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1TpIiNTfR1pnpn85VWQTTdvQ2Xcr0GStmWJ2UvfKxG_A"", ""Mzdy!ac1:ad200"")"),30.0)</f>
-        <v>30</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1TpIiNTfR1pnpn85VWQTTdvQ2Xcr0GStmWJ2UvfKxG_A"", ""Mzdy!ac1:ad200"")"),31.0)</f>
+        <v>31</v>
       </c>
       <c r="W1" s="200" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"dní")</f>
@@ -27924,10 +25410,10 @@
     </row>
     <row r="4">
       <c r="A4" s="201" t="s">
-        <v>457</v>
+        <v>237</v>
       </c>
       <c r="B4" s="201" t="s">
-        <v>458</v>
+        <v>238</v>
       </c>
       <c r="C4" s="197" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Manažer")</f>
@@ -27987,7 +25473,7 @@
       </c>
       <c r="B5" s="202" t="str">
         <f>IF(OR(E5=Report!$B$1, F5=Report!$B$1, G5=Report!$B$1, H5=Report!$B$1), D5, "")</f>
-        <v>Nedbal Michal</v>
+        <v/>
       </c>
       <c r="C5" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
@@ -28028,8 +25514,8 @@
         <v>432.3078</v>
       </c>
       <c r="W5" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
-        <v>2882.052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
+        <v>2789.082581</v>
       </c>
       <c r="X5" s="197"/>
       <c r="Y5" s="197"/>
@@ -28094,8 +25580,8 @@
         <v>432.3078</v>
       </c>
       <c r="W6" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
-        <v>2882.052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
+        <v>2789.082581</v>
       </c>
       <c r="X6" s="197"/>
       <c r="Y6" s="197"/>
@@ -28154,8 +25640,8 @@
         <v>341.19</v>
       </c>
       <c r="W7" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
-        <v>2274.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
+        <v>2201.225806</v>
       </c>
       <c r="X7" s="197"/>
       <c r="Y7" s="197"/>
@@ -28179,7 +25665,7 @@
       </c>
       <c r="B8" s="202" t="str">
         <f>IF(OR(E8=Report!$B$1, F8=Report!$B$1, G8=Report!$B$1, H8=Report!$B$1), D8, "")</f>
-        <v>Ahurieva Viktoriia</v>
+        <v/>
       </c>
       <c r="C8" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -28223,8 +25709,8 @@
         <v>432.3078</v>
       </c>
       <c r="W8" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
-        <v>2882.052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
+        <v>2789.082581</v>
       </c>
       <c r="X8" s="197"/>
       <c r="Y8" s="197"/>
@@ -28248,7 +25734,7 @@
       </c>
       <c r="B9" s="202" t="str">
         <f>IF(OR(E9=Report!$B$1, F9=Report!$B$1, G9=Report!$B$1, H9=Report!$B$1), D9, "")</f>
-        <v>Pešová Hana</v>
+        <v/>
       </c>
       <c r="C9" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
@@ -28286,8 +25772,8 @@
         <v>341.19</v>
       </c>
       <c r="W9" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
-        <v>2274.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
+        <v>2201.225806</v>
       </c>
       <c r="X9" s="197"/>
       <c r="Y9" s="197"/>
@@ -28307,11 +25793,11 @@
     <row r="10">
       <c r="A10" s="197" t="str">
         <f>IF(AND(B10&lt;&gt;"", C10=TRUE, E10=Report!$B$1), B10, "")</f>
-        <v>Šebesta Tomáš</v>
+        <v/>
       </c>
       <c r="B10" s="202" t="str">
         <f>IF(OR(E10=Report!$B$1, F10=Report!$B$1, G10=Report!$B$1, H10=Report!$B$1), D10, "")</f>
-        <v>Šebesta Tomáš</v>
+        <v/>
       </c>
       <c r="C10" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
@@ -28355,8 +25841,8 @@
         <v>432.3078</v>
       </c>
       <c r="W10" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
-        <v>2882.052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
+        <v>2789.082581</v>
       </c>
       <c r="X10" s="197"/>
       <c r="Y10" s="197"/>
@@ -28535,8 +26021,8 @@
         <v>341.19</v>
       </c>
       <c r="W13" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
-        <v>2274.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
+        <v>2201.225806</v>
       </c>
       <c r="X13" s="197"/>
       <c r="Y13" s="197"/>
@@ -28661,8 +26147,8 @@
         <v>341.19</v>
       </c>
       <c r="W15" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
-        <v>2274.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
+        <v>2201.225806</v>
       </c>
       <c r="X15" s="197"/>
       <c r="Y15" s="197"/>
@@ -28682,11 +26168,11 @@
     <row r="16">
       <c r="A16" s="197" t="str">
         <f>IF(AND(B16&lt;&gt;"", C16=TRUE, E16=Report!$B$1), B16, "")</f>
-        <v>Nováková Adéla</v>
+        <v/>
       </c>
       <c r="B16" s="202" t="str">
         <f>IF(OR(E16=Report!$B$1, F16=Report!$B$1, G16=Report!$B$1, H16=Report!$B$1), D16, "")</f>
-        <v>Nováková Adéla</v>
+        <v/>
       </c>
       <c r="C16" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
@@ -28724,8 +26210,8 @@
         <v>341.19</v>
       </c>
       <c r="W16" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2274.6)</f>
-        <v>2274.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2201.2258064516127)</f>
+        <v>2201.225806</v>
       </c>
       <c r="X16" s="197"/>
       <c r="Y16" s="197"/>
@@ -28869,7 +26355,7 @@
       </c>
       <c r="B19" s="202" t="str">
         <f>IF(OR(E19=Report!$B$1, F19=Report!$B$1, G19=Report!$B$1, H19=Report!$B$1), D19, "")</f>
-        <v/>
+        <v>Rothová Anastasia</v>
       </c>
       <c r="C19" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -29030,8 +26516,8 @@
         <v>432.3078</v>
       </c>
       <c r="W21" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
-        <v>2882.052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
+        <v>2789.082581</v>
       </c>
       <c r="X21" s="197"/>
       <c r="Y21" s="197"/>
@@ -29051,11 +26537,11 @@
     <row r="22">
       <c r="A22" s="197" t="str">
         <f>IF(AND(B22&lt;&gt;"", C22=TRUE, E22=Report!$B$1), B22, "")</f>
-        <v/>
+        <v>Roth Stanislav ml.</v>
       </c>
       <c r="B22" s="202" t="str">
         <f>IF(OR(E22=Report!$B$1, F22=Report!$B$1, G22=Report!$B$1, H22=Report!$B$1), D22, "")</f>
-        <v/>
+        <v>Roth Stanislav ml.</v>
       </c>
       <c r="C22" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),TRUE)</f>
@@ -29090,8 +26576,8 @@
         <v>432.3078</v>
       </c>
       <c r="W22" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2882.052)</f>
-        <v>2882.052</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2789.082580645161)</f>
+        <v>2789.082581</v>
       </c>
       <c r="X22" s="197"/>
       <c r="Y22" s="197"/>
@@ -29115,7 +26601,7 @@
       </c>
       <c r="B23" s="202" t="str">
         <f>IF(OR(E23=Report!$B$1, F23=Report!$B$1, G23=Report!$B$1, H23=Report!$B$1), D23, "")</f>
-        <v>Makula Radek</v>
+        <v/>
       </c>
       <c r="C23" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -29298,20 +26784,14 @@
       </c>
       <c r="B26" s="202" t="str">
         <f>IF(OR(E26=Report!$B$1, F26=Report!$B$1, G26=Report!$B$1, H26=Report!$B$1), D26, "")</f>
-        <v>Bušek Pavel</v>
+        <v/>
       </c>
       <c r="C26" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bušek Pavel")</f>
-        <v>Bušek Pavel</v>
-      </c>
-      <c r="E26" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="D26" s="197"/>
+      <c r="E26" s="197"/>
       <c r="F26" s="197"/>
       <c r="G26" s="197"/>
       <c r="H26" s="197"/>
@@ -29329,8 +26809,8 @@
       <c r="T26" s="197"/>
       <c r="U26" s="197"/>
       <c r="V26" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W26" s="200">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -29484,7 +26964,7 @@
       </c>
       <c r="B29" s="202" t="str">
         <f>IF(OR(E29=Report!$B$1, F29=Report!$B$1, G29=Report!$B$1, H29=Report!$B$1), D29, "")</f>
-        <v/>
+        <v>Raboch Tomáš</v>
       </c>
       <c r="C29" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -29667,7 +27147,7 @@
       </c>
       <c r="B32" s="202" t="str">
         <f>IF(OR(E32=Report!$B$1, F32=Report!$B$1, G32=Report!$B$1, H32=Report!$B$1), D32, "")</f>
-        <v/>
+        <v>Kratochvíl Kryštof</v>
       </c>
       <c r="C32" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -29910,7 +27390,7 @@
       </c>
       <c r="B36" s="202" t="str">
         <f>IF(OR(E36=Report!$B$1, F36=Report!$B$1, G36=Report!$B$1, H36=Report!$B$1), D36, "")</f>
-        <v/>
+        <v>Tůma Vladimír</v>
       </c>
       <c r="C36" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -30030,7 +27510,7 @@
       </c>
       <c r="B38" s="202" t="str">
         <f>IF(OR(E38=Report!$B$1, F38=Report!$B$1, G38=Report!$B$1, H38=Report!$B$1), D38, "")</f>
-        <v>Putna Jaroslav</v>
+        <v/>
       </c>
       <c r="C38" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -30093,7 +27573,7 @@
       </c>
       <c r="B39" s="202" t="str">
         <f>IF(OR(E39=Report!$B$1, F39=Report!$B$1, G39=Report!$B$1, H39=Report!$B$1), D39, "")</f>
-        <v>Kopic Jakub</v>
+        <v/>
       </c>
       <c r="C39" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -30162,7 +27642,7 @@
       </c>
       <c r="B40" s="202" t="str">
         <f>IF(OR(E40=Report!$B$1, F40=Report!$B$1, G40=Report!$B$1, H40=Report!$B$1), D40, "")</f>
-        <v>Fáberová Kateřina</v>
+        <v/>
       </c>
       <c r="C40" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -32145,7 +29625,7 @@
       <c r="A80" s="197"/>
       <c r="B80" s="202" t="str">
         <f>IF(OR(E80=Report!$B$1, F80=Report!$B$1, G80=Report!$B$1, H80=Report!$B$1), D80, "")</f>
-        <v>Hanibal Filip</v>
+        <v/>
       </c>
       <c r="C80" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -32496,7 +29976,7 @@
       <c r="A86" s="197"/>
       <c r="B86" s="202" t="str">
         <f>IF(OR(E86=Report!$B$1, F86=Report!$B$1, G86=Report!$B$1, H86=Report!$B$1), D86, "")</f>
-        <v>Mikuš Pavel</v>
+        <v/>
       </c>
       <c r="C86" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -32610,7 +30090,7 @@
       <c r="A88" s="197"/>
       <c r="B88" s="202" t="str">
         <f>IF(OR(E88=Report!$B$1, F88=Report!$B$1, G88=Report!$B$1, H88=Report!$B$1), D88, "")</f>
-        <v>Šmídová Sabina</v>
+        <v/>
       </c>
       <c r="C88" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -32733,7 +30213,7 @@
       <c r="A90" s="197"/>
       <c r="B90" s="202" t="str">
         <f>IF(OR(E90=Report!$B$1, F90=Report!$B$1, G90=Report!$B$1, H90=Report!$B$1), D90, "")</f>
-        <v>Kormash Liubov</v>
+        <v/>
       </c>
       <c r="C90" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -32799,14 +30279,8 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D91" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Čermák Jakub")</f>
-        <v>Čermák Jakub</v>
-      </c>
-      <c r="E91" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Chodov")</f>
-        <v>Chodov</v>
-      </c>
+      <c r="D91" s="197"/>
+      <c r="E91" s="197"/>
       <c r="F91" s="197"/>
       <c r="G91" s="197"/>
       <c r="H91" s="197"/>
@@ -32824,8 +30298,8 @@
       <c r="T91" s="197"/>
       <c r="U91" s="197"/>
       <c r="V91" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W91" s="200">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -32970,7 +30444,7 @@
       <c r="A94" s="197"/>
       <c r="B94" s="202" t="str">
         <f>IF(OR(E94=Report!$B$1, F94=Report!$B$1, G94=Report!$B$1, H94=Report!$B$1), D94, "")</f>
-        <v>Vychivskyi Volodymyr</v>
+        <v/>
       </c>
       <c r="C94" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -33033,20 +30507,14 @@
       <c r="A95" s="197"/>
       <c r="B95" s="202" t="str">
         <f>IF(OR(E95=Report!$B$1, F95=Report!$B$1, G95=Report!$B$1, H95=Report!$B$1), D95, "")</f>
-        <v>Dvořák Radim</v>
+        <v/>
       </c>
       <c r="C95" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D95" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Dvořák Radim")</f>
-        <v>Dvořák Radim</v>
-      </c>
-      <c r="E95" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="D95" s="197"/>
+      <c r="E95" s="197"/>
       <c r="F95" s="197"/>
       <c r="G95" s="197"/>
       <c r="H95" s="197"/>
@@ -33064,8 +30532,8 @@
       <c r="T95" s="197"/>
       <c r="U95" s="197"/>
       <c r="V95" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W95" s="200">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -33090,7 +30558,7 @@
       <c r="A96" s="197"/>
       <c r="B96" s="202" t="str">
         <f>IF(OR(E96=Report!$B$1, F96=Report!$B$1, G96=Report!$B$1, H96=Report!$B$1), D96, "")</f>
-        <v>Hřebík Martin</v>
+        <v/>
       </c>
       <c r="C96" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -33130,12 +30598,12 @@
       <c r="T96" s="197"/>
       <c r="U96" s="197"/>
       <c r="V96" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),389.6925)</f>
-        <v>389.6925</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),386.68199999999996)</f>
+        <v>386.682</v>
       </c>
       <c r="W96" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2597.95)</f>
-        <v>2597.95</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2494.722580645161)</f>
+        <v>2494.722581</v>
       </c>
       <c r="X96" s="197"/>
       <c r="Y96" s="197"/>
@@ -33213,7 +30681,7 @@
       <c r="A98" s="197"/>
       <c r="B98" s="202" t="str">
         <f>IF(OR(E98=Report!$B$1, F98=Report!$B$1, G98=Report!$B$1, H98=Report!$B$1), D98, "")</f>
-        <v>Reischl Jan</v>
+        <v/>
       </c>
       <c r="C98" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -33279,7 +30747,7 @@
       <c r="A99" s="197"/>
       <c r="B99" s="202" t="str">
         <f>IF(OR(E99=Report!$B$1, F99=Report!$B$1, G99=Report!$B$1, H99=Report!$B$1), D99, "")</f>
-        <v/>
+        <v>Mikešová Adéla</v>
       </c>
       <c r="C99" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -33450,20 +30918,14 @@
       <c r="A102" s="197"/>
       <c r="B102" s="202" t="str">
         <f>IF(OR(E102=Report!$B$1, F102=Report!$B$1, G102=Report!$B$1, H102=Report!$B$1), D102, "")</f>
-        <v>Kináč Jozef</v>
+        <v/>
       </c>
       <c r="C102" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D102" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Kináč Jozef")</f>
-        <v>Kináč Jozef</v>
-      </c>
-      <c r="E102" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="D102" s="197"/>
+      <c r="E102" s="197"/>
       <c r="F102" s="197"/>
       <c r="G102" s="197"/>
       <c r="H102" s="197"/>
@@ -33481,8 +30943,8 @@
       <c r="T102" s="197"/>
       <c r="U102" s="197"/>
       <c r="V102" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W102" s="200">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -33507,20 +30969,14 @@
       <c r="A103" s="197"/>
       <c r="B103" s="202" t="str">
         <f>IF(OR(E103=Report!$B$1, F103=Report!$B$1, G103=Report!$B$1, H103=Report!$B$1), D103, "")</f>
-        <v>Bednařík Peter</v>
+        <v/>
       </c>
       <c r="C103" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D103" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bednařík Peter")</f>
-        <v>Bednařík Peter</v>
-      </c>
-      <c r="E103" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="D103" s="197"/>
+      <c r="E103" s="197"/>
       <c r="F103" s="197"/>
       <c r="G103" s="197"/>
       <c r="H103" s="197"/>
@@ -33538,8 +30994,8 @@
       <c r="T103" s="197"/>
       <c r="U103" s="197"/>
       <c r="V103" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W103" s="200">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -33564,7 +31020,7 @@
       <c r="A104" s="197"/>
       <c r="B104" s="202" t="str">
         <f>IF(OR(E104=Report!$B$1, F104=Report!$B$1, G104=Report!$B$1, H104=Report!$B$1), D104, "")</f>
-        <v>Kulinič Michail</v>
+        <v/>
       </c>
       <c r="C104" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -33681,20 +31137,14 @@
       <c r="A106" s="197"/>
       <c r="B106" s="202" t="str">
         <f>IF(OR(E106=Report!$B$1, F106=Report!$B$1, G106=Report!$B$1, H106=Report!$B$1), D106, "")</f>
-        <v>Čonka Ludovít</v>
+        <v/>
       </c>
       <c r="C106" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D106" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Čonka Ludovít")</f>
-        <v>Čonka Ludovít</v>
-      </c>
-      <c r="E106" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="D106" s="197"/>
+      <c r="E106" s="197"/>
       <c r="F106" s="197"/>
       <c r="G106" s="197"/>
       <c r="H106" s="197"/>
@@ -33712,8 +31162,8 @@
       <c r="T106" s="197"/>
       <c r="U106" s="197"/>
       <c r="V106" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W106" s="200">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -33738,7 +31188,7 @@
       <c r="A107" s="197"/>
       <c r="B107" s="202" t="str">
         <f>IF(OR(E107=Report!$B$1, F107=Report!$B$1, G107=Report!$B$1, H107=Report!$B$1), D107, "")</f>
-        <v/>
+        <v>Kaločai Rudolf</v>
       </c>
       <c r="C107" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -33809,7 +31259,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
         <v>Libuš</v>
       </c>
-      <c r="F108" s="197"/>
+      <c r="F108" s="197" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Malešice")</f>
+        <v>Malešice</v>
+      </c>
       <c r="G108" s="197"/>
       <c r="H108" s="197"/>
       <c r="I108" s="197"/>
@@ -33852,7 +31305,7 @@
       <c r="A109" s="197"/>
       <c r="B109" s="202" t="str">
         <f>IF(OR(E109=Report!$B$1, F109=Report!$B$1, G109=Report!$B$1, H109=Report!$B$1), D109, "")</f>
-        <v>Kačena Stanislav</v>
+        <v/>
       </c>
       <c r="C109" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -34023,7 +31476,7 @@
       <c r="A112" s="197"/>
       <c r="B112" s="202" t="str">
         <f>IF(OR(E112=Report!$B$1, F112=Report!$B$1, G112=Report!$B$1, H112=Report!$B$1), D112, "")</f>
-        <v/>
+        <v>Vopatová Anna</v>
       </c>
       <c r="C112" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -34080,7 +31533,7 @@
       <c r="A113" s="197"/>
       <c r="B113" s="202" t="str">
         <f>IF(OR(E113=Report!$B$1, F113=Report!$B$1, G113=Report!$B$1, H113=Report!$B$1), D113, "")</f>
-        <v/>
+        <v>Vopatová Šárka</v>
       </c>
       <c r="C113" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -34228,8 +31681,8 @@
       <c r="T115" s="197"/>
       <c r="U115" s="197"/>
       <c r="V115" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),231.474)</f>
-        <v>231.474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
+        <v>250.206</v>
       </c>
       <c r="W115" s="200">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -34368,24 +31821,15 @@
       <c r="A118" s="197"/>
       <c r="B118" s="202" t="str">
         <f>IF(OR(E118=Report!$B$1, F118=Report!$B$1, G118=Report!$B$1, H118=Report!$B$1), D118, "")</f>
-        <v>Novák Dalibor</v>
+        <v/>
       </c>
       <c r="C118" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D118" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Novák Dalibor")</f>
-        <v>Novák Dalibor</v>
-      </c>
-      <c r="E118" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Libuš")</f>
-        <v>Libuš</v>
-      </c>
-      <c r="F118" s="197" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Prosek")</f>
-        <v>Prosek</v>
-      </c>
+      <c r="D118" s="197"/>
+      <c r="E118" s="197"/>
+      <c r="F118" s="197"/>
       <c r="G118" s="197"/>
       <c r="H118" s="197"/>
       <c r="I118" s="197"/>
@@ -34402,8 +31846,8 @@
       <c r="T118" s="197"/>
       <c r="U118" s="197"/>
       <c r="V118" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),250.20600000000002)</f>
-        <v>250.206</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="W118" s="200">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -34428,7 +31872,7 @@
       <c r="A119" s="197"/>
       <c r="B119" s="202" t="str">
         <f>IF(OR(E119=Report!$B$1, F119=Report!$B$1, G119=Report!$B$1, H119=Report!$B$1), D119, "")</f>
-        <v/>
+        <v>Světlík František</v>
       </c>
       <c r="C119" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -34485,7 +31929,7 @@
       <c r="A120" s="197"/>
       <c r="B120" s="202" t="str">
         <f>IF(OR(E120=Report!$B$1, F120=Report!$B$1, G120=Report!$B$1, H120=Report!$B$1), D120, "")</f>
-        <v/>
+        <v>Ženíšek Lukáš</v>
       </c>
       <c r="C120" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -34599,7 +32043,7 @@
       <c r="A122" s="197"/>
       <c r="B122" s="202" t="str">
         <f>IF(OR(E122=Report!$B$1, F122=Report!$B$1, G122=Report!$B$1, H122=Report!$B$1), D122, "")</f>
-        <v/>
+        <v>Roth Stanislav st.</v>
       </c>
       <c r="C122" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
@@ -34634,8 +32078,8 @@
         <v>49506</v>
       </c>
       <c r="W122" s="200">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1650.2)</f>
-        <v>1650.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1596.967741935484)</f>
+        <v>1596.967742</v>
       </c>
       <c r="X122" s="197"/>
       <c r="Y122" s="197"/>
@@ -34827,7 +32271,7 @@
       <c r="A126" s="197"/>
       <c r="B126" s="202" t="str">
         <f>IF(OR(E126=Report!$B$1, F126=Report!$B$1, G126=Report!$B$1, H126=Report!$B$1), D126, "")</f>
-        <v/>
+        <v>Irena Kovacsova</v>
       </c>
       <c r="C126" s="197" t="b">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),FALSE)</f>
